--- a/Results/Phase 2/Hydrogen/hydrogen acidification results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen acidification results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0109151346371606</v>
+        <v>0.01091513463716061</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0114699456424947</v>
+        <v>0.01146994564249471</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02206836822124691</v>
+        <v>0.02206836822124689</v>
       </c>
       <c r="F2" t="n">
         <v>0.01122832170963525</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0121082792279671</v>
+        <v>0.01210827922796711</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="J2" t="n">
         <v>0.01167450390902263</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0124883450968028</v>
+        <v>0.01248834509680281</v>
       </c>
       <c r="N2" t="n">
         <v>0.01154725716353045</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="V2" t="n">
-        <v>0.006684555280670224</v>
+        <v>0.006684555280670228</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01138388677450655</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0117097692454488</v>
+        <v>0.01170976924544881</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +683,7 @@
         <v>0.01087263557402776</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02194099255058726</v>
+        <v>0.02194099255058725</v>
       </c>
       <c r="F3" t="n">
         <v>0.01087263557402776</v>
@@ -734,7 +734,7 @@
         <v>0.01087263557402776</v>
       </c>
       <c r="V3" t="n">
-        <v>0.006406592279095964</v>
+        <v>0.006406592279095969</v>
       </c>
       <c r="W3" t="n">
         <v>0.01087263557402776</v>
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2866454977028782</v>
+        <v>0.2866454977028784</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07593941329498317</v>
+        <v>0.07593941329498322</v>
       </c>
       <c r="D4" t="n">
         <v>0.2454846214426774</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1439934821261117</v>
+        <v>0.1439934821261115</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1754363176595919</v>
+        <v>0.1754363176595915</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4017717473905865</v>
+        <v>0.401771747390586</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1962658423428211</v>
+        <v>0.1962658423428212</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2681345708915646</v>
+        <v>0.2681345708915641</v>
       </c>
       <c r="J4" t="n">
         <v>0.2985664635798611</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3728369181203214</v>
+        <v>0.3728369181203215</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4766240255878497</v>
+        <v>0.4766240255878503</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5606098361049622</v>
+        <v>0.5606098361049614</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4520200866381898</v>
+        <v>0.4520200866381894</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2568593550927983</v>
+        <v>0.256859355092798</v>
       </c>
       <c r="P4" t="n">
         <v>0.259049340866974</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.153243001793791</v>
+        <v>0.1532430017937907</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1573797288162011</v>
+        <v>0.1573797288162014</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2929103742202725</v>
+        <v>0.2929103742202722</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2730232325704274</v>
+        <v>0.2730232325704275</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4520200866381898</v>
+        <v>0.4520200866381891</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1156908871692334</v>
+        <v>0.115690887169233</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2880097361518295</v>
+        <v>0.2880097361518293</v>
       </c>
       <c r="X4" t="n">
         <v>0.2337616156675126</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2970343743062908</v>
+        <v>0.2970343743062901</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2008678914013187</v>
+        <v>0.2008678914013182</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2996509794698131</v>
+        <v>0.2996509794698128</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6875225603538027</v>
+        <v>0.6875225603538018</v>
       </c>
     </row>
     <row r="5">
@@ -853,40 +853,40 @@
         <v>0.009071621357754332</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="F5" t="n">
         <v>0.009071621357754332</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009049184086679526</v>
+        <v>0.009049184086679528</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="M5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="O5" t="n">
         <v>0.009071621357754332</v>
@@ -898,19 +898,19 @@
         <v>0.009071621357754332</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="U5" t="n">
-        <v>0.008863895436332937</v>
+        <v>0.00886389543633294</v>
       </c>
       <c r="V5" t="n">
-        <v>0.008922713258657915</v>
+        <v>0.00892271325865791</v>
       </c>
       <c r="W5" t="n">
         <v>0.009071621357754332</v>
@@ -919,13 +919,13 @@
         <v>0.009071621357754332</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.008863895436332937</v>
+        <v>0.00886389543633294</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00907162135775433</v>
+        <v>0.009071621357754332</v>
       </c>
       <c r="AB5" t="n">
         <v>0.009071621357754332</v>
@@ -938,58 +938,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01109596187592395</v>
+        <v>0.01709383908617393</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01709383908617391</v>
+        <v>0.01709383908617393</v>
       </c>
       <c r="D6" t="n">
         <v>0.01109596187592395</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01709383908617391</v>
+        <v>0.01109596187592395</v>
       </c>
       <c r="F6" t="n">
+        <v>0.01709383908617393</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01709383908617393</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.01709383908617393</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.01109596187592395</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.01109596187592395</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.01709383908617391</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.01709383908617391</v>
-      </c>
       <c r="J6" t="n">
-        <v>0.01107352460484909</v>
+        <v>0.01707140181509911</v>
       </c>
       <c r="K6" t="n">
         <v>0.01109596187592395</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01709383908617391</v>
+        <v>0.01109596187592395</v>
       </c>
       <c r="M6" t="n">
         <v>0.01109596187592395</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01112412555437007</v>
+        <v>0.01112412555437004</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01711841518271239</v>
+        <v>0.01711841518271241</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01711841744852056</v>
+        <v>0.01711841744852059</v>
       </c>
       <c r="Q6" t="n">
         <v>0.01109596187592395</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01709383908617391</v>
+        <v>0.01109596187592395</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01709383908617391</v>
+        <v>0.01709383908617393</v>
       </c>
       <c r="T6" t="n">
         <v>0.01109596187592395</v>
@@ -1001,22 +1001,22 @@
         <v>0.01694493098707749</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01130776170702383</v>
+        <v>0.01711841692072275</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01709383908617391</v>
+        <v>0.01709383908617393</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01123450664628586</v>
+        <v>0.0112345066462861</v>
       </c>
       <c r="Z6" t="n">
         <v>0.01109596187592395</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01709383908617391</v>
+        <v>0.01109596187592395</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01125271466687818</v>
+        <v>0.01125271466687817</v>
       </c>
     </row>
     <row r="7">
@@ -1050,7 +1050,7 @@
         <v>0.01385523807144656</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01383280080037177</v>
+        <v>0.01383280080037176</v>
       </c>
       <c r="K7" t="n">
         <v>0.01385523807144656</v>
@@ -1086,7 +1086,7 @@
         <v>0.01384944309929192</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01370632997235015</v>
+        <v>0.01370632997235014</v>
       </c>
       <c r="W7" t="n">
         <v>0.01385523807144656</v>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02279100112789014</v>
+        <v>0.02279100112789017</v>
       </c>
       <c r="C8" t="n">
         <v>0.03234403982559669</v>
@@ -1123,13 +1123,13 @@
         <v>0.03234403982559669</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03234403982559669</v>
+        <v>0.02725732851620648</v>
       </c>
       <c r="F8" t="n">
         <v>0.0242792529082095</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03234403982559669</v>
+        <v>0.03432492463178164</v>
       </c>
       <c r="H8" t="n">
         <v>0.03234403982559669</v>
@@ -1147,19 +1147,19 @@
         <v>0.03234403982559669</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03234403982559669</v>
+        <v>0.03234403982559598</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02493883664617232</v>
+        <v>0.02493883664617234</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02697385077788556</v>
+        <v>0.0269738507778856</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02647501964139749</v>
+        <v>0.0264750196413975</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02091361098649705</v>
+        <v>0.02091361098649704</v>
       </c>
       <c r="R8" t="n">
         <v>0.03234403982559669</v>
@@ -1171,28 +1171,28 @@
         <v>0.03234403982559669</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02646149428220057</v>
+        <v>0.02767695959831504</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03219513172650024</v>
+        <v>0.02957932273122089</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03234591727084572</v>
+        <v>0.03234591727084574</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02178916596495639</v>
+        <v>0.02178916596495641</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.04183493374701377</v>
+        <v>0.04183493374701382</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03234403982559669</v>
+        <v>0.02261354852960352</v>
       </c>
       <c r="AA8" t="n">
         <v>0.03234403982559669</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04232298755689223</v>
+        <v>0.04232298755689227</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02866058217707964</v>
+        <v>0.02866058217707963</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03310754826841217</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.02111446457264386</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.0344418386903618</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="J9" t="n">
         <v>0.03441940121080631</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03635773952895423</v>
+        <v>0.03635773952895421</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03677441509002558</v>
+        <v>0.03677441509002556</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03444183869036182</v>
+        <v>0.0344418386903618</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03429293038278469</v>
+        <v>0.04096436836872477</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03095625510224017</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03444183848188112</v>
+        <v>0.03444183848188111</v>
       </c>
     </row>
     <row r="10">
@@ -1290,85 +1290,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.004865348706484717</v>
+        <v>0.004865348706484722</v>
       </c>
       <c r="C10" t="n">
         <v>0.009682575942331489</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006434143531237969</v>
+        <v>0.006434143531237974</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01918887680143511</v>
+        <v>0.01918887680143506</v>
       </c>
       <c r="F10" t="n">
-        <v>0.007864271614443571</v>
+        <v>0.00786427161444357</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002571594502572803</v>
+        <v>0.002571594502572806</v>
       </c>
       <c r="H10" t="n">
-        <v>0.007541530045392093</v>
+        <v>0.007541530045392104</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00606038057997374</v>
+        <v>0.006060380579973742</v>
       </c>
       <c r="J10" t="n">
-        <v>0.004933282729923347</v>
+        <v>0.004933282729923351</v>
       </c>
       <c r="K10" t="n">
-        <v>0.003920000148833844</v>
+        <v>0.00392000014883384</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001415186855610067</v>
+        <v>0.001415186855610076</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0005083607992275855</v>
+        <v>0.000508360799227579</v>
       </c>
       <c r="N10" t="n">
-        <v>0.005960548253119924</v>
+        <v>0.005960548253119922</v>
       </c>
       <c r="O10" t="n">
-        <v>0.00539157066046313</v>
+        <v>0.005391570660463136</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005565737120058353</v>
+        <v>0.005565737120058345</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.008146868388164448</v>
+        <v>0.008146868388164454</v>
       </c>
       <c r="R10" t="n">
         <v>0.008205085785081404</v>
       </c>
       <c r="S10" t="n">
-        <v>0.004929576070348863</v>
+        <v>0.004929576070348867</v>
       </c>
       <c r="T10" t="n">
-        <v>0.005925745799598389</v>
+        <v>0.005925745799598391</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001729987247323462</v>
+        <v>0.00172998724732346</v>
       </c>
       <c r="V10" t="n">
-        <v>0.004207491983780709</v>
+        <v>0.004207491983780716</v>
       </c>
       <c r="W10" t="n">
         <v>0.005328294141769749</v>
       </c>
       <c r="X10" t="n">
-        <v>0.006598736037024519</v>
+        <v>0.006598736037024523</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.005151607319464382</v>
+        <v>0.005151607319464384</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.00688094634191928</v>
+        <v>0.006880946341919286</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.005135176156942672</v>
+        <v>0.005135176156942673</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.001481655311312953</v>
+        <v>-0.00148165531131294</v>
       </c>
     </row>
     <row r="11">
@@ -1378,85 +1378,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.008976434576629382</v>
+        <v>0.008976434576629387</v>
       </c>
       <c r="C11" t="n">
         <v>0.01037365371224378</v>
       </c>
       <c r="D11" t="n">
-        <v>0.009450417618390458</v>
+        <v>0.009450417618390468</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02081614678491016</v>
+        <v>0.02081614678491014</v>
       </c>
       <c r="F11" t="n">
-        <v>0.009859506520937342</v>
+        <v>0.009859506520937353</v>
       </c>
       <c r="G11" t="n">
-        <v>0.008331279086606812</v>
+        <v>0.008331279086606819</v>
       </c>
       <c r="H11" t="n">
         <v>0.01019410561431613</v>
       </c>
       <c r="I11" t="n">
-        <v>0.009520177887407499</v>
+        <v>0.009520177887407496</v>
       </c>
       <c r="J11" t="n">
-        <v>0.008988127115741828</v>
+        <v>0.008988127115741831</v>
       </c>
       <c r="K11" t="n">
-        <v>0.008546297970251127</v>
+        <v>0.008546297970251143</v>
       </c>
       <c r="L11" t="n">
-        <v>0.007406599939467973</v>
+        <v>0.00740659993946798</v>
       </c>
       <c r="M11" t="n">
-        <v>0.007772567045284754</v>
+        <v>0.00777256704528477</v>
       </c>
       <c r="N11" t="n">
         <v>0.009312241778623902</v>
       </c>
       <c r="O11" t="n">
-        <v>0.009215867242659406</v>
+        <v>0.009215867242659418</v>
       </c>
       <c r="P11" t="n">
-        <v>0.00929511353681082</v>
+        <v>0.009295113536810826</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01046953648937639</v>
+        <v>0.01046953648937641</v>
       </c>
       <c r="R11" t="n">
         <v>0.01049602559050144</v>
       </c>
       <c r="S11" t="n">
-        <v>0.009005658231868037</v>
+        <v>0.009005658231868049</v>
       </c>
       <c r="T11" t="n">
-        <v>0.009458918633281115</v>
+        <v>0.009458918633281126</v>
       </c>
       <c r="U11" t="n">
-        <v>0.007549835120906883</v>
+        <v>0.007549835120906887</v>
       </c>
       <c r="V11" t="n">
-        <v>0.005683957638184967</v>
+        <v>0.00568395763818497</v>
       </c>
       <c r="W11" t="n">
-        <v>0.009187076225003626</v>
+        <v>0.009187076225003638</v>
       </c>
       <c r="X11" t="n">
-        <v>0.009765131336002651</v>
+        <v>0.009765131336002663</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.009106683157787192</v>
+        <v>0.009106683157787199</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.009567655453138368</v>
+        <v>0.009567655453138375</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.009099206926476814</v>
+        <v>0.009099206926476816</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.006088527521829757</v>
+        <v>0.006088527521829774</v>
       </c>
     </row>
   </sheetData>
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.009451541139918643</v>
+        <v>0.009451541139918638</v>
       </c>
       <c r="C2" t="n">
         <v>0.009481071465067418</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009479010171189036</v>
+        <v>0.009479010171189038</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02090521649359467</v>
+        <v>0.02090521649359468</v>
       </c>
       <c r="F2" t="n">
         <v>0.009505377981698836</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009410659042310395</v>
+        <v>0.009410659042310393</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009487755433044844</v>
+        <v>0.009487755433044845</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009491938287052843</v>
+        <v>0.009491938287052836</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009540867541665665</v>
+        <v>0.009540867541665662</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009536849154368201</v>
+        <v>0.009536849154368199</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009547930061144783</v>
+        <v>0.009547930061144778</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00949073385964349</v>
+        <v>0.009490733859643484</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00949809581317323</v>
+        <v>0.009498095813173226</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009511261580707283</v>
+        <v>0.009511261580707284</v>
       </c>
       <c r="P2" t="n">
-        <v>0.009507298289830914</v>
+        <v>0.00950729828983091</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.009475018991756843</v>
+        <v>0.009475018991756842</v>
       </c>
       <c r="R2" t="n">
-        <v>0.009526068730145297</v>
+        <v>0.009526068730145301</v>
       </c>
       <c r="S2" t="n">
-        <v>0.009529984369172703</v>
+        <v>0.009529984369172708</v>
       </c>
       <c r="T2" t="n">
         <v>0.009491750299950105</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009575611387782502</v>
+        <v>0.009575611387782512</v>
       </c>
       <c r="V2" t="n">
-        <v>0.005044872716861364</v>
+        <v>0.005044872716861356</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009559002696844329</v>
+        <v>0.009559002696844322</v>
       </c>
       <c r="X2" t="n">
         <v>0.01121384195915816</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01050665952635869</v>
+        <v>0.01050665952635868</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009525403590584961</v>
+        <v>0.009525403590584958</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.009668725836782258</v>
+        <v>0.009668725836782256</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00934995673762145</v>
+        <v>0.009349956737621443</v>
       </c>
     </row>
     <row r="3">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009589576590701745</v>
+        <v>0.009589576590701743</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02118587257816849</v>
+        <v>0.02118587257816848</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009583710689150376</v>
+        <v>0.009583710689150374</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009451161726197596</v>
+        <v>0.009451161726197595</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009569760525957904</v>
+        <v>0.009569760525957908</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009578574843225584</v>
+        <v>0.009578574843225583</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009566794952658173</v>
+        <v>0.009566794952658171</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="R3" t="n">
-        <v>0.009540972692626734</v>
+        <v>0.009540972692626732</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="U3" t="n">
         <v>0.009564823926976777</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005020084210727666</v>
+        <v>0.005020084210727665</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009527128965965149</v>
+        <v>0.009527128965965147</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009574142993357243</v>
+        <v>0.009574142993357241</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009572970915732911</v>
+        <v>0.00957297091573291</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009451065452742482</v>
+        <v>0.00945106545274248</v>
       </c>
     </row>
     <row r="4">
@@ -1798,40 +1798,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0174684866017474</v>
+        <v>0.01746848660174741</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02205423528131391</v>
+        <v>0.02205423528131395</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02537879617971746</v>
+        <v>0.02537879617971748</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01985237944148176</v>
+        <v>0.01985237944148182</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02975721022089047</v>
+        <v>0.02975721022089046</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03343945721940383</v>
+        <v>0.03343945721940363</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02864213871825121</v>
+        <v>0.02864213871825119</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02898446413278421</v>
+        <v>0.02898446413278418</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03993820921660916</v>
+        <v>0.03993820921660918</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03704821729990864</v>
+        <v>0.03704821729990865</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0400515751692487</v>
+        <v>0.04005157516924865</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02869295353624575</v>
+        <v>0.02869295353624574</v>
       </c>
       <c r="N4" t="n">
         <v>0.03004073653105688</v>
@@ -1840,43 +1840,43 @@
         <v>0.03094660952788004</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03126991943813118</v>
+        <v>0.03126991943813116</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0237148939311436</v>
+        <v>0.02371489393114361</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04627973212822021</v>
+        <v>0.04627973212822017</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03528768612644342</v>
+        <v>0.0352876861264434</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02889492647930524</v>
+        <v>0.02889492647930527</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0473937909220393</v>
+        <v>0.04739379092203921</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03464507774772498</v>
+        <v>0.03464507774772501</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04486089374738456</v>
+        <v>0.04486089374738451</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4581134571272734</v>
+        <v>0.4581134571272715</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2884575111962951</v>
+        <v>0.288457511196295</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03318363323720287</v>
+        <v>0.03318363323720288</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.07327455542171428</v>
+        <v>0.07327455542171436</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0216139838297646</v>
+        <v>0.02161398382976467</v>
       </c>
     </row>
     <row r="5">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005971281969148843</v>
+        <v>0.00597128196914885</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005971281969148844</v>
+        <v>0.005971281969148852</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005954131876798149</v>
+        <v>0.005954131876798151</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="N5" t="n">
         <v>0.03004073653105688</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005971281969148844</v>
+        <v>0.005971281969148852</v>
       </c>
       <c r="P5" t="n">
-        <v>0.005971281969148844</v>
+        <v>0.005971281969148852</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.005971281969148844</v>
+        <v>0.005971281969148852</v>
       </c>
       <c r="R5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="T5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="U5" t="n">
-        <v>0.005892615724608035</v>
+        <v>0.005892615724608037</v>
       </c>
       <c r="V5" t="n">
         <v>0.005855487883568315</v>
       </c>
       <c r="W5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="X5" t="n">
-        <v>0.005971281969148844</v>
+        <v>0.005971281969148852</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005892615724608035</v>
+        <v>0.005892615724608037</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005971281969148846</v>
+        <v>0.005971281969148855</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.005971281969148844</v>
+        <v>0.005971281969148852</v>
       </c>
     </row>
     <row r="6">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01102519588183277</v>
+        <v>0.007314486334694912</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01102519588183277</v>
+        <v>0.007314486334694912</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01102519588183277</v>
+        <v>0.01102519588183281</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01102519588183277</v>
+        <v>0.007314486334694912</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01102519588183277</v>
+        <v>0.007314486334694912</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007314486334694894</v>
+        <v>0.01102519588183281</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007314486334694894</v>
+        <v>0.01102519588183281</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007314486334694894</v>
+        <v>0.01102519588183281</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007297336242344182</v>
+        <v>0.0110080457894821</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01102519588183277</v>
+        <v>0.007314486334694912</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007314486334694894</v>
+        <v>0.01102519588183281</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007314486334694894</v>
+        <v>0.01102519588183281</v>
       </c>
       <c r="N6" t="n">
         <v>0.03004073653105688</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01108490584839364</v>
+        <v>0.01108490584839365</v>
       </c>
       <c r="P6" t="n">
-        <v>0.007228612657319894</v>
+        <v>0.0110522043131958</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01102519588183277</v>
+        <v>0.01102519588183281</v>
       </c>
       <c r="R6" t="n">
-        <v>0.007314486334694894</v>
+        <v>0.01102519588183281</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007314486334694894</v>
+        <v>0.01102519588183281</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01102519588183277</v>
+        <v>0.007314486334694912</v>
       </c>
       <c r="U6" t="n">
-        <v>0.007314486334694894</v>
+        <v>0.01102519588183281</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007198692249114361</v>
+        <v>0.01090940179625227</v>
       </c>
       <c r="W6" t="n">
-        <v>0.007432977698474333</v>
+        <v>0.007432977698474339</v>
       </c>
       <c r="X6" t="n">
-        <v>0.007314486334694894</v>
+        <v>0.007314486334694912</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.007439041002669797</v>
+        <v>0.007439041002669818</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01102519588183277</v>
+        <v>0.007314486334694912</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.007314486334694894</v>
+        <v>0.007314486334694912</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.007313360697568195</v>
+        <v>0.007313360697568218</v>
       </c>
     </row>
     <row r="7">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009026511243519312</v>
+        <v>0.00902651124351931</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="M7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="N7" t="n">
         <v>0.03004073653105688</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009043539751019743</v>
+        <v>0.009043539751019739</v>
       </c>
       <c r="P7" t="n">
-        <v>0.009043539751019743</v>
+        <v>0.009043539751019739</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="R7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="S7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="U7" t="n">
-        <v>0.009036070572397638</v>
+        <v>0.009036070572397645</v>
       </c>
       <c r="V7" t="n">
         <v>0.00892786725028947</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="X7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.009043661335870017</v>
+        <v>0.009043661335870019</v>
       </c>
     </row>
     <row r="8">
@@ -2150,85 +2150,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01583383929501494</v>
+        <v>0.01583383929501496</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.02257361449573269</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.02257361449573269</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.01898488301230754</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01688381750186065</v>
+        <v>0.01688381750186067</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.02397115078914015</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.02257361449573269</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.02257361449573269</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02255646440338194</v>
+        <v>0.02255646440338202</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.02257361449573269</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.02257361449573269</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.0225736144957317</v>
       </c>
       <c r="N8" t="n">
         <v>0.03004073653105688</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01878488631088666</v>
+        <v>0.01878488631088669</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01843295538818003</v>
+        <v>0.01843295538818005</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01450931964025214</v>
+        <v>0.01450931964025216</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.02257361449573269</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.02257361449573269</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.02257361449573269</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01842087251179466</v>
+        <v>0.01927823174489241</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02245782041015208</v>
+        <v>0.02060935375525005</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02257493905456462</v>
+        <v>0.02257493905456464</v>
       </c>
       <c r="X8" t="n">
-        <v>0.015127033429467</v>
+        <v>0.01512703342946703</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02926491725082901</v>
+        <v>0.02926491725082907</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.0157086445104714</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02257361449573261</v>
+        <v>0.02257361449573269</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.02961387326360173</v>
+        <v>0.0296138732636018</v>
       </c>
     </row>
     <row r="9">
@@ -2238,46 +2238,46 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01390387779923792</v>
+        <v>0.01390387779923791</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01574979104232418</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.0107715223609843</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364828103827</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01628649707723069</v>
+        <v>0.01628649707723067</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="N9" t="n">
         <v>0.03004073653105688</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01709892907647567</v>
+        <v>0.01709892907647569</v>
       </c>
       <c r="P9" t="n">
         <v>0.01727188900476265</v>
@@ -2286,37 +2286,37 @@
         <v>0.01630364828103827</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01618785308400087</v>
+        <v>0.01895713628327185</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01485680007642998</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0163036471695814</v>
+        <v>0.01630364716958141</v>
       </c>
     </row>
     <row r="10">
@@ -2326,82 +2326,82 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.009410908092708361</v>
+        <v>0.009410908092708366</v>
       </c>
       <c r="C10" t="n">
-        <v>0.009345787191563803</v>
+        <v>0.009345787191563789</v>
       </c>
       <c r="D10" t="n">
-        <v>0.009252662867773723</v>
+        <v>0.00925266286777373</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02086678026485354</v>
+        <v>0.02086678026485353</v>
       </c>
       <c r="F10" t="n">
-        <v>0.009168527683240137</v>
+        <v>0.009168527683240143</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008870426833517943</v>
+        <v>0.008870426833517948</v>
       </c>
       <c r="H10" t="n">
-        <v>0.009204016144624582</v>
+        <v>0.009204016144624589</v>
       </c>
       <c r="I10" t="n">
-        <v>0.009177696679327751</v>
+        <v>0.009177696679327756</v>
       </c>
       <c r="J10" t="n">
-        <v>0.008862610251362495</v>
+        <v>0.008862610251362492</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008948563847818189</v>
+        <v>0.00894856384781819</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008842153967664718</v>
+        <v>0.008842153967664723</v>
       </c>
       <c r="M10" t="n">
-        <v>0.009185506229457853</v>
+        <v>0.009185506229457848</v>
       </c>
       <c r="N10" t="n">
         <v>0.009138996886501445</v>
       </c>
       <c r="O10" t="n">
-        <v>0.009055045690608601</v>
+        <v>0.009055045690608603</v>
       </c>
       <c r="P10" t="n">
-        <v>0.009038383959276287</v>
+        <v>0.009038383959276293</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.009275255193501246</v>
+        <v>0.009275255193501258</v>
       </c>
       <c r="R10" t="n">
-        <v>0.008776803045706605</v>
+        <v>0.00877680304570661</v>
       </c>
       <c r="S10" t="n">
         <v>0.00894620876583133</v>
       </c>
       <c r="T10" t="n">
-        <v>0.009178294761893732</v>
+        <v>0.00917829476189373</v>
       </c>
       <c r="U10" t="n">
-        <v>0.008625399247212583</v>
+        <v>0.008625399247212579</v>
       </c>
       <c r="V10" t="n">
-        <v>0.004410814980685218</v>
+        <v>0.004410814980685212</v>
       </c>
       <c r="W10" t="n">
-        <v>0.008778039569600094</v>
+        <v>0.008778039569600098</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.001210724114858344</v>
+        <v>-0.001210724114858346</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.003195324771479861</v>
+        <v>0.003195324771479865</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.008979702847642978</v>
+        <v>0.008979702847642983</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.008131638624531983</v>
+        <v>0.008131638624531987</v>
       </c>
       <c r="AB10" t="n">
         <v>0.009234207697310733</v>
@@ -2417,82 +2417,82 @@
         <v>0.009377802038978903</v>
       </c>
       <c r="C11" t="n">
-        <v>0.009370146511548921</v>
+        <v>0.009370146511548919</v>
       </c>
       <c r="D11" t="n">
-        <v>0.009333268988606433</v>
+        <v>0.009333268988606432</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02076002847414949</v>
+        <v>0.0207600284741495</v>
       </c>
       <c r="F11" t="n">
         <v>0.009316468390899934</v>
       </c>
       <c r="G11" t="n">
-        <v>0.009146422815448852</v>
+        <v>0.009146422815448854</v>
       </c>
       <c r="H11" t="n">
-        <v>0.009319879836401458</v>
+        <v>0.009319879836401455</v>
       </c>
       <c r="I11" t="n">
-        <v>0.009312087249824247</v>
+        <v>0.009312087249824234</v>
       </c>
       <c r="J11" t="n">
-        <v>0.009219111913170522</v>
+        <v>0.009219111913170519</v>
       </c>
       <c r="K11" t="n">
-        <v>0.009250192143731913</v>
+        <v>0.009250192143731907</v>
       </c>
       <c r="L11" t="n">
-        <v>0.009215406020798324</v>
+        <v>0.00921540602079832</v>
       </c>
       <c r="M11" t="n">
-        <v>0.009314436192611651</v>
+        <v>0.009314436192611643</v>
       </c>
       <c r="N11" t="n">
         <v>0.009300636246879733</v>
       </c>
       <c r="O11" t="n">
-        <v>0.009275603952745954</v>
+        <v>0.009275603952745955</v>
       </c>
       <c r="P11" t="n">
-        <v>0.009266869603896234</v>
+        <v>0.009266869603896227</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.009339557389377725</v>
+        <v>0.00933955738937773</v>
       </c>
       <c r="R11" t="n">
         <v>0.009178369105532474</v>
       </c>
       <c r="S11" t="n">
-        <v>0.009244805593595027</v>
+        <v>0.009244805593595024</v>
       </c>
       <c r="T11" t="n">
         <v>0.009312171392194995</v>
       </c>
       <c r="U11" t="n">
-        <v>0.009148170164720974</v>
+        <v>0.009148170164720975</v>
       </c>
       <c r="V11" t="n">
-        <v>0.00476765327556622</v>
+        <v>0.004767653275566216</v>
       </c>
       <c r="W11" t="n">
-        <v>0.009197306401058016</v>
+        <v>0.009197306401058009</v>
       </c>
       <c r="X11" t="n">
-        <v>0.006328084587876081</v>
+        <v>0.00632808458787608</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.007604810206371207</v>
+        <v>0.007604810206371209</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.009254931429916615</v>
+        <v>0.009254931429916621</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.009012915051032357</v>
+        <v>0.009012915051032354</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.009251285767815339</v>
+        <v>0.00925128576781533</v>
       </c>
     </row>
   </sheetData>
@@ -2661,13 +2661,13 @@
         <v>0.01145500769029916</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01083125172043224</v>
+        <v>0.01083125172043223</v>
       </c>
       <c r="D2" t="n">
         <v>0.01142769804794527</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02177799102787242</v>
+        <v>0.02177799102787247</v>
       </c>
       <c r="F2" t="n">
         <v>0.01103583021310129</v>
@@ -2691,7 +2691,7 @@
         <v>0.01145500769029916</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01127258440329547</v>
+        <v>0.01127258440329548</v>
       </c>
       <c r="N2" t="n">
         <v>0.01119881833664558</v>
@@ -2718,7 +2718,7 @@
         <v>0.01145574506413324</v>
       </c>
       <c r="V2" t="n">
-        <v>0.006374590983098294</v>
+        <v>0.006374590983098292</v>
       </c>
       <c r="W2" t="n">
         <v>0.01145500769029916</v>
@@ -2730,7 +2730,7 @@
         <v>0.01145500769029916</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01117984165478384</v>
+        <v>0.01117984165478385</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01145500769029916</v>
@@ -2755,13 +2755,13 @@
         <v>0.01081781698218405</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02188582029713989</v>
+        <v>0.0218858202971399</v>
       </c>
       <c r="F3" t="n">
         <v>0.01082355069064332</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0107567482352392</v>
+        <v>0.01075674823523919</v>
       </c>
       <c r="H3" t="n">
         <v>0.01081781698218405</v>
@@ -2788,7 +2788,7 @@
         <v>0.01081781698218405</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01081777445023007</v>
+        <v>0.01081777445023006</v>
       </c>
       <c r="Q3" t="n">
         <v>0.01081781698218405</v>
@@ -2806,7 +2806,7 @@
         <v>0.01081862389310598</v>
       </c>
       <c r="V3" t="n">
-        <v>0.006246418589408375</v>
+        <v>0.006246418589408376</v>
       </c>
       <c r="W3" t="n">
         <v>0.01081781698218405</v>
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2208379563083962</v>
+        <v>0.2208379563083958</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05752302898728494</v>
+        <v>0.05752302898728491</v>
       </c>
       <c r="D4" t="n">
-        <v>0.232582292278017</v>
+        <v>0.2325822922780166</v>
       </c>
       <c r="E4" t="n">
         <v>0.07039113760755578</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1196814674461344</v>
+        <v>0.1196814674461346</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3231764485480549</v>
+        <v>0.3231764485480546</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06556429376861657</v>
+        <v>0.06556429376861671</v>
       </c>
       <c r="I4" t="n">
-        <v>0.142436642557712</v>
+        <v>0.1424366425577121</v>
       </c>
       <c r="J4" t="n">
         <v>0.2223974651024173</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2889955960679051</v>
+        <v>0.2889955960679053</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3435289358520943</v>
+        <v>0.3435289358520947</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1894848404338885</v>
+        <v>0.1894848404338888</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3872510157951978</v>
+        <v>0.3872510157951974</v>
       </c>
       <c r="O4" t="n">
         <v>0.2093200725293519</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2953741215841524</v>
+        <v>0.2953741215841525</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1078810074251148</v>
+        <v>0.1078810074251149</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07479209906984494</v>
+        <v>0.07479209906984499</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2643303143537293</v>
+        <v>0.2643303143537303</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2054681062978037</v>
+        <v>0.2054681062978033</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3872510157951978</v>
+        <v>0.3872510157951973</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06777946154909478</v>
+        <v>0.06777946154909466</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2453033428774959</v>
+        <v>0.2453033428774958</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2733686595486057</v>
+        <v>0.2733686595486059</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2500160284586513</v>
+        <v>0.2500160284586515</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1474332562778021</v>
+        <v>0.1474332562778019</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2284064544563081</v>
+        <v>0.2284064544563085</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2663456446998841</v>
+        <v>0.2663456446998838</v>
       </c>
     </row>
     <row r="5">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008471983130546956</v>
+        <v>0.008471983130546954</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008471983130546956</v>
+        <v>0.008471983130546954</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="J5" t="n">
         <v>0.008446483530045536</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="N5" t="n">
-        <v>0.008471983130546956</v>
+        <v>0.008471983130546954</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008471983130546956</v>
+        <v>0.008471983130546954</v>
       </c>
       <c r="P5" t="n">
-        <v>0.008471983130546956</v>
+        <v>0.008471983130546954</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008471983130546956</v>
+        <v>0.008471983130546954</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="S5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="T5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="U5" t="n">
-        <v>0.008295537860478373</v>
+        <v>0.008295537860478363</v>
       </c>
       <c r="V5" t="n">
-        <v>0.008302450945448521</v>
+        <v>0.008302450945448504</v>
       </c>
       <c r="W5" t="n">
         <v>0.008471983130546956</v>
       </c>
       <c r="X5" t="n">
-        <v>0.008471983130546956</v>
+        <v>0.008471983130546954</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.008295537860478373</v>
+        <v>0.008295537860478363</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.008471983130546952</v>
+        <v>0.008471983130546958</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.008471983130546956</v>
+        <v>0.008471983130546954</v>
       </c>
     </row>
     <row r="6">
@@ -3010,85 +3010,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01633324851132351</v>
+        <v>0.01092854566612675</v>
       </c>
       <c r="C6" t="n">
         <v>0.01633324851132351</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01092854566612676</v>
+        <v>0.01633324851132351</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01092854566612676</v>
+        <v>0.01092854566612675</v>
       </c>
       <c r="F6" t="n">
+        <v>0.01092854566612675</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01092854566612675</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.01633324851132351</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
+        <v>0.01092854566612675</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.01630774891082206</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.01633324851132351</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.01092854566612676</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.01092854566612676</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.01630774891082207</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.01092854566612676</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01092854566612676</v>
+        <v>0.01092854566612675</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01092854566612676</v>
+        <v>0.01092854566612675</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01095990793434612</v>
+        <v>0.01095990793434615</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01635065077764154</v>
+        <v>0.01635065077764157</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01635060928303288</v>
+        <v>0.01635060928303292</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01092854566612676</v>
+        <v>0.01633324851132351</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01092854566612676</v>
+        <v>0.01633324851132351</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01092854566612676</v>
+        <v>0.01633324851132351</v>
       </c>
       <c r="T6" t="n">
+        <v>0.01092854566612675</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.01092854566612675</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.01616371632622505</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.01635061001976192</v>
+      </c>
+      <c r="X6" t="n">
         <v>0.01633324851132351</v>
       </c>
-      <c r="U6" t="n">
+      <c r="Y6" t="n">
+        <v>0.0110924977075073</v>
+      </c>
+      <c r="Z6" t="n">
         <v>0.01633324851132351</v>
       </c>
-      <c r="V6" t="n">
-        <v>0.01616371632622507</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.0163506100197619</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.01092854566612676</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.01109249770750728</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.01092854566612676</v>
-      </c>
       <c r="AA6" t="n">
-        <v>0.01633324851132351</v>
+        <v>0.01092854566612675</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01098374257603265</v>
+        <v>0.01098374257603266</v>
       </c>
     </row>
     <row r="7">
@@ -3098,85 +3098,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01249950732214581</v>
+        <v>0.01249950732214582</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01252486150238836</v>
+        <v>0.01252486150238835</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01252486150238836</v>
+        <v>0.01252486150238835</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01251943003230121</v>
+        <v>0.01251943003230122</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0123554747375488</v>
+        <v>0.01235547473754879</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01252500692264723</v>
+        <v>0.01252500692264722</v>
       </c>
     </row>
     <row r="8">
@@ -3186,85 +3186,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02070312512741333</v>
+        <v>0.02070312512741334</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.02930194614073035</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.02930194614073035</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.02472332760060516</v>
       </c>
       <c r="F8" t="n">
         <v>0.02204272094468291</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.03108496769390677</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.02930194614073035</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.02930194614073035</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02927644654022889</v>
+        <v>0.0292764465402289</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.02930194614073035</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.02930194614073035</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.02930194614072924</v>
       </c>
       <c r="N8" t="n">
         <v>0.02263642130385292</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02446816540453453</v>
+        <v>0.02446816540453451</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02401916066434312</v>
+        <v>0.02401916066434313</v>
       </c>
       <c r="Q8" t="n">
         <v>0.01901326053994293</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.02930194614073035</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.02930194614073035</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.02930194614073035</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02400672698195749</v>
+        <v>0.02510076711499933</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02913241395563186</v>
+        <v>0.0267775838316824</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02930363605489678</v>
+        <v>0.02930363605489676</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01980135957159194</v>
+        <v>0.01980135957159195</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03784435733996752</v>
+        <v>0.0378443573399675</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.02054339761250245</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02930194614073033</v>
+        <v>0.02930194614073035</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03828413371033645</v>
+        <v>0.03828413371033643</v>
       </c>
     </row>
     <row r="9">
@@ -3274,85 +3274,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02389288062465217</v>
+        <v>0.02389288062465219</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02745030373368261</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.01785624067774467</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851769113527606</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02849218759479227</v>
+        <v>0.02849218759479226</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="O9" t="n">
         <v>0.03005034728282437</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03038367369896509</v>
+        <v>0.03038367369896513</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02851769113527605</v>
+        <v>0.02851769113527606</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02834815501019524</v>
+        <v>0.03368508418723264</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02572934165156652</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02851768719529365</v>
+        <v>0.02851768719529368</v>
       </c>
     </row>
     <row r="10">
@@ -3362,85 +3362,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.005892185324271717</v>
+        <v>0.005892185324271715</v>
       </c>
       <c r="C10" t="n">
         <v>0.009908609609066204</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006315146781843484</v>
+        <v>0.006315146781843477</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02053410679495846</v>
+        <v>0.02053410679495849</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008657625855803333</v>
+        <v>0.00865762585580333</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003589720559569434</v>
+        <v>0.003589720559569426</v>
       </c>
       <c r="H10" t="n">
-        <v>0.009802578298456148</v>
+        <v>0.009802578298456141</v>
       </c>
       <c r="I10" t="n">
-        <v>0.008204004810500039</v>
+        <v>0.008204004810500036</v>
       </c>
       <c r="J10" t="n">
-        <v>0.006066473651791453</v>
+        <v>0.006066473651791447</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004691311157432316</v>
+        <v>0.004691311157432312</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00359697428916309</v>
+        <v>0.003596974289163087</v>
       </c>
       <c r="M10" t="n">
-        <v>0.007237410645758195</v>
+        <v>0.007237410645758181</v>
       </c>
       <c r="N10" t="n">
-        <v>0.007642393672090809</v>
+        <v>0.007642393672090803</v>
       </c>
       <c r="O10" t="n">
-        <v>0.006038452933493698</v>
+        <v>0.006038452933493687</v>
       </c>
       <c r="P10" t="n">
-        <v>0.004258037219147474</v>
+        <v>0.004258037219147456</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.008824617557551888</v>
+        <v>0.008824617557551881</v>
       </c>
       <c r="R10" t="n">
-        <v>0.009597372189053379</v>
+        <v>0.009597372189053375</v>
       </c>
       <c r="S10" t="n">
-        <v>0.005033907581827058</v>
+        <v>0.00503390758182704</v>
       </c>
       <c r="T10" t="n">
-        <v>0.006868916593763665</v>
+        <v>0.006868916593763666</v>
       </c>
       <c r="U10" t="n">
-        <v>0.002448663936152621</v>
+        <v>0.00244866393615262</v>
       </c>
       <c r="V10" t="n">
-        <v>0.004955978112782909</v>
+        <v>0.004955978112782918</v>
       </c>
       <c r="W10" t="n">
-        <v>0.00579324315893257</v>
+        <v>0.005793243158932564</v>
       </c>
       <c r="X10" t="n">
-        <v>0.005361354639214118</v>
+        <v>0.005361354639214112</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.005640143555803232</v>
+        <v>0.005640143555803233</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.007727072231384953</v>
+        <v>0.007727072231384954</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.006155064807375538</v>
+        <v>0.00615506480737554</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.005747553553063425</v>
+        <v>0.005747553553063428</v>
       </c>
     </row>
     <row r="11">
@@ -3450,70 +3450,70 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.00921382958889232</v>
+        <v>0.009213829588892313</v>
       </c>
       <c r="C11" t="n">
         <v>0.01041033681434324</v>
       </c>
       <c r="D11" t="n">
-        <v>0.009378968757631787</v>
+        <v>0.009378968757631783</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02116295707672458</v>
+        <v>0.02116295707672459</v>
       </c>
       <c r="F11" t="n">
         <v>0.0100503275108562</v>
       </c>
       <c r="G11" t="n">
-        <v>0.008547526173204327</v>
+        <v>0.008547526173204307</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01099307085382924</v>
+        <v>0.01099307085382925</v>
       </c>
       <c r="I11" t="n">
         <v>0.01026571482245777</v>
       </c>
       <c r="J11" t="n">
-        <v>0.009274161788497099</v>
+        <v>0.009274161788497095</v>
       </c>
       <c r="K11" t="n">
         <v>0.008668842057055523</v>
       </c>
       <c r="L11" t="n">
-        <v>0.008169501253514332</v>
+        <v>0.008169501253514323</v>
       </c>
       <c r="M11" t="n">
         <v>0.009643488110143723</v>
       </c>
       <c r="N11" t="n">
-        <v>0.009753990611079486</v>
+        <v>0.009753990611079478</v>
       </c>
       <c r="O11" t="n">
-        <v>0.009280381817215539</v>
+        <v>0.009280381817215537</v>
       </c>
       <c r="P11" t="n">
-        <v>0.008470267476040823</v>
+        <v>0.008470267476040814</v>
       </c>
       <c r="Q11" t="n">
         <v>0.01054809560014184</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01089996644645454</v>
+        <v>0.01089996644645453</v>
       </c>
       <c r="S11" t="n">
-        <v>0.008823310480911128</v>
+        <v>0.008823310480911126</v>
       </c>
       <c r="T11" t="n">
-        <v>0.009658245429169035</v>
+        <v>0.009658245429169036</v>
       </c>
       <c r="U11" t="n">
-        <v>0.007647386610239719</v>
+        <v>0.00764738661023972</v>
       </c>
       <c r="V11" t="n">
-        <v>0.005787436453843905</v>
+        <v>0.005787436453843908</v>
       </c>
       <c r="W11" t="n">
-        <v>0.009168810588353036</v>
+        <v>0.009168810588353025</v>
       </c>
       <c r="X11" t="n">
         <v>0.008968456288920778</v>
@@ -3522,13 +3522,13 @@
         <v>0.009099149781029693</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.009773220604440299</v>
+        <v>0.009773220604440302</v>
       </c>
       <c r="AA11" t="n">
         <v>0.00933344059145177</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.009092088755914137</v>
+        <v>0.009092088755914133</v>
       </c>
     </row>
   </sheetData>
@@ -3700,7 +3700,7 @@
         <v>0.01145184035412129</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01222805766607464</v>
+        <v>0.01222805766607465</v>
       </c>
       <c r="E2" t="n">
         <v>0.0225220968902012</v>
@@ -3718,25 +3718,25 @@
         <v>0.01206478772776503</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01203383259832114</v>
+        <v>0.01203383259832113</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01206878242296028</v>
+        <v>0.01206878242296029</v>
       </c>
       <c r="L2" t="n">
         <v>0.01206478772776503</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01179413359263323</v>
+        <v>0.01179413359263324</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01170099327752007</v>
+        <v>0.01170099327752008</v>
       </c>
       <c r="O2" t="n">
         <v>0.01206478772776503</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01206476911988623</v>
+        <v>0.01206476911988624</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01206478772776503</v>
@@ -3751,16 +3751,16 @@
         <v>0.01206478772776503</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01205820381155084</v>
+        <v>0.01205820381155085</v>
       </c>
       <c r="V2" t="n">
-        <v>0.006991071951732548</v>
+        <v>0.006991071951732553</v>
       </c>
       <c r="W2" t="n">
         <v>0.01206478772776503</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01197341124500966</v>
+        <v>0.01197341124500967</v>
       </c>
       <c r="Y2" t="n">
         <v>0.01206478772776503</v>
@@ -3772,7 +3772,7 @@
         <v>0.01206478772776503</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01195338743745041</v>
+        <v>0.01195338743745042</v>
       </c>
     </row>
     <row r="3">
@@ -3785,13 +3785,13 @@
         <v>0.01147156511720422</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0114882359626352</v>
+        <v>0.01148823596263521</v>
       </c>
       <c r="D3" t="n">
         <v>0.01147156511720422</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02246431946542939</v>
+        <v>0.02246431946542941</v>
       </c>
       <c r="F3" t="n">
         <v>0.0114796572382968</v>
@@ -3824,13 +3824,13 @@
         <v>0.01147156511720422</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01147154475552867</v>
+        <v>0.01147154475552868</v>
       </c>
       <c r="Q3" t="n">
         <v>0.01147156511720422</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01145496577406482</v>
+        <v>0.01145496577406483</v>
       </c>
       <c r="S3" t="n">
         <v>0.01147156511720422</v>
@@ -3842,7 +3842,7 @@
         <v>0.0114643603319215</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00680362973506299</v>
+        <v>0.006803629735062997</v>
       </c>
       <c r="W3" t="n">
         <v>0.01147156511720422</v>
@@ -3854,7 +3854,7 @@
         <v>0.01147156511720422</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01147275631953786</v>
+        <v>0.01147275631953787</v>
       </c>
       <c r="AA3" t="n">
         <v>0.01147156511720422</v>
@@ -3873,79 +3873,79 @@
         <v>0.172713175835512</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04585277867737419</v>
+        <v>0.04585277867737424</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2545805355190522</v>
+        <v>0.2545805355190531</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1084749739671827</v>
+        <v>0.1084749739671829</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1298805047803034</v>
+        <v>0.1298805047803032</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2811162847741177</v>
+        <v>0.2811162847741178</v>
       </c>
       <c r="H4" t="n">
         <v>0.03296097449101743</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1919849180706315</v>
+        <v>0.1919849180706314</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1958460864577863</v>
+        <v>0.1958460864577865</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2311789023665709</v>
+        <v>0.231178902366571</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2666474703933147</v>
+        <v>0.2666474703933149</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1429111057535261</v>
+        <v>0.1429111057535262</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3270270144652752</v>
+        <v>0.3270270144652764</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1652137382637515</v>
+        <v>0.1652137382637519</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2696019888855143</v>
+        <v>0.2696019888855159</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08972221333850372</v>
+        <v>0.0897222133385039</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04400212883646768</v>
+        <v>0.0440021288364677</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2199023930318186</v>
+        <v>0.2199023930318189</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1815784107966713</v>
+        <v>0.1815784107966718</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3270270144652752</v>
+        <v>0.3270270144652764</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07666221360931319</v>
+        <v>0.07666221360931341</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1641169381813842</v>
+        <v>0.1641169381813837</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5681352532138815</v>
+        <v>0.5681352532138824</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4853545282739657</v>
+        <v>0.485354528273966</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.131773424314216</v>
+        <v>0.1317734243142158</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2291931142980898</v>
+        <v>0.2291931142980902</v>
       </c>
       <c r="AB4" t="n">
         <v>0.1875422428537266</v>
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251978</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008779797192777231</v>
+        <v>0.008779797192777229</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="N5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251978</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251978</v>
       </c>
       <c r="P5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251978</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251978</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="S5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="T5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="U5" t="n">
         <v>0.00865391090229769</v>
       </c>
       <c r="V5" t="n">
-        <v>0.008644713752312122</v>
+        <v>0.008644713752312112</v>
       </c>
       <c r="W5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251979</v>
       </c>
       <c r="X5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251978</v>
       </c>
       <c r="Y5" t="n">
         <v>0.00865391090229769</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251976</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.008803676300251983</v>
+        <v>0.008803676300251978</v>
       </c>
     </row>
     <row r="6">
@@ -4046,55 +4046,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01829866046236696</v>
+        <v>0.01280018598931178</v>
       </c>
       <c r="C6" t="n">
         <v>0.01280018598931178</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01829866046236696</v>
+        <v>0.01829866046236697</v>
       </c>
       <c r="E6" t="n">
         <v>0.01280018598931178</v>
       </c>
       <c r="F6" t="n">
+        <v>0.01829866046236697</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.01280018598931178</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.01829866046236696</v>
       </c>
       <c r="H6" t="n">
         <v>0.01280018598931178</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01829866046236696</v>
+        <v>0.01280018598931178</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01827478135489222</v>
+        <v>0.01827478135489223</v>
       </c>
       <c r="K6" t="n">
+        <v>0.01829866046236697</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.01280018598931178</v>
       </c>
-      <c r="L6" t="n">
-        <v>0.01829866046236696</v>
-      </c>
       <c r="M6" t="n">
-        <v>0.01829866046236696</v>
+        <v>0.01829866046236697</v>
       </c>
       <c r="N6" t="n">
+        <v>0.01281948946303907</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.01281948946303908</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.01832740307706124</v>
-      </c>
       <c r="P6" t="n">
-        <v>0.01832725767569402</v>
+        <v>0.01832725767569404</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01829866046236696</v>
+        <v>0.01829866046236697</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01829866046236696</v>
+        <v>0.01829866046236697</v>
       </c>
       <c r="S6" t="n">
         <v>0.01280018598931178</v>
@@ -4103,13 +4103,13 @@
         <v>0.01280018598931178</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01829866046236696</v>
+        <v>0.01280018598931178</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01813969791442711</v>
+        <v>0.01813969791442712</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01832738393808174</v>
+        <v>0.01309861508317106</v>
       </c>
       <c r="X6" t="n">
         <v>0.01280018598931178</v>
@@ -4118,10 +4118,10 @@
         <v>0.01303719509349709</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01829866046236696</v>
+        <v>0.01280018598931178</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01280018598931178</v>
+        <v>0.01829866046236697</v>
       </c>
       <c r="AB6" t="n">
         <v>0.01281930135098405</v>
@@ -4191,10 +4191,10 @@
         <v>0.01225053982513799</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01224274939324475</v>
+        <v>0.01224274939324474</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01209157727719813</v>
+        <v>0.01209157727719812</v>
       </c>
       <c r="W7" t="n">
         <v>0.01225053982513799</v>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02019406716227942</v>
+        <v>0.02019406716227943</v>
       </c>
       <c r="C8" t="n">
         <v>0.02844930794870626</v>
@@ -4231,13 +4231,13 @@
         <v>0.02844930794870626</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02844930794870626</v>
+        <v>0.02405363574443139</v>
       </c>
       <c r="F8" t="n">
         <v>0.02148013719569258</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02844930794870626</v>
+        <v>0.03016108590361479</v>
       </c>
       <c r="H8" t="n">
         <v>0.02844930794870626</v>
@@ -4246,7 +4246,7 @@
         <v>0.02844930794870626</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02842542884123148</v>
+        <v>0.02842542884123151</v>
       </c>
       <c r="K8" t="n">
         <v>0.02844930794870626</v>
@@ -4255,19 +4255,19 @@
         <v>0.02844930794870626</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02844930794870626</v>
+        <v>0.02844930794870541</v>
       </c>
       <c r="N8" t="n">
         <v>0.02205011526736265</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0238086689791359</v>
+        <v>0.02380866897913591</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02337760497179745</v>
+        <v>0.02337760497179748</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01857172393124515</v>
+        <v>0.01857172393124514</v>
       </c>
       <c r="R8" t="n">
         <v>0.02844930794870626</v>
@@ -4279,22 +4279,22 @@
         <v>0.02844930794870626</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02336389471175218</v>
+        <v>0.02441410541443026</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0282903454007664</v>
+        <v>0.02602752334771704</v>
       </c>
       <c r="W8" t="n">
         <v>0.02845093033942567</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01932833315234442</v>
+        <v>0.01932833315234443</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03664716199093665</v>
+        <v>0.03664716199093666</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02844930794870626</v>
+        <v>0.02004072182647974</v>
       </c>
       <c r="AA8" t="n">
         <v>0.02844930794870626</v>
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0220869555462207</v>
+        <v>0.02208695554622072</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02525346937311456</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.01671365490864979</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.0262035663568605</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0261796829158608</v>
+        <v>0.02617968291586081</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02756780578926491</v>
+        <v>0.02756780578926494</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02786450445940603</v>
+        <v>0.02786450445940604</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02620356635686049</v>
+        <v>0.0262035663568605</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0260445994753957</v>
+        <v>0.03079507782969471</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02372161610136081</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02620356202333554</v>
+        <v>0.02620356202333553</v>
       </c>
     </row>
     <row r="10">
@@ -4398,85 +4398,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.007473488101359871</v>
+        <v>0.007473488101359874</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01074436736294098</v>
+        <v>0.01074436736294099</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006092617490109031</v>
+        <v>0.006092617490109024</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0201229987595506</v>
+        <v>0.02012299875955057</v>
       </c>
       <c r="F10" t="n">
         <v>0.008882782364679145</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00463234097011843</v>
+        <v>0.004632340970118447</v>
       </c>
       <c r="H10" t="n">
         <v>0.01106412962558104</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00756169524995579</v>
+        <v>0.00756169524995578</v>
       </c>
       <c r="J10" t="n">
-        <v>0.006969614197221371</v>
+        <v>0.006969614197221357</v>
       </c>
       <c r="K10" t="n">
-        <v>0.006024009399988666</v>
+        <v>0.006024009399988658</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005487682635798422</v>
+        <v>0.005487682635798437</v>
       </c>
       <c r="M10" t="n">
-        <v>0.008645150134021458</v>
+        <v>0.008645150134021465</v>
       </c>
       <c r="N10" t="n">
-        <v>0.009170172520187687</v>
+        <v>0.009170172520187692</v>
       </c>
       <c r="O10" t="n">
-        <v>0.007453262187397393</v>
+        <v>0.007453262187397387</v>
       </c>
       <c r="P10" t="n">
-        <v>0.004983777499018595</v>
+        <v>0.004983777499018569</v>
       </c>
       <c r="Q10" t="n">
         <v>0.009702009858085394</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01079770011812744</v>
+        <v>0.01079770011812745</v>
       </c>
       <c r="S10" t="n">
-        <v>0.006309021601457382</v>
+        <v>0.006309021601457365</v>
       </c>
       <c r="T10" t="n">
-        <v>0.007761379310214667</v>
+        <v>0.007761379310214658</v>
       </c>
       <c r="U10" t="n">
-        <v>0.003826393946648625</v>
+        <v>0.00382639394664861</v>
       </c>
       <c r="V10" t="n">
-        <v>0.005153364735314051</v>
+        <v>0.005153364735314055</v>
       </c>
       <c r="W10" t="n">
-        <v>0.007960781010497634</v>
+        <v>0.007960781010497639</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.001191652444651338</v>
+        <v>-0.00119165244465137</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0003948694520717406</v>
+        <v>0.000394869452071729</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.008349598106679105</v>
+        <v>0.008349598106679108</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.00645369298259386</v>
+        <v>0.006453692982593856</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.007703277027453119</v>
+        <v>0.00770327702745312</v>
       </c>
     </row>
     <row r="11">
@@ -4486,82 +4486,82 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01024564994444038</v>
+        <v>0.01024564994444039</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01111337777069183</v>
+        <v>0.01111337777069184</v>
       </c>
       <c r="D11" t="n">
-        <v>0.009780619354057322</v>
+        <v>0.009780619354057328</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02145678850767994</v>
+        <v>0.02145678850767993</v>
       </c>
       <c r="F11" t="n">
         <v>0.01058109302403579</v>
       </c>
       <c r="G11" t="n">
-        <v>0.009302937640716458</v>
+        <v>0.00930293764071646</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0118794032806566</v>
+        <v>0.01187940328065661</v>
       </c>
       <c r="I11" t="n">
         <v>0.01028578447815104</v>
       </c>
       <c r="J11" t="n">
-        <v>0.009999516878161908</v>
+        <v>0.009999516878161909</v>
       </c>
       <c r="K11" t="n">
-        <v>0.009588138221997979</v>
+        <v>0.00958813822199798</v>
       </c>
       <c r="L11" t="n">
-        <v>0.009342102129223394</v>
+        <v>0.009342102129223401</v>
       </c>
       <c r="M11" t="n">
         <v>0.01050810576803497</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01065385231177451</v>
+        <v>0.01065385231177452</v>
       </c>
       <c r="O11" t="n">
         <v>0.01023644708913128</v>
       </c>
       <c r="P11" t="n">
-        <v>0.009112814342886636</v>
+        <v>0.009112814342886627</v>
       </c>
       <c r="Q11" t="n">
         <v>0.01125963444562794</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01175056089316119</v>
+        <v>0.0117505608931612</v>
       </c>
       <c r="S11" t="n">
-        <v>0.009715813976050185</v>
+        <v>0.009715813976050191</v>
       </c>
       <c r="T11" t="n">
         <v>0.01037664136192415</v>
       </c>
       <c r="U11" t="n">
-        <v>0.008582904765497047</v>
+        <v>0.00858290476549704</v>
       </c>
       <c r="V11" t="n">
         <v>0.006240196117764277</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01046736977100841</v>
+        <v>0.01046736977100843</v>
       </c>
       <c r="X11" t="n">
-        <v>0.006257104211060838</v>
+        <v>0.006257104211060834</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.007024855900795116</v>
+        <v>0.007024855900795107</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01041533220580452</v>
+        <v>0.01041533220580453</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.009781639915507628</v>
+        <v>0.009781639915507633</v>
       </c>
       <c r="AB11" t="n">
         <v>0.01029427172194236</v>
@@ -4739,7 +4739,7 @@
         <v>0.01094528389091697</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02167811494082109</v>
+        <v>0.02167811494082108</v>
       </c>
       <c r="F2" t="n">
         <v>0.01082912831742517</v>
@@ -4754,7 +4754,7 @@
         <v>0.01098787908698632</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01096903313914347</v>
+        <v>0.01096903313914348</v>
       </c>
       <c r="K2" t="n">
         <v>0.01099300011556876</v>
@@ -4763,16 +4763,16 @@
         <v>0.01098787908698632</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01071806672669311</v>
+        <v>0.0107180667266931</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0105534817702533</v>
+        <v>0.01055348177025329</v>
       </c>
       <c r="O2" t="n">
         <v>0.01098787908698632</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01098223533331225</v>
+        <v>0.01098223533331224</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01098787908698632</v>
@@ -4790,7 +4790,7 @@
         <v>0.01098043416022461</v>
       </c>
       <c r="V2" t="n">
-        <v>0.006273118300613037</v>
+        <v>0.006273118300613034</v>
       </c>
       <c r="W2" t="n">
         <v>0.01098787908698632</v>
@@ -4821,19 +4821,19 @@
         <v>0.01046833898532438</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01048494466029322</v>
+        <v>0.01048494466029321</v>
       </c>
       <c r="D3" t="n">
         <v>0.01046833898532438</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02173922857803622</v>
+        <v>0.0217392285780362</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01047907875874185</v>
+        <v>0.01047907875874184</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01034652979578907</v>
+        <v>0.01034652979578906</v>
       </c>
       <c r="H3" t="n">
         <v>0.01046833898532438</v>
@@ -4875,10 +4875,10 @@
         <v>0.01046833898532438</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01046019199656825</v>
+        <v>0.01046019199656824</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005918790003494011</v>
+        <v>0.005918790003494007</v>
       </c>
       <c r="W3" t="n">
         <v>0.01046833898532438</v>
@@ -4906,61 +4906,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1409191485336698</v>
+        <v>0.14091914853367</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04608082142485252</v>
+        <v>0.04608082142485257</v>
       </c>
       <c r="D4" t="n">
         <v>0.1724301326879963</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07409520598441856</v>
+        <v>0.07409520598441871</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1440908964422964</v>
+        <v>0.1440908964422963</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2386992237111272</v>
+        <v>0.2386992237111275</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03100047275528882</v>
+        <v>0.03100047275528891</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1869653130178781</v>
+        <v>0.1869653130178784</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1724491651553592</v>
+        <v>0.1724491651553595</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2689665701396269</v>
+        <v>0.2689665701396282</v>
       </c>
       <c r="L4" t="n">
-        <v>0.205849297789348</v>
+        <v>0.2058492977893483</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1172743522916755</v>
+        <v>0.1172743522916756</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3418670377981832</v>
+        <v>0.3418670377981828</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1069312270533022</v>
+        <v>0.1069312270533021</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2285100778795991</v>
+        <v>0.2285100778795996</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08920618481652444</v>
+        <v>0.08920618481652458</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06945034817998644</v>
+        <v>0.06945034817998663</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2030545624375945</v>
+        <v>0.2030545624375949</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1807758407164989</v>
+        <v>0.1807758407164991</v>
       </c>
       <c r="U4" t="n">
         <v>0.3418670377981829</v>
@@ -4969,22 +4969,22 @@
         <v>0.1113039455917263</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1122156598360185</v>
+        <v>0.1122156598360184</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6678736353618961</v>
+        <v>0.6678736353618996</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7129911723556697</v>
+        <v>0.7129911723556708</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1130101754735237</v>
+        <v>0.1130101754735238</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2436578969914449</v>
+        <v>0.2436578969914458</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.165971181000937</v>
+        <v>0.1659711810009371</v>
       </c>
     </row>
     <row r="5">
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00791780399908493</v>
+        <v>0.007917803999084932</v>
       </c>
       <c r="C5" t="n">
         <v>0.007917803999084932</v>
@@ -5006,7 +5006,7 @@
         <v>0.007917803999084932</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00791780399908493</v>
+        <v>0.007917803999084932</v>
       </c>
       <c r="G5" t="n">
         <v>0.007917803999084932</v>
@@ -5030,16 +5030,16 @@
         <v>0.007917803999084932</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00791780399908493</v>
+        <v>0.007917803999084932</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00791780399908493</v>
+        <v>0.007917803999084932</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00791780399908493</v>
+        <v>0.007917803999084932</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00791780399908493</v>
+        <v>0.007917803999084932</v>
       </c>
       <c r="R5" t="n">
         <v>0.007917803999084932</v>
@@ -5051,19 +5051,19 @@
         <v>0.007917803999084932</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007812122658714873</v>
+        <v>0.007812122658714875</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007781169591273187</v>
+        <v>0.007781169591273189</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00791780399908493</v>
+        <v>0.007917803999084932</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00791780399908493</v>
+        <v>0.007917803999084932</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.007812122658714873</v>
+        <v>0.007812122658714875</v>
       </c>
       <c r="Z5" t="n">
         <v>0.007917803999084932</v>
@@ -5072,7 +5072,7 @@
         <v>0.007917803999084932</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00791780399908493</v>
+        <v>0.007917803999084932</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009822762459568219</v>
+        <v>0.0145621858583562</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009822762459568219</v>
+        <v>0.009822762459568221</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009822762459568219</v>
+        <v>0.009822762459568221</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009822762459568219</v>
+        <v>0.0145621858583562</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009822762459568219</v>
+        <v>0.009822762459568221</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009822762459568219</v>
+        <v>0.0145621858583562</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01456218585835619</v>
+        <v>0.009822762459568221</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009822762459568219</v>
+        <v>0.009822762459568221</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009802337638071725</v>
+        <v>0.0145417610368597</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01456218585835619</v>
+        <v>0.0145621858583562</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009822762459568219</v>
+        <v>0.0145621858583562</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009822762459568219</v>
+        <v>0.009822762459568221</v>
       </c>
       <c r="N6" t="n">
-        <v>0.009863246607761953</v>
+        <v>0.009863246607761889</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009863246607761951</v>
+        <v>0.01458115226115348</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01458102472915484</v>
+        <v>0.0096924301336389</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01456218585835619</v>
+        <v>0.0145621858583562</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01456218585835619</v>
+        <v>0.0145621858583562</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01456218585835619</v>
+        <v>0.0145621858583562</v>
       </c>
       <c r="T6" t="n">
-        <v>0.009822762459568219</v>
+        <v>0.0145621858583562</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01456218585835619</v>
+        <v>0.009822762459568221</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01442555145054445</v>
+        <v>0.009686128051756481</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01458114747141313</v>
+        <v>0.01458114747141311</v>
       </c>
       <c r="X6" t="n">
-        <v>0.009822762459568219</v>
+        <v>0.009822762459568221</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009978473644859759</v>
+        <v>0.009978473644859747</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01456218585835619</v>
+        <v>0.0145621858583562</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01456218585835619</v>
+        <v>0.0145621858583562</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.009846283078435891</v>
+        <v>0.009846283078435885</v>
       </c>
     </row>
     <row r="7">
@@ -5194,7 +5194,7 @@
         <v>0.01157117278959281</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01155074796809631</v>
+        <v>0.0115507479680963</v>
       </c>
       <c r="K7" t="n">
         <v>0.01157117278959281</v>
@@ -5230,7 +5230,7 @@
         <v>0.01156269336165771</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01143453838178107</v>
+        <v>0.01143453838178106</v>
       </c>
       <c r="W7" t="n">
         <v>0.01157117278959281</v>
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01898058556043536</v>
+        <v>0.01898058556043535</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.02670345389028954</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.02670345389028954</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.02259125431509783</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02018371818711081</v>
+        <v>0.02018371818711079</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.02830484094825823</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.02670345389028954</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.02670345389028954</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02668302906879306</v>
+        <v>0.02668302906879304</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.02670345389028954</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.02670345389028954</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.02670345389028886</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02071693892681769</v>
+        <v>0.02071693892681766</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02236208521860196</v>
+        <v>0.02236208521860194</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02195882011019933</v>
+        <v>0.02195882011019931</v>
       </c>
       <c r="Q8" t="n">
         <v>0.01746286566787795</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.02670345389028954</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.02670345389028954</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.02670345389028954</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02194513082281499</v>
+        <v>0.0229275583685557</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02656681948247783</v>
+        <v>0.02444891068826057</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02670497165477086</v>
+        <v>0.02670497165477081</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01817068189561447</v>
+        <v>0.01817068189561446</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03437106367429024</v>
+        <v>0.03437106367429019</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.01883712931632497</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02670345389028957</v>
+        <v>0.02670345389028954</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03477063563615447</v>
+        <v>0.03477063563615444</v>
       </c>
     </row>
     <row r="9">
@@ -5346,43 +5346,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02017159932696531</v>
+        <v>0.02017159932696529</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02301056760063995</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.01535411522017905</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238614343614</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02384195791674643</v>
+        <v>0.0238419579167464</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="O9" t="n">
         <v>0.02508550806174195</v>
@@ -5391,40 +5391,40 @@
         <v>0.02535151609373535</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02386238614343616</v>
+        <v>0.02386238614343614</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02372574833043118</v>
+        <v>0.02798483564391859</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02163716989067333</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02386238273824296</v>
+        <v>0.02386238273824294</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.007152632063355138</v>
+        <v>0.007152632063355134</v>
       </c>
       <c r="C10" t="n">
-        <v>0.009718747779983355</v>
+        <v>0.009718747779983347</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006764108820063815</v>
+        <v>0.006764108820063806</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02011287357849443</v>
+        <v>0.02011287357849444</v>
       </c>
       <c r="F10" t="n">
-        <v>0.007527250168491107</v>
+        <v>0.007527250168491106</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004439280603241837</v>
+        <v>0.004439280603241823</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01009192758919282</v>
+        <v>0.01009192758919281</v>
       </c>
       <c r="I10" t="n">
-        <v>0.006589358402629616</v>
+        <v>0.006589358402629602</v>
       </c>
       <c r="J10" t="n">
-        <v>0.006456139779472757</v>
+        <v>0.006456139779472749</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004060364023055963</v>
+        <v>0.004060364023055945</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005726708614070105</v>
+        <v>0.005726708614070092</v>
       </c>
       <c r="M10" t="n">
-        <v>0.008104088008668015</v>
+        <v>0.008104088008668006</v>
       </c>
       <c r="N10" t="n">
-        <v>0.009053094801828872</v>
+        <v>0.009053094801828865</v>
       </c>
       <c r="O10" t="n">
-        <v>0.007993008935816432</v>
+        <v>0.007993008935816419</v>
       </c>
       <c r="P10" t="n">
-        <v>0.004804741441920321</v>
+        <v>0.004804741441920297</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.008656494637496973</v>
+        <v>0.008656494637496955</v>
       </c>
       <c r="R10" t="n">
-        <v>0.009221953630714843</v>
+        <v>0.009221953630714831</v>
       </c>
       <c r="S10" t="n">
-        <v>0.005648155914943031</v>
+        <v>0.005648155914943018</v>
       </c>
       <c r="T10" t="n">
-        <v>0.006769901369880384</v>
+        <v>0.006769901369880362</v>
       </c>
       <c r="U10" t="n">
-        <v>0.002143228947323997</v>
+        <v>0.002143228947323976</v>
       </c>
       <c r="V10" t="n">
-        <v>0.003307120544291309</v>
+        <v>0.003307120544291312</v>
       </c>
       <c r="W10" t="n">
-        <v>0.00815743763066416</v>
+        <v>0.008157437630664158</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.004909598936319446</v>
+        <v>-0.004909598936319492</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.005621426070859355</v>
+        <v>-0.005621426070859392</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.00768447884404241</v>
+        <v>0.007684478844042407</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.005134129334979215</v>
+        <v>0.005134129334979188</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.00709638478689999</v>
+        <v>0.007096384786899986</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.009479221870959295</v>
+        <v>0.00947922187095929</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0101101008949921</v>
+        <v>0.01011010089499209</v>
       </c>
       <c r="D11" t="n">
-        <v>0.009259847361042291</v>
+        <v>0.009259847361042284</v>
       </c>
       <c r="E11" t="n">
         <v>0.02093811823314375</v>
       </c>
       <c r="F11" t="n">
-        <v>0.009486036901941523</v>
+        <v>0.009486036901941525</v>
       </c>
       <c r="G11" t="n">
-        <v>0.008507244716316238</v>
+        <v>0.008507244716316229</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01081661070219451</v>
+        <v>0.0108166107021945</v>
       </c>
       <c r="I11" t="n">
-        <v>0.009222930560282547</v>
+        <v>0.00922293056028254</v>
       </c>
       <c r="J11" t="n">
-        <v>0.009152045661541928</v>
+        <v>0.009152045661541921</v>
       </c>
       <c r="K11" t="n">
-        <v>0.008074801281864262</v>
+        <v>0.008074801281864255</v>
       </c>
       <c r="L11" t="n">
-        <v>0.008830422157386183</v>
+        <v>0.008830422157386181</v>
       </c>
       <c r="M11" t="n">
-        <v>0.00964232499789363</v>
+        <v>0.009642324997893626</v>
       </c>
       <c r="N11" t="n">
-        <v>0.009909541156647229</v>
+        <v>0.009909541156647222</v>
       </c>
       <c r="O11" t="n">
-        <v>0.009861596026051368</v>
+        <v>0.009861596026051359</v>
       </c>
       <c r="P11" t="n">
-        <v>0.008408090485129558</v>
+        <v>0.008408090485129548</v>
       </c>
       <c r="Q11" t="n">
         <v>0.01016348413471949</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01040608829613271</v>
+        <v>0.0104060882961327</v>
       </c>
       <c r="S11" t="n">
-        <v>0.008794680428950773</v>
+        <v>0.008794680428950766</v>
       </c>
       <c r="T11" t="n">
-        <v>0.009305078185737921</v>
+        <v>0.009305078185737913</v>
       </c>
       <c r="U11" t="n">
-        <v>0.007196189468229847</v>
+        <v>0.007196189468229836</v>
       </c>
       <c r="V11" t="n">
-        <v>0.005084800373779073</v>
+        <v>0.00508480037377907</v>
       </c>
       <c r="W11" t="n">
-        <v>0.009936411606210248</v>
+        <v>0.009936411606210244</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003969835046523851</v>
+        <v>0.003969835046523835</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.00366698471138382</v>
+        <v>0.003666984711383806</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.009515399345095977</v>
+        <v>0.009515399345095973</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.008560796696961729</v>
+        <v>0.008560796696961722</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.009397696264758464</v>
+        <v>0.00939769626475846</v>
       </c>
     </row>
   </sheetData>
@@ -5775,7 +5775,7 @@
         <v>0.01033218359652395</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02132783949340143</v>
+        <v>0.02132783949340142</v>
       </c>
       <c r="F2" t="n">
         <v>0.01008985219794828</v>
@@ -5790,10 +5790,10 @@
         <v>0.01026682314283262</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01025483539664272</v>
+        <v>0.01025483539664273</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0102696394285741</v>
+        <v>0.01026963942857411</v>
       </c>
       <c r="L2" t="n">
         <v>0.01026682314283262</v>
@@ -5814,7 +5814,7 @@
         <v>0.01026682314283262</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01026735096758027</v>
+        <v>0.01026735096758028</v>
       </c>
       <c r="S2" t="n">
         <v>0.01026682314283262</v>
@@ -5826,7 +5826,7 @@
         <v>0.01026756051666669</v>
       </c>
       <c r="V2" t="n">
-        <v>0.005655519146458633</v>
+        <v>0.005655519146458621</v>
       </c>
       <c r="W2" t="n">
         <v>0.01026682314283262</v>
@@ -5838,13 +5838,13 @@
         <v>0.01026682314283262</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01020397329181585</v>
+        <v>0.01020397329181584</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01026682314283262</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.010155422852518</v>
+        <v>0.01015542285251801</v>
       </c>
     </row>
     <row r="3">
@@ -5854,28 +5854,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0101704596664341</v>
+        <v>0.01017045966643409</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02152983166699955</v>
+        <v>0.02152983166699954</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01016031952157157</v>
+        <v>0.01016031952157156</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01009351706616745</v>
+        <v>0.01009351706616744</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="J3" t="n">
         <v>0.01014259670035243</v>
@@ -5884,55 +5884,55 @@
         <v>0.01015766764802706</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="P3" t="n">
         <v>0.01015454328115831</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01015516338794838</v>
+        <v>0.01015516338794837</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="U3" t="n">
         <v>0.01015539272403423</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005650708068157292</v>
+        <v>0.005650708068157285</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01014620858740043</v>
+        <v>0.01014620858740042</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01015529424575672</v>
+        <v>0.01015529424575671</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0101545858131123</v>
+        <v>0.01015458581311229</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01003268035012187</v>
+        <v>0.01003268035012186</v>
       </c>
     </row>
     <row r="4">
@@ -5942,85 +5942,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04421545350753825</v>
+        <v>0.04421545350753824</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01855529990856977</v>
+        <v>0.01855529990856975</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1048584596554704</v>
+        <v>0.1048584596554705</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04318116876844185</v>
+        <v>0.04318116876844189</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03578383920482341</v>
+        <v>0.03578383920482346</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09186727057479725</v>
+        <v>0.09186727057479742</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05402471324290094</v>
+        <v>0.05402471324290092</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07083216539350524</v>
+        <v>0.07083216539350516</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07859189250457953</v>
+        <v>0.07859189250457956</v>
       </c>
       <c r="K4" t="n">
-        <v>0.123820210774966</v>
+        <v>0.1238202107749658</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1056016295393481</v>
+        <v>0.1056016295393482</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07260141794384227</v>
+        <v>0.07260141794384233</v>
       </c>
       <c r="N4" t="n">
         <v>0.15809459909721</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04456460871250177</v>
+        <v>0.04456460871250172</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09620475098911559</v>
+        <v>0.09620475098911556</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05632828620110981</v>
+        <v>0.0563282862011098</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05109151448395206</v>
+        <v>0.05109151448395201</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05885905491965904</v>
+        <v>0.05885905491965899</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05309169567216648</v>
+        <v>0.05309169567216647</v>
       </c>
       <c r="U4" t="n">
         <v>0.15809459909721</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03431668159590216</v>
+        <v>0.03431668159590206</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1121903715662427</v>
+        <v>0.1121903715662428</v>
       </c>
       <c r="X4" t="n">
         <v>0.1149933927224791</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06448856329121268</v>
+        <v>0.06448856329121233</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06109174039777616</v>
+        <v>0.06109174039777609</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1223225463036629</v>
+        <v>0.122322546303663</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5458752201923469</v>
+        <v>0.5458752201923467</v>
       </c>
     </row>
     <row r="5">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006800406831111851</v>
+        <v>0.006800406831111849</v>
       </c>
       <c r="C5" t="n">
         <v>0.00680040683111185</v>
@@ -6042,7 +6042,7 @@
         <v>0.00680040683111185</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006800406831111851</v>
+        <v>0.006800406831111849</v>
       </c>
       <c r="G5" t="n">
         <v>0.00680040683111185</v>
@@ -6066,16 +6066,16 @@
         <v>0.00680040683111185</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006800406831111851</v>
+        <v>0.006800406831111849</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006800406831111851</v>
+        <v>0.006800406831111849</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006800406831111851</v>
+        <v>0.006800406831111849</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.006800406831111851</v>
+        <v>0.006800406831111849</v>
       </c>
       <c r="R5" t="n">
         <v>0.00680040683111185</v>
@@ -6087,19 +6087,19 @@
         <v>0.00680040683111185</v>
       </c>
       <c r="U5" t="n">
-        <v>0.006727682074371817</v>
+        <v>0.00672768207437182</v>
       </c>
       <c r="V5" t="n">
-        <v>0.006660997065917199</v>
+        <v>0.006660997065917207</v>
       </c>
       <c r="W5" t="n">
-        <v>0.006800406831111851</v>
+        <v>0.006800406831111849</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006800406831111851</v>
+        <v>0.006800406831111849</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.006727682074371817</v>
+        <v>0.00672768207437182</v>
       </c>
       <c r="Z5" t="n">
         <v>0.00680040683111185</v>
@@ -6108,7 +6108,7 @@
         <v>0.00680040683111185</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.006800406831111851</v>
+        <v>0.006800406831111849</v>
       </c>
     </row>
     <row r="6">
@@ -6118,82 +6118,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008934690107395201</v>
+        <v>0.008934690107395176</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01356754323179954</v>
+        <v>0.01356754323179955</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01356754323179954</v>
+        <v>0.008934690107395176</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01356754323179954</v>
+        <v>0.008934690107395176</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01356754323179954</v>
+        <v>0.01356754323179955</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008934690107395201</v>
+        <v>0.01356754323179955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008934690107395201</v>
+        <v>0.008934690107395176</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01356754323179954</v>
+        <v>0.008934690107395176</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008913913343659666</v>
+        <v>0.008913913343659624</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01356754323179954</v>
+        <v>0.008934690107395176</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01356754323179954</v>
+        <v>0.008934690107395176</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008934690107395201</v>
+        <v>0.01356754323179955</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008941911903621808</v>
+        <v>0.008941911903621806</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0135804675128057</v>
+        <v>0.01358046751280573</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01358041270606523</v>
+        <v>0.008759657271101557</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01356754323179954</v>
+        <v>0.01356754323179955</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01356754323179954</v>
+        <v>0.008934690107395176</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01356754323179954</v>
+        <v>0.008934690107395176</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008934690107395201</v>
+        <v>0.01356754323179955</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01356754323179954</v>
+        <v>0.008934690107395176</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00879528034220055</v>
+        <v>0.01342813346660488</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009116242916921495</v>
+        <v>0.009116242916921379</v>
       </c>
       <c r="X6" t="n">
-        <v>0.008934690107395201</v>
+        <v>0.008934690107395176</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009071469193812718</v>
+        <v>0.009071469193812741</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008934690107395201</v>
+        <v>0.01356754323179955</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008934690107395201</v>
+        <v>0.01356754323179955</v>
       </c>
       <c r="AB6" t="n">
         <v>0.009089276724844848</v>
@@ -6230,7 +6230,7 @@
         <v>0.01022108535383666</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0102003085901011</v>
+        <v>0.01020030859010111</v>
       </c>
       <c r="K7" t="n">
         <v>0.01022108535383666</v>
@@ -6245,10 +6245,10 @@
         <v>0.01022108535383666</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01022095017273915</v>
+        <v>0.01022095017273916</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01022095017273915</v>
+        <v>0.01022095017273916</v>
       </c>
       <c r="Q7" t="n">
         <v>0.01022108535383666</v>
@@ -6294,85 +6294,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01786715050276232</v>
+        <v>0.01786715050276231</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.02556606877657202</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.02556606877657202</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.02146662189970414</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01906655199063082</v>
+        <v>0.0190665519906308</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.02716248963440827</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.02556606877657202</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.02556606877657202</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02554529201283647</v>
+        <v>0.02554529201283645</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.02556606877657202</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.02556606877657202</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.02556606877657061</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01959811911332773</v>
+        <v>0.01959811911332771</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0212381634994935</v>
+        <v>0.02123816349949349</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02083614899142946</v>
+        <v>0.02083614899142944</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01635413734280187</v>
+        <v>0.01635413734280185</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.02556606877657202</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.02556606877657202</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.02556606877657202</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02082417037514282</v>
+        <v>0.02180365962919517</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02542665901137737</v>
+        <v>0.02331727780484813</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02556758183433782</v>
+        <v>0.02556758183433777</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01705975850041142</v>
+        <v>0.01705975850041141</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03321293914735117</v>
+        <v>0.03321293914735114</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.01772413914322021</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02556606877657204</v>
+        <v>0.02556606877657202</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03360823268638202</v>
+        <v>0.03360823268638201</v>
       </c>
     </row>
     <row r="9">
@@ -6382,85 +6382,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01815405044565901</v>
+        <v>0.01815405044565902</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02079267058272494</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.0136765398330774</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437564719872</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="J9" t="n">
         <v>0.02156359762364985</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="O9" t="n">
         <v>0.02272118092736143</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02296841657150284</v>
+        <v>0.02296841657150283</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02158437564719871</v>
+        <v>0.02158437564719872</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02144496462219074</v>
+        <v>0.02540348450874346</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.01951619458708883</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02158437438738541</v>
+        <v>0.02158437438738543</v>
       </c>
     </row>
     <row r="10">
@@ -6470,85 +6470,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00938848113982335</v>
+        <v>0.009388481139823344</v>
       </c>
       <c r="C10" t="n">
         <v>0.01004626522565863</v>
       </c>
       <c r="D10" t="n">
-        <v>0.008218420789941137</v>
+        <v>0.008218420789941134</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02074175340893392</v>
+        <v>0.02074175340893393</v>
       </c>
       <c r="F10" t="n">
-        <v>0.009676734175712468</v>
+        <v>0.009676734175712465</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008078690607069039</v>
+        <v>0.008078690607069033</v>
       </c>
       <c r="H10" t="n">
-        <v>0.009331710599223208</v>
+        <v>0.009331710599223209</v>
       </c>
       <c r="I10" t="n">
-        <v>0.008950474853105067</v>
+        <v>0.008950474853105071</v>
       </c>
       <c r="J10" t="n">
-        <v>0.008572954785618075</v>
+        <v>0.008572954785618076</v>
       </c>
       <c r="K10" t="n">
-        <v>0.007601708459191399</v>
+        <v>0.00760170845919139</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007857396840900751</v>
+        <v>0.007857396840900747</v>
       </c>
       <c r="M10" t="n">
-        <v>0.008822415334317931</v>
+        <v>0.008822415334317924</v>
       </c>
       <c r="N10" t="n">
-        <v>0.008344336202429987</v>
+        <v>0.008344336202429989</v>
       </c>
       <c r="O10" t="n">
-        <v>0.009366405287447692</v>
+        <v>0.00936640528744769</v>
       </c>
       <c r="P10" t="n">
-        <v>0.008171753033392723</v>
+        <v>0.008171753033392721</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.00917895434715703</v>
+        <v>0.009178954347157028</v>
       </c>
       <c r="R10" t="n">
-        <v>0.009376061240658975</v>
+        <v>0.009376061240658979</v>
       </c>
       <c r="S10" t="n">
         <v>0.008943600487347455</v>
       </c>
       <c r="T10" t="n">
-        <v>0.009282612581625712</v>
+        <v>0.009282612581625709</v>
       </c>
       <c r="U10" t="n">
-        <v>0.006793247093828518</v>
+        <v>0.006793247093828515</v>
       </c>
       <c r="V10" t="n">
-        <v>0.005128028592490149</v>
+        <v>0.005128028592490143</v>
       </c>
       <c r="W10" t="n">
-        <v>0.007980083392285894</v>
+        <v>0.007980083392285892</v>
       </c>
       <c r="X10" t="n">
-        <v>0.007966083427261692</v>
+        <v>0.00796608342726169</v>
       </c>
       <c r="Y10" t="n">
         <v>0.009008485456944711</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.008956610045923573</v>
+        <v>0.008956610045923569</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.007757049532944744</v>
+        <v>0.007757049532944742</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.0008943067077360834</v>
+        <v>-0.0008943067077360903</v>
       </c>
     </row>
     <row r="11">
@@ -6561,82 +6561,82 @@
         <v>0.00991824307505541</v>
       </c>
       <c r="C11" t="n">
-        <v>0.009980813890213035</v>
+        <v>0.00998081389021304</v>
       </c>
       <c r="D11" t="n">
-        <v>0.009451222340789248</v>
+        <v>0.009451222340789244</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02096926137452516</v>
+        <v>0.02096926137452517</v>
       </c>
       <c r="F11" t="n">
-        <v>0.009869819324487336</v>
+        <v>0.00986981932448734</v>
       </c>
       <c r="G11" t="n">
-        <v>0.009367917082977207</v>
+        <v>0.009367917082977212</v>
       </c>
       <c r="H11" t="n">
-        <v>0.009892412298165374</v>
+        <v>0.009892412298165379</v>
       </c>
       <c r="I11" t="n">
-        <v>0.009718948818755391</v>
+        <v>0.009718948818755386</v>
       </c>
       <c r="J11" t="n">
-        <v>0.009540643323286618</v>
+        <v>0.009540643323286619</v>
       </c>
       <c r="K11" t="n">
-        <v>0.009106669852295241</v>
+        <v>0.009106669852295244</v>
       </c>
       <c r="L11" t="n">
-        <v>0.009221594839769491</v>
+        <v>0.00922159483976949</v>
       </c>
       <c r="M11" t="n">
-        <v>0.009623800858125045</v>
+        <v>0.009623800858125043</v>
       </c>
       <c r="N11" t="n">
-        <v>0.009485708414172556</v>
+        <v>0.009485708414172555</v>
       </c>
       <c r="O11" t="n">
-        <v>0.009908198491872928</v>
+        <v>0.009908198491872933</v>
       </c>
       <c r="P11" t="n">
-        <v>0.00936460839184813</v>
+        <v>0.009364608391848137</v>
       </c>
       <c r="Q11" t="n">
         <v>0.009822907716669969</v>
       </c>
       <c r="R11" t="n">
-        <v>0.00991285700771238</v>
+        <v>0.009912857007712382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.009715820960428369</v>
+        <v>0.009715820960428372</v>
       </c>
       <c r="T11" t="n">
-        <v>0.009870072543692394</v>
+        <v>0.009870072543692399</v>
       </c>
       <c r="U11" t="n">
-        <v>0.008737773540400715</v>
+        <v>0.008737773540400716</v>
       </c>
       <c r="V11" t="n">
-        <v>0.005417698319349426</v>
+        <v>0.005417698319349415</v>
       </c>
       <c r="W11" t="n">
-        <v>0.009277417611628569</v>
+        <v>0.009277417611628567</v>
       </c>
       <c r="X11" t="n">
-        <v>0.009267203936314</v>
+        <v>0.009267203936314002</v>
       </c>
       <c r="Y11" t="n">
         <v>0.009745343828371247</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.009658568160911861</v>
+        <v>0.009658568160911865</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.009175936494861611</v>
+        <v>0.009175936494861613</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.005183608918951022</v>
+        <v>0.00518360891895102</v>
       </c>
     </row>
   </sheetData>
@@ -6802,7 +6802,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01031287081599359</v>
+        <v>0.0103128708159936</v>
       </c>
       <c r="C2" t="n">
         <v>0.01028477524575652</v>
@@ -6817,70 +6817,70 @@
         <v>0.0103019735484565</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01022166755965759</v>
+        <v>0.0102216675596576</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01031287081599359</v>
+        <v>0.0103128708159936</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01031287081599359</v>
+        <v>0.0103128708159936</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01030944047583431</v>
+        <v>0.01030944047583432</v>
       </c>
       <c r="K2" t="n">
         <v>0.01031686551118885</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01031287081599359</v>
+        <v>0.0103128708159936</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01026566512996305</v>
+        <v>0.01026566512996304</v>
       </c>
       <c r="N2" t="n">
         <v>0.01030243304417949</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01031287081599359</v>
+        <v>0.0103128708159936</v>
       </c>
       <c r="P2" t="n">
         <v>0.0103128522081148</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01031287081599359</v>
+        <v>0.0103128708159936</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01029770194942264</v>
+        <v>0.01029770194942265</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01031287081599359</v>
+        <v>0.0103128708159936</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01031287081599359</v>
+        <v>0.0103128708159936</v>
       </c>
       <c r="U2" t="n">
         <v>0.01030628689977941</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00583003880455422</v>
+        <v>0.005830038804554221</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01031287081599359</v>
+        <v>0.0103128708159936</v>
       </c>
       <c r="X2" t="n">
         <v>0.01022149433323823</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01031287081599359</v>
+        <v>0.0103128708159936</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01033012894668094</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01031287081599359</v>
+        <v>0.0103128708159936</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01020147052567898</v>
+        <v>0.01020147052567899</v>
       </c>
     </row>
     <row r="3">
@@ -6890,85 +6890,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01037537222778999</v>
+        <v>0.01037537222779</v>
       </c>
       <c r="D3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0217094718214175</v>
+        <v>0.02170947182141751</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01036679350345158</v>
+        <v>0.01036679350345159</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01028665086921328</v>
+        <v>0.01028665086921329</v>
       </c>
       <c r="H3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="I3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01035527065653601</v>
+        <v>0.01035527065653603</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01036307275679518</v>
+        <v>0.01036307275679519</v>
       </c>
       <c r="L3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="M3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="N3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="O3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01035868102068346</v>
+        <v>0.01035868102068347</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0103421020392196</v>
+        <v>0.01034210203921961</v>
       </c>
       <c r="S3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="T3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01035149659707628</v>
+        <v>0.01035149659707629</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005811634102796548</v>
+        <v>0.005811634102796546</v>
       </c>
       <c r="W3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0102587079904571</v>
+        <v>0.01025870799045711</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01035989258469265</v>
+        <v>0.01035989258469266</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.010358701382359</v>
+        <v>0.01035870138235901</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01023679591936857</v>
+        <v>0.01023679591936858</v>
       </c>
     </row>
     <row r="4">
@@ -6978,85 +6978,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02314051701889737</v>
+        <v>0.02314051701889733</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02788424857029083</v>
+        <v>0.02788424857029085</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04084043877055247</v>
+        <v>0.04084043877055243</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03200043289503302</v>
+        <v>0.03200043289503305</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03440391680364951</v>
+        <v>0.03440391680364954</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03001284828920626</v>
+        <v>0.03001284828920624</v>
       </c>
       <c r="H4" t="n">
         <v>0.03685190696165019</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03635160709065475</v>
+        <v>0.03635160709065479</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03684165771397928</v>
+        <v>0.03684165771397929</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03201687913328003</v>
+        <v>0.03201687913328005</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03327842628725758</v>
+        <v>0.03327842628725761</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02724220331726519</v>
+        <v>0.02724220331726525</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02510507131349994</v>
+        <v>0.02510507131349999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03509860039514543</v>
+        <v>0.03509860039514542</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03415943133265034</v>
+        <v>0.03415943133265031</v>
       </c>
       <c r="Q4" t="n">
         <v>0.02312079462885063</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05236141436347325</v>
+        <v>0.05236141436347323</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03554834339372808</v>
+        <v>0.0355483433937281</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02623936588562228</v>
+        <v>0.02623936588562226</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02510507131349994</v>
+        <v>0.02510507131349998</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03437081534506142</v>
+        <v>0.03437081534506146</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05537704840830494</v>
+        <v>0.05537704840830496</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2000017829514158</v>
+        <v>0.2000017829514157</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1439422581171594</v>
+        <v>0.1439422581171592</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03906759313308266</v>
+        <v>0.03906759313308271</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05894214648976116</v>
+        <v>0.05894214648976105</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0200048093869589</v>
+        <v>0.02000480938695889</v>
       </c>
     </row>
     <row r="5">
@@ -7066,85 +7066,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006545060136482253</v>
+        <v>0.00654506013648228</v>
       </c>
       <c r="C5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.00654506013648228</v>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.006526890820274318</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="N5" t="n">
         <v>0.00654506013648228</v>
       </c>
-      <c r="E5" t="n">
+      <c r="O5" t="n">
         <v>0.00654506013648228</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.006545060136482253</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="P5" t="n">
         <v>0.00654506013648228</v>
       </c>
-      <c r="H5" t="n">
+      <c r="Q5" t="n">
         <v>0.00654506013648228</v>
       </c>
-      <c r="I5" t="n">
+      <c r="R5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.00651147234199701</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.00642249342945902</v>
+      </c>
+      <c r="W5" t="n">
         <v>0.00654506013648228</v>
       </c>
-      <c r="J5" t="n">
-        <v>0.006526890820274319</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="X5" t="n">
         <v>0.00654506013648228</v>
       </c>
-      <c r="L5" t="n">
+      <c r="Y5" t="n">
+        <v>0.00651147234199701</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.006545060136482279</v>
+      </c>
+      <c r="AB5" t="n">
         <v>0.00654506013648228</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.00654506013648228</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.006545060136482253</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.006545060136482253</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.006545060136482253</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.006545060136482253</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.00654506013648228</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.00654506013648228</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.00654506013648228</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.006511472341997004</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.006422493429459006</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.006545060136482253</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.006545060136482253</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.006511472341997004</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.00654506013648228</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.00654506013648228</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.006545060136482253</v>
       </c>
     </row>
     <row r="6">
@@ -7154,85 +7154,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009435505355836508</v>
+        <v>0.009435505355836491</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01366554304187156</v>
+        <v>0.009435505355836491</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009435505355836508</v>
+        <v>0.009435505355836491</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01366554304187156</v>
+        <v>0.01366554304187154</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01366554304187156</v>
+        <v>0.01366554304187154</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01366554304187156</v>
+        <v>0.009435505355836491</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01366554304187156</v>
+        <v>0.009435505355836491</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009435505355836508</v>
+        <v>0.009435505355836491</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01364737372566361</v>
+        <v>0.00941733603962853</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009435505355836508</v>
+        <v>0.009435505355836491</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01366554304187156</v>
+        <v>0.01366554304187154</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009435505355836508</v>
+        <v>0.01366554304187154</v>
       </c>
       <c r="N6" t="n">
-        <v>0.009437139561633614</v>
+        <v>0.009437139561633581</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009437139561633614</v>
+        <v>0.009437139561633593</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01367924267355222</v>
+        <v>0.0092058476403831</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01366554304187156</v>
+        <v>0.009435505355836491</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01366554304187156</v>
+        <v>0.01366554304187154</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01366554304187156</v>
+        <v>0.009435505355836491</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01366554304187156</v>
+        <v>0.01366554304187154</v>
       </c>
       <c r="U6" t="n">
-        <v>0.009435505355836508</v>
+        <v>0.009435505355836491</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009312938648813223</v>
+        <v>0.0135429763348483</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009646136178234184</v>
+        <v>0.009646136178234142</v>
       </c>
       <c r="X6" t="n">
-        <v>0.009435505355836508</v>
+        <v>0.009435505355836491</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009612017478387894</v>
+        <v>0.009612017478387887</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01366554304187156</v>
+        <v>0.01366554304187154</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009435505355836508</v>
+        <v>0.01366554304187154</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.009429994558739009</v>
+        <v>0.009429994558738998</v>
       </c>
     </row>
     <row r="7">
@@ -7242,85 +7242,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="J7" t="n">
         <v>0.009381676714579195</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009399719331354781</v>
+        <v>0.009399719331354771</v>
       </c>
       <c r="P7" t="n">
-        <v>0.009399719331354781</v>
+        <v>0.009399719331354771</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="U7" t="n">
-        <v>0.009392852585331792</v>
+        <v>0.00939285258533178</v>
       </c>
       <c r="V7" t="n">
-        <v>0.009277279323763902</v>
+        <v>0.0092772793237639</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00939984603078717</v>
+        <v>0.009399846030787151</v>
       </c>
     </row>
     <row r="8">
@@ -7330,85 +7330,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01654661328204165</v>
+        <v>0.01654661328204164</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.02362650108151134</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.02362650108151134</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.01985666967194805</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01764957705678113</v>
+        <v>0.01764957705678111</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.02509456193789557</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.02362650108151134</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.02362650108151134</v>
       </c>
       <c r="J8" t="n">
         <v>0.0236083317653034</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.02362650108151134</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.02362650108151134</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.02362650108150954</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01813840359745061</v>
+        <v>0.0181384035974506</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01964658043834983</v>
+        <v>0.01964658043834979</v>
       </c>
       <c r="P8" t="n">
         <v>0.01927688985199085</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01515525373893538</v>
+        <v>0.01515525373893536</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.02362650108151134</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.02362650108151134</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.02362650108151134</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01926490989787118</v>
+        <v>0.02016558078109833</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02350393437448805</v>
+        <v>0.02156302476251342</v>
       </c>
       <c r="W8" t="n">
         <v>0.02362789248216664</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01580413952361079</v>
+        <v>0.0158041395236108</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03065676873162551</v>
+        <v>0.0306567687316255</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.01641510073135735</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02362650108151135</v>
+        <v>0.02362650108151134</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03102203589850066</v>
+        <v>0.03102203589850061</v>
       </c>
     </row>
     <row r="9">
@@ -7418,85 +7418,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01561112943246703</v>
+        <v>0.015611129432467</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.0177824645071208</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01192656123575645</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396297449195</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01841579218237161</v>
+        <v>0.01841579218237158</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01936944631413392</v>
+        <v>0.0193694463141339</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01957289789031488</v>
+        <v>0.01957289789031485</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01843396297449197</v>
+        <v>0.01843396297449195</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0183113947915563</v>
+        <v>0.02156888368001278</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01673204536480335</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01843396149857959</v>
+        <v>0.01843396149857955</v>
       </c>
     </row>
     <row r="10">
@@ -7509,31 +7509,31 @@
         <v>0.01005838278884387</v>
       </c>
       <c r="C10" t="n">
-        <v>0.009999596871262176</v>
+        <v>0.00999959687126218</v>
       </c>
       <c r="D10" t="n">
-        <v>0.009673622120963284</v>
+        <v>0.009673622120963277</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02111421000448127</v>
+        <v>0.02111421000448129</v>
       </c>
       <c r="F10" t="n">
-        <v>0.009847405097781666</v>
+        <v>0.009847405097781672</v>
       </c>
       <c r="G10" t="n">
-        <v>0.009798667707179631</v>
+        <v>0.009798667707179638</v>
       </c>
       <c r="H10" t="n">
-        <v>0.009818572844814237</v>
+        <v>0.009818572844814244</v>
       </c>
       <c r="I10" t="n">
-        <v>0.009800982781798509</v>
+        <v>0.009800982781798534</v>
       </c>
       <c r="J10" t="n">
-        <v>0.009720079427026296</v>
+        <v>0.009720079427026303</v>
       </c>
       <c r="K10" t="n">
-        <v>0.009876198202811369</v>
+        <v>0.009876198202811371</v>
       </c>
       <c r="L10" t="n">
         <v>0.009778960078241505</v>
@@ -7542,49 +7542,49 @@
         <v>0.01000745363338207</v>
       </c>
       <c r="N10" t="n">
-        <v>0.009788259323363774</v>
+        <v>0.009788259323363772</v>
       </c>
       <c r="O10" t="n">
-        <v>0.009737006635680041</v>
+        <v>0.00973700663568005</v>
       </c>
       <c r="P10" t="n">
-        <v>0.009770958463920671</v>
+        <v>0.009770958463920676</v>
       </c>
       <c r="Q10" t="n">
         <v>0.01007606266206191</v>
       </c>
       <c r="R10" t="n">
-        <v>0.009439866102778787</v>
+        <v>0.009439866102778782</v>
       </c>
       <c r="S10" t="n">
-        <v>0.009702061031972123</v>
+        <v>0.009702061031972133</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01002742785759128</v>
+        <v>0.01002742785759129</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01001562077303368</v>
+        <v>0.01001562077303369</v>
       </c>
       <c r="V10" t="n">
-        <v>0.005212806229776381</v>
+        <v>0.005212806229776374</v>
       </c>
       <c r="W10" t="n">
-        <v>0.009278593274837666</v>
+        <v>0.009278593274837672</v>
       </c>
       <c r="X10" t="n">
-        <v>0.005687843331567725</v>
+        <v>0.005687843331567729</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.007267470398428348</v>
+        <v>0.007267470398428361</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.009625381506042328</v>
+        <v>0.009625381506042337</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.009244925702004803</v>
+        <v>0.009244925702004806</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.01006091971799374</v>
+        <v>0.01006091971799375</v>
       </c>
     </row>
     <row r="11">
@@ -7597,10 +7597,10 @@
         <v>0.01017622489888563</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01011379626101135</v>
+        <v>0.01011379626101136</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01001070846088847</v>
+        <v>0.01001070846088849</v>
       </c>
       <c r="E11" t="n">
         <v>0.02120413913094254</v>
@@ -7609,7 +7609,7 @@
         <v>0.01006565016868406</v>
       </c>
       <c r="G11" t="n">
-        <v>0.009999633665822225</v>
+        <v>0.009999633665822235</v>
       </c>
       <c r="H11" t="n">
         <v>0.01006711061012321</v>
@@ -7618,22 +7618,22 @@
         <v>0.01005910707539487</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01002042644217304</v>
+        <v>0.01002042644217303</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01009533603754906</v>
+        <v>0.01009533603754905</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01004908667509421</v>
+        <v>0.01004908667509422</v>
       </c>
       <c r="M11" t="n">
         <v>0.01010584628481837</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01004288008944567</v>
+        <v>0.01004288008944568</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01002999772503106</v>
+        <v>0.01002999772503107</v>
       </c>
       <c r="P11" t="n">
         <v>0.01004543657182707</v>
@@ -7642,7 +7642,7 @@
         <v>0.01018426929754226</v>
       </c>
       <c r="R11" t="n">
-        <v>0.009887181723086726</v>
+        <v>0.009887181723086738</v>
       </c>
       <c r="S11" t="n">
         <v>0.01001409736397892</v>
@@ -7651,7 +7651,7 @@
         <v>0.01016214030651819</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01015346232946727</v>
+        <v>0.01015346232946728</v>
       </c>
       <c r="V11" t="n">
         <v>0.005557570213978844</v>
@@ -7660,10 +7660,10 @@
         <v>0.00982141818497108</v>
       </c>
       <c r="X11" t="n">
-        <v>0.008141736346962166</v>
+        <v>0.008141736346962174</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0089063508671365</v>
+        <v>0.008906350867136502</v>
       </c>
       <c r="Z11" t="n">
         <v>0.009995924065147131</v>
@@ -7672,7 +7672,7 @@
         <v>0.009806099332039929</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01012144629356924</v>
+        <v>0.01012144629356925</v>
       </c>
     </row>
   </sheetData>
@@ -7838,85 +7838,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0096517917826296</v>
+        <v>0.009651791782629595</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009632206942482161</v>
+        <v>0.009632206942482154</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009649205178203149</v>
+        <v>0.009649205178203144</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02110107031867204</v>
+        <v>0.02110107031867201</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009645122584734551</v>
+        <v>0.009645122584734548</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009507276567429874</v>
+        <v>0.009507276567429871</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0096517917826296</v>
+        <v>0.009651791782629595</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0096517917826296</v>
+        <v>0.009651791782629595</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009650125639207547</v>
+        <v>0.009650125639207544</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009656912811212039</v>
+        <v>0.009656912811212033</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0096517917826296</v>
+        <v>0.009651791782629595</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009613742397193077</v>
+        <v>0.009613742397193072</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00962400607064055</v>
+        <v>0.009624006070640546</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0096517917826296</v>
+        <v>0.009651791782629595</v>
       </c>
       <c r="P2" t="n">
-        <v>0.009646148028955522</v>
+        <v>0.009646148028955517</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0096517917826296</v>
+        <v>0.009651791782629595</v>
       </c>
       <c r="R2" t="n">
-        <v>0.009622551006632195</v>
+        <v>0.00962255100663219</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0096517917826296</v>
+        <v>0.009651791782629595</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0096517917826296</v>
+        <v>0.009651791782629595</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009644346855867885</v>
+        <v>0.009644346855867878</v>
       </c>
       <c r="V2" t="n">
-        <v>0.005200943279011839</v>
+        <v>0.005200943279011833</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0096517917826296</v>
+        <v>0.009651791782629595</v>
       </c>
       <c r="X2" t="n">
-        <v>0.009609900269861547</v>
+        <v>0.009609900269861542</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0096517917826296</v>
+        <v>0.009651791782629595</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00965261011558098</v>
+        <v>0.009652610115580973</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0096517917826296</v>
+        <v>0.009651791782629595</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00954039149231499</v>
+        <v>0.009540391492314984</v>
       </c>
     </row>
     <row r="3">
@@ -7926,85 +7926,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009722104442473845</v>
+        <v>0.009722104442473853</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02131777569193057</v>
+        <v>0.02131777569193055</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009716238540922476</v>
+        <v>0.009716238540922484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009583689577969696</v>
+        <v>0.009583689577969704</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009703832441634044</v>
+        <v>0.009703832441634043</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009711102694997684</v>
+        <v>0.009711102694997692</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009699322804430269</v>
+        <v>0.009699322804430279</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="R3" t="n">
-        <v>0.009673500544398833</v>
+        <v>0.009673500544398842</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="U3" t="n">
-        <v>0.009697351778748874</v>
+        <v>0.009697351778748885</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005165825771422366</v>
+        <v>0.005165825771422364</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009659656817737249</v>
+        <v>0.009659656817737257</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009706670845129342</v>
+        <v>0.009706670845129351</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009705498767505011</v>
+        <v>0.00970549876750502</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009583593304514582</v>
+        <v>0.00958359330451459</v>
       </c>
     </row>
     <row r="4">
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02764153601940816</v>
+        <v>0.02764153601940817</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02678824731731593</v>
+        <v>0.02678824731731594</v>
       </c>
       <c r="D4" t="n">
         <v>0.03493762699567501</v>
@@ -8026,73 +8026,73 @@
         <v>0.03502371380505376</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03193650828548418</v>
+        <v>0.03193650828548424</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02566363524759127</v>
+        <v>0.0256636352475911</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03022943032166625</v>
+        <v>0.03022943032166624</v>
       </c>
       <c r="I4" t="n">
         <v>0.02943441546363674</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03411957299448451</v>
+        <v>0.03411957299448429</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02776238265627415</v>
+        <v>0.02776238265627411</v>
       </c>
       <c r="L4" t="n">
         <v>0.03333918054059059</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02642332301146393</v>
+        <v>0.02642332301146391</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02548598714136096</v>
+        <v>0.02548598714136094</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03470630993260398</v>
+        <v>0.03470630993260402</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03351711628717915</v>
+        <v>0.03351711628717913</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02259336197421199</v>
+        <v>0.02259336197421198</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04970999646736683</v>
+        <v>0.04970999646736681</v>
       </c>
       <c r="S4" t="n">
         <v>0.03261395976221807</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02384552286151633</v>
+        <v>0.02384552286151634</v>
       </c>
       <c r="U4" t="n">
         <v>0.02548598714136094</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03723216581855634</v>
+        <v>0.0372321658185564</v>
       </c>
       <c r="W4" t="n">
         <v>0.04459316441245688</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2489436754613663</v>
+        <v>0.248943675461366</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1301380828770411</v>
+        <v>0.1301380828770412</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03222372911859412</v>
+        <v>0.03222372911859416</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05904038369564198</v>
+        <v>0.05904038369564194</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02449427614270862</v>
+        <v>0.02449427614270861</v>
       </c>
     </row>
     <row r="5">
@@ -8102,85 +8102,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006102585954199024</v>
+        <v>0.006102585954199039</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006102585954199024</v>
+        <v>0.006102585954199039</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006085719413407138</v>
+        <v>0.006085719413407155</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="M5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006102585954199024</v>
+        <v>0.006102585954199039</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006102585954199024</v>
+        <v>0.006102585954199039</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006102585954199024</v>
+        <v>0.006102585954199039</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.006102585954199024</v>
+        <v>0.006102585954199039</v>
       </c>
       <c r="R5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="S5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="T5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="U5" t="n">
-        <v>0.006084716936245397</v>
+        <v>0.006084716936245396</v>
       </c>
       <c r="V5" t="n">
-        <v>0.005988606392718906</v>
+        <v>0.005988606392718923</v>
       </c>
       <c r="W5" t="n">
-        <v>0.006102585954199024</v>
+        <v>0.006102585954199039</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006102585954199024</v>
+        <v>0.006102585954199039</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.006084716936245397</v>
+        <v>0.006084716936245396</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.006102585954199023</v>
+        <v>0.006102585954199041</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.006102585954199024</v>
+        <v>0.006102585954199039</v>
       </c>
     </row>
     <row r="6">
@@ -8190,82 +8190,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.01146238364431685</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.01146238364431685</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.01146238364431685</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.01146238364431685</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007642179193890633</v>
+        <v>0.01146238364431685</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007642179193890633</v>
+        <v>0.01146238364431685</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007642179193890633</v>
+        <v>0.007642179193890632</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.007642179193890632</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01144551710352498</v>
+        <v>0.007625312653098747</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007642179193890633</v>
+        <v>0.01146238364431685</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.01146238364431685</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.01146238364431685</v>
       </c>
       <c r="N6" t="n">
-        <v>0.007642235392666932</v>
+        <v>0.007642235392666924</v>
       </c>
       <c r="O6" t="n">
-        <v>0.007642235392666907</v>
+        <v>0.01144638575627914</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01144631464096386</v>
+        <v>0.01144631464096387</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.01146238364431685</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.007642179193890632</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007642179193890633</v>
+        <v>0.007642179193890632</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.01146238364431685</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.01146238364431685</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007528199632410518</v>
+        <v>0.00752819963241052</v>
       </c>
       <c r="W6" t="n">
         <v>0.01144644807883664</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.007642179193890632</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.007745991865069311</v>
+        <v>0.007745991865069303</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.007642179193890632</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01146238364431686</v>
+        <v>0.007642179193890632</v>
       </c>
       <c r="AB6" t="n">
         <v>0.007636648048694055</v>
@@ -8278,85 +8278,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009078058281061617</v>
+        <v>0.009078058281061613</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="M7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="N7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009094799019503365</v>
+        <v>0.009094799019503363</v>
       </c>
       <c r="P7" t="n">
-        <v>0.009094799019503365</v>
+        <v>0.009094799019503361</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="R7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="S7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="U7" t="n">
-        <v>0.009088921519616749</v>
+        <v>0.009088921519616747</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008980945260373394</v>
+        <v>0.00898094526037339</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="X7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.009094924821853508</v>
+        <v>0.009094924821853499</v>
       </c>
     </row>
     <row r="8">
@@ -8369,82 +8369,82 @@
         <v>0.01594204848383727</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.02272371764909973</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.02272371764909973</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.01911267886531119</v>
       </c>
       <c r="F8" t="n">
         <v>0.01699855328074944</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.02412994092898402</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.02272371764909973</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.02272371764909973</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02270685110830788</v>
+        <v>0.02270685110830785</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.02272371764909973</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.02272371764909973</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.022723717649098</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01746678949749812</v>
+        <v>0.01746678949749809</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01891143899873913</v>
+        <v>0.01891143899873911</v>
       </c>
       <c r="P8" t="n">
-        <v>0.018557320498354</v>
+        <v>0.01855732049835396</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01460929570880581</v>
+        <v>0.0146092957088058</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.02272371764909973</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.02272371764909973</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.02272371764909973</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01854635455058768</v>
+        <v>0.01940912052536491</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02260973808761962</v>
+        <v>0.02075118170820053</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0227250504414665</v>
+        <v>0.02272505044146646</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01523084916321872</v>
+        <v>0.0152308491632187</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02945878479968092</v>
+        <v>0.02945878479968086</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.01581607549737329</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02272371764909977</v>
+        <v>0.02272371764909973</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.02980773816622182</v>
+        <v>0.02980773816622178</v>
       </c>
     </row>
     <row r="9">
@@ -8457,43 +8457,43 @@
         <v>0.01471895610779527</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01672926575483102</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01130763416238365</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244933035271</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="J9" t="n">
         <v>0.01731558169452973</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01819855756223088</v>
+        <v>0.0181985575622309</v>
       </c>
       <c r="P9" t="n">
         <v>0.01838692124274962</v>
@@ -8502,37 +8502,37 @@
         <v>0.01733244933035271</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0172184686738415</v>
+        <v>0.02023438337237207</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01575674531803548</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01733244823532161</v>
+        <v>0.01733244823532162</v>
       </c>
     </row>
     <row r="10">
@@ -8542,85 +8542,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.009283444796177424</v>
+        <v>0.009283444796177426</v>
       </c>
       <c r="C10" t="n">
-        <v>0.009367539833187156</v>
+        <v>0.009367539833187158</v>
       </c>
       <c r="D10" t="n">
-        <v>0.009162902166758849</v>
+        <v>0.009162902166758842</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02061888342101356</v>
+        <v>0.02061888342101352</v>
       </c>
       <c r="F10" t="n">
-        <v>0.009257346137995802</v>
+        <v>0.009257346137995804</v>
       </c>
       <c r="G10" t="n">
-        <v>0.009214793924398416</v>
+        <v>0.009214793924398413</v>
       </c>
       <c r="H10" t="n">
-        <v>0.009302796013314133</v>
+        <v>0.009302796013314124</v>
       </c>
       <c r="I10" t="n">
-        <v>0.009302339782989921</v>
+        <v>0.009302339782989923</v>
       </c>
       <c r="J10" t="n">
-        <v>0.009141404287607872</v>
+        <v>0.009141404287607867</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00933036298824922</v>
+        <v>0.009330362988249222</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009135136149489633</v>
+        <v>0.009135136149489631</v>
       </c>
       <c r="M10" t="n">
-        <v>0.009371936891900875</v>
+        <v>0.009371936891900882</v>
       </c>
       <c r="N10" t="n">
-        <v>0.009308791989207432</v>
+        <v>0.009308791989207433</v>
       </c>
       <c r="O10" t="n">
-        <v>0.009089805579513791</v>
+        <v>0.009089805579513787</v>
       </c>
       <c r="P10" t="n">
         <v>0.009113163583009931</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.009436589852309532</v>
+        <v>0.009436589852309531</v>
       </c>
       <c r="R10" t="n">
-        <v>0.008833070443718338</v>
+        <v>0.008833070443718342</v>
       </c>
       <c r="S10" t="n">
-        <v>0.009149486827837677</v>
+        <v>0.00914948682783767</v>
       </c>
       <c r="T10" t="n">
-        <v>0.009425396083385825</v>
+        <v>0.009425396083385823</v>
       </c>
       <c r="U10" t="n">
-        <v>0.009344078317761568</v>
+        <v>0.009344078317761562</v>
       </c>
       <c r="V10" t="n">
-        <v>0.004492739822213558</v>
+        <v>0.004492739822213553</v>
       </c>
       <c r="W10" t="n">
-        <v>0.008899060668062762</v>
+        <v>0.00889906066806276</v>
       </c>
       <c r="X10" t="n">
-        <v>0.003801740815153242</v>
+        <v>0.003801740815153249</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.006966977276299921</v>
+        <v>0.006966977276299922</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.009142175382326289</v>
+        <v>0.009142175382326293</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.008588517530552774</v>
+        <v>0.008588517530552772</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.009304082496628842</v>
+        <v>0.00930408249662884</v>
       </c>
     </row>
     <row r="11">
@@ -8630,85 +8630,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.009459755880669343</v>
+        <v>0.009459755880669335</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00947087891532635</v>
+        <v>0.009470878915326346</v>
       </c>
       <c r="D11" t="n">
         <v>0.009402321995710871</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02078307210816729</v>
+        <v>0.02078307210816727</v>
       </c>
       <c r="F11" t="n">
-        <v>0.009436325078999603</v>
+        <v>0.009436325078999597</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00933942786945424</v>
+        <v>0.009339427869454233</v>
       </c>
       <c r="H11" t="n">
-        <v>0.009468560746135219</v>
+        <v>0.009468560746135215</v>
       </c>
       <c r="I11" t="n">
-        <v>0.009468353159883772</v>
+        <v>0.009468353159883766</v>
       </c>
       <c r="J11" t="n">
-        <v>0.009394219036773467</v>
+        <v>0.00939421903677347</v>
       </c>
       <c r="K11" t="n">
-        <v>0.009483675031296036</v>
+        <v>0.009483675031296027</v>
       </c>
       <c r="L11" t="n">
         <v>0.009392274973794777</v>
       </c>
       <c r="M11" t="n">
-        <v>0.00946197068079457</v>
+        <v>0.009461970680794567</v>
       </c>
       <c r="N11" t="n">
-        <v>0.009443503222285663</v>
+        <v>0.009443503222285659</v>
       </c>
       <c r="O11" t="n">
-        <v>0.009371649419995813</v>
+        <v>0.009371649419995812</v>
       </c>
       <c r="P11" t="n">
-        <v>0.009379443715230659</v>
+        <v>0.009379443715230654</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.009529437369253794</v>
+        <v>0.009529437369253786</v>
       </c>
       <c r="R11" t="n">
-        <v>0.009240152632530757</v>
+        <v>0.009240152632530746</v>
       </c>
       <c r="S11" t="n">
-        <v>0.009398804578176035</v>
+        <v>0.00939880457817603</v>
       </c>
       <c r="T11" t="n">
-        <v>0.009524344168721064</v>
+        <v>0.009524344168721052</v>
       </c>
       <c r="U11" t="n">
-        <v>0.009483606305302929</v>
+        <v>0.009483606305302913</v>
       </c>
       <c r="V11" t="n">
-        <v>0.004894687027124179</v>
+        <v>0.004894687027124176</v>
       </c>
       <c r="W11" t="n">
-        <v>0.009284859877417624</v>
+        <v>0.009284859877417622</v>
       </c>
       <c r="X11" t="n">
-        <v>0.006944529820615185</v>
+        <v>0.006944529820615169</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.008405755776981109</v>
+        <v>0.0084057557769811</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.009395762881065292</v>
+        <v>0.009395762881065287</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.009143561760208325</v>
+        <v>0.009143561760208314</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.009413213183978876</v>
+        <v>0.009413213183978872</v>
       </c>
     </row>
   </sheetData>
@@ -8880,7 +8880,7 @@
         <v>0.01057839048714225</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01100740559761079</v>
+        <v>0.01100740559761078</v>
       </c>
       <c r="E2" t="n">
         <v>0.02161706138846215</v>
@@ -8889,7 +8889,7 @@
         <v>0.01070651361306183</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01156989268787498</v>
+        <v>0.01156989268787497</v>
       </c>
       <c r="H2" t="n">
         <v>0.01116684151365128</v>
@@ -8907,7 +8907,7 @@
         <v>0.01116684151365128</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01107725119516877</v>
+        <v>0.01107725119516876</v>
       </c>
       <c r="N2" t="n">
         <v>0.01107878445663701</v>
@@ -8934,7 +8934,7 @@
         <v>0.01116757888748536</v>
       </c>
       <c r="V2" t="n">
-        <v>0.006151947317461457</v>
+        <v>0.006151947317461459</v>
       </c>
       <c r="W2" t="n">
         <v>0.01116684151365128</v>
@@ -8962,28 +8962,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01064896037847586</v>
+        <v>0.01064896037847585</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02178109174605163</v>
+        <v>0.02178109174605164</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01063882023361333</v>
+        <v>0.01063882023361332</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01057201777820921</v>
+        <v>0.0105720177782092</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="J3" t="n">
         <v>0.0106003572414288</v>
@@ -8992,55 +8992,55 @@
         <v>0.01063616836006882</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="P3" t="n">
         <v>0.01063304399320007</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="R3" t="n">
         <v>0.01063366409999014</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="U3" t="n">
         <v>0.01063389343607599</v>
       </c>
       <c r="V3" t="n">
-        <v>0.006066015510062237</v>
+        <v>0.006066015510062232</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01062470929944219</v>
+        <v>0.01062470929944218</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01063379495779848</v>
+        <v>0.01063379495779847</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01063308652515406</v>
+        <v>0.01063308652515405</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01051118106216363</v>
+        <v>0.01051118106216362</v>
       </c>
     </row>
     <row r="4">
@@ -9053,82 +9053,82 @@
         <v>0.1331384153796702</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03800786002753703</v>
+        <v>0.03800786002753696</v>
       </c>
       <c r="D4" t="n">
         <v>0.1645868529134894</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05470405111277767</v>
+        <v>0.05470405111277769</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07703633737946788</v>
+        <v>0.0770363373794677</v>
       </c>
       <c r="G4" t="n">
         <v>0.295238061359376</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06270978782810864</v>
+        <v>0.0627097878281086</v>
       </c>
       <c r="I4" t="n">
         <v>0.1374543367176682</v>
       </c>
       <c r="J4" t="n">
-        <v>0.188318210705854</v>
+        <v>0.1883182107058541</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1850445624477006</v>
+        <v>0.1850445624477003</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2907241571136338</v>
+        <v>0.2907241571136337</v>
       </c>
       <c r="M4" t="n">
         <v>0.1726737369844984</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3259046673348899</v>
+        <v>0.325904667334891</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1137265753323704</v>
+        <v>0.1137265753323703</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2229275312833394</v>
+        <v>0.2229275312833387</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07543530674639129</v>
+        <v>0.07543530674639125</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08111033060886981</v>
+        <v>0.08111033060886985</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1518711333760929</v>
+        <v>0.1518711333760927</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1356592587876493</v>
+        <v>0.1356592587876492</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3259046673348899</v>
+        <v>0.3259046673348907</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05646902917455055</v>
+        <v>0.05646902917455049</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1623439813291111</v>
+        <v>0.162343981329111</v>
       </c>
       <c r="X4" t="n">
         <v>0.3965383782297418</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2630367634075376</v>
+        <v>0.2630367634075373</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1152420537460316</v>
+        <v>0.1152420537460317</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2025527276126781</v>
+        <v>0.2025527276126779</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.231615666816111</v>
+        <v>0.2316156668161105</v>
       </c>
     </row>
     <row r="5">
@@ -9138,85 +9138,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008071354966065262</v>
+        <v>0.008071354966065229</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008071354966065262</v>
+        <v>0.008071354966065229</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008046311163832354</v>
+        <v>0.008046311163832335</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="N5" t="n">
-        <v>0.008071354966065262</v>
+        <v>0.008071354966065229</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008071354966065262</v>
+        <v>0.008071354966065229</v>
       </c>
       <c r="P5" t="n">
-        <v>0.008071354966065262</v>
+        <v>0.008071354966065229</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008071354966065262</v>
+        <v>0.008071354966065229</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="S5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="T5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007903290408758958</v>
+        <v>0.007903290408758892</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007904704466833475</v>
+        <v>0.007904704466833468</v>
       </c>
       <c r="W5" t="n">
-        <v>0.008071354966065262</v>
+        <v>0.008071354966065229</v>
       </c>
       <c r="X5" t="n">
-        <v>0.008071354966065262</v>
+        <v>0.008071354966065229</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.007903290408758958</v>
+        <v>0.007903290408758892</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.008071354966065265</v>
+        <v>0.008071354966065227</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.008071354966065262</v>
+        <v>0.008071354966065229</v>
       </c>
     </row>
     <row r="6">
@@ -9226,85 +9226,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0156396138046624</v>
+        <v>0.01563961380466233</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01036294908657517</v>
+        <v>0.01036294908657513</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0156396138046624</v>
+        <v>0.01563961380466233</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0156396138046624</v>
+        <v>0.01563961380466233</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0156396138046624</v>
+        <v>0.01563961380466233</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01036294908657517</v>
+        <v>0.01036294908657513</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0156396138046624</v>
+        <v>0.01563961380466233</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01036294908657517</v>
+        <v>0.01036294908657513</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01561457000242945</v>
+        <v>0.01033790528434225</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01036294908657517</v>
+        <v>0.01036294908657513</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01036294908657517</v>
+        <v>0.01563961380466233</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0156396138046624</v>
+        <v>0.01563961380466233</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01039032762815508</v>
+        <v>0.01039032762815501</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01039032762815507</v>
+        <v>0.01039032762815501</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01567250580190639</v>
+        <v>0.01567250580190631</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01036294908657517</v>
+        <v>0.01563961380466233</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0156396138046624</v>
+        <v>0.01563961380466233</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0156396138046624</v>
+        <v>0.01563961380466233</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0156396138046624</v>
+        <v>0.01036294908657513</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0156396138046624</v>
+        <v>0.01563961380466233</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01019629858734338</v>
+        <v>0.01547296330543057</v>
       </c>
       <c r="W6" t="n">
         <v>0.01057477764432764</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0156396138046624</v>
+        <v>0.01036294908657513</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01051535826559054</v>
+        <v>0.01051535826559068</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01036294908657517</v>
+        <v>0.01036294908657513</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0156396138046624</v>
+        <v>0.01563961380466233</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01041327083701208</v>
+        <v>0.01041327083701204</v>
       </c>
     </row>
     <row r="7">
@@ -9314,85 +9314,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01193973618436619</v>
+        <v>0.01193973618436615</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0119646372351622</v>
+        <v>0.01196463723516214</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0119646372351622</v>
+        <v>0.01196463723516214</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0119584287173019</v>
+        <v>0.01195842871730181</v>
       </c>
       <c r="V7" t="n">
         <v>0.01179812948736727</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01196477998659908</v>
+        <v>0.01196477998659902</v>
       </c>
     </row>
     <row r="8">
@@ -9402,85 +9402,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02000669045986155</v>
+        <v>0.02000669045986149</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.02838187167882876</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.02838187167882876</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.0239223347322256</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02131144581090836</v>
+        <v>0.0213114458109083</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.03011852006377022</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.02838187167882876</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.02838187167882876</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02835682787659591</v>
+        <v>0.02835682787659589</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.02838187167882876</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.02838187167882876</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.02838187167882748</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02188970509670276</v>
+        <v>0.0218897050967027</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02367380884375004</v>
+        <v>0.02367380884374998</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02323648190538509</v>
+        <v>0.02323648190538501</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01836077619630129</v>
+        <v>0.01836077619630118</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.02838187167882876</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.02838187167882876</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.02838187167882876</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02322370335458503</v>
+        <v>0.02428924605890252</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02821522117959703</v>
+        <v>0.02592085098234207</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02838351764139865</v>
+        <v>0.02838351764139858</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01912837819643803</v>
+        <v>0.01912837819643796</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03670089274399374</v>
+        <v>0.03670089274399372</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.01985111716894443</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02838187167882884</v>
+        <v>0.02838187167882876</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03713044878281072</v>
+        <v>0.03713044878281067</v>
       </c>
     </row>
     <row r="9">
@@ -9490,85 +9490,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0228152333115861</v>
+        <v>0.02281523331158609</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02621668774907802</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.01704325873739889</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727751374697</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02721223066685002</v>
+        <v>0.02721223066684999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02870273717217042</v>
+        <v>0.02870273717217038</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0290214495048241</v>
+        <v>0.02902144950482408</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02723727751374701</v>
+        <v>0.02723727751374697</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02707062396985113</v>
+        <v>0.03217356533912726</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02457117808335692</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02723727446908296</v>
+        <v>0.02723727446908292</v>
       </c>
     </row>
     <row r="10">
@@ -9578,13 +9578,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00776834056449846</v>
+        <v>0.007768340564498455</v>
       </c>
       <c r="C10" t="n">
         <v>0.01013434707681942</v>
       </c>
       <c r="D10" t="n">
-        <v>0.007521142309890312</v>
+        <v>0.0075211423098903</v>
       </c>
       <c r="E10" t="n">
         <v>0.02076536483339558</v>
@@ -9593,70 +9593,70 @@
         <v>0.009326541095645405</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003736691779381318</v>
+        <v>0.003736691779381313</v>
       </c>
       <c r="H10" t="n">
-        <v>0.009665166718095445</v>
+        <v>0.009665166718095435</v>
       </c>
       <c r="I10" t="n">
-        <v>0.008084499871023871</v>
+        <v>0.008084499871023875</v>
       </c>
       <c r="J10" t="n">
-        <v>0.006507739565869558</v>
+        <v>0.006507739565869555</v>
       </c>
       <c r="K10" t="n">
         <v>0.006682967001638111</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004328342681225227</v>
+        <v>0.004328342681225226</v>
       </c>
       <c r="M10" t="n">
-        <v>0.007125422912141579</v>
+        <v>0.007125422912141583</v>
       </c>
       <c r="N10" t="n">
-        <v>0.007088058410905714</v>
+        <v>0.007088058410905712</v>
       </c>
       <c r="O10" t="n">
-        <v>0.008173091105208679</v>
+        <v>0.008173091105208677</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005743857091157503</v>
+        <v>0.005743857091157512</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.009290235820315431</v>
+        <v>0.009290235820315424</v>
       </c>
       <c r="R10" t="n">
-        <v>0.009278133509842522</v>
+        <v>0.009278133509842511</v>
       </c>
       <c r="S10" t="n">
-        <v>0.007223281034090822</v>
+        <v>0.007223281034090819</v>
       </c>
       <c r="T10" t="n">
-        <v>0.008112279899642624</v>
+        <v>0.008112279899642616</v>
       </c>
       <c r="U10" t="n">
-        <v>0.003579635188467911</v>
+        <v>0.003579635188467895</v>
       </c>
       <c r="V10" t="n">
-        <v>0.005037713354763686</v>
+        <v>0.005037713354763685</v>
       </c>
       <c r="W10" t="n">
-        <v>0.007397700430149466</v>
+        <v>0.007397700430149462</v>
       </c>
       <c r="X10" t="n">
-        <v>0.002573552403515812</v>
+        <v>0.002573552403515797</v>
       </c>
       <c r="Y10" t="n">
         <v>0.005142299898890566</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.008220635262847565</v>
+        <v>0.008220635262847558</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.006517533315834025</v>
+        <v>0.006517533315834019</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.006219549474928946</v>
+        <v>0.006219549474928939</v>
       </c>
     </row>
     <row r="11">
@@ -9666,43 +9666,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.009863372972149289</v>
+        <v>0.009863372972149282</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01034423979491328</v>
+        <v>0.01034423979491327</v>
       </c>
       <c r="D11" t="n">
-        <v>0.009591461062487995</v>
+        <v>0.009591461062487993</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02115490240627402</v>
+        <v>0.02115490240627404</v>
       </c>
       <c r="F11" t="n">
         <v>0.01010942242330096</v>
       </c>
       <c r="G11" t="n">
-        <v>0.008459797575516799</v>
+        <v>0.008459797575516795</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01072643491686221</v>
+        <v>0.0107264349168622</v>
       </c>
       <c r="I11" t="n">
         <v>0.01000722646415828</v>
       </c>
       <c r="J11" t="n">
-        <v>0.009271961890146226</v>
+        <v>0.009271961890146219</v>
       </c>
       <c r="K11" t="n">
-        <v>0.009370938583201567</v>
+        <v>0.00937093858320156</v>
       </c>
       <c r="L11" t="n">
-        <v>0.008298162972637163</v>
+        <v>0.008298162972637167</v>
       </c>
       <c r="M11" t="n">
-        <v>0.009481253072987417</v>
+        <v>0.009481253072987415</v>
       </c>
       <c r="N11" t="n">
-        <v>0.009465785367319722</v>
+        <v>0.009465785367319719</v>
       </c>
       <c r="O11" t="n">
         <v>0.01004753575803588</v>
@@ -9717,34 +9717,34 @@
         <v>0.0105505986000621</v>
       </c>
       <c r="S11" t="n">
-        <v>0.009615369148812142</v>
+        <v>0.009615369148812137</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0100198664657095</v>
+        <v>0.01001986646570949</v>
       </c>
       <c r="U11" t="n">
-        <v>0.007957868904236505</v>
+        <v>0.0079578689042365</v>
       </c>
       <c r="V11" t="n">
         <v>0.005684066559796088</v>
       </c>
       <c r="W11" t="n">
-        <v>0.009694730529860474</v>
+        <v>0.009694730529860472</v>
       </c>
       <c r="X11" t="n">
-        <v>0.007495884157481262</v>
+        <v>0.007495884157481254</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.00866851610060264</v>
+        <v>0.008668516100602635</v>
       </c>
       <c r="Z11" t="n">
         <v>0.009784838127532247</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.009294251687920783</v>
+        <v>0.009294251687920786</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.009102735174526507</v>
+        <v>0.009102735174526505</v>
       </c>
     </row>
   </sheetData>
@@ -9910,85 +9910,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01129675929067533</v>
+        <v>0.01129675929067535</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01088100269821729</v>
+        <v>0.01088100269821732</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01094186570066913</v>
+        <v>0.01094186570066911</v>
       </c>
       <c r="E2" t="n">
         <v>0.02188885949256535</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01089312874787802</v>
+        <v>0.01089312874787804</v>
       </c>
       <c r="G2" t="n">
-        <v>0.011659201634928</v>
+        <v>0.01165920163492799</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01129675929067533</v>
+        <v>0.01129675929067535</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01129675929067533</v>
+        <v>0.01129675929067535</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01127116349356331</v>
+        <v>0.0112711634935633</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01130075398587059</v>
+        <v>0.01130075398587061</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01129675929067533</v>
+        <v>0.01129675929067535</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01092804885098423</v>
+        <v>0.01092804885098426</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0109340997429154</v>
+        <v>0.01093409974291537</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01129675929067533</v>
+        <v>0.01129675929067535</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01129674068279654</v>
+        <v>0.01129674068279655</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01129675929067533</v>
+        <v>0.01129675929067535</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01128159042410438</v>
+        <v>0.0112815904241044</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01129675929067533</v>
+        <v>0.01129675929067535</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01129675929067533</v>
+        <v>0.01129675929067535</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01129017537446115</v>
+        <v>0.01129017537446116</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00627822198864664</v>
+        <v>0.006278221988646643</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01129675929067533</v>
+        <v>0.01129675929067535</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01120538280791997</v>
+        <v>0.01120538280791998</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01129675929067533</v>
+        <v>0.01129675929067535</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01093398272175581</v>
+        <v>0.01093398272175582</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01129675929067533</v>
+        <v>0.01129675929067535</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01118535900036072</v>
+        <v>0.01118535900036074</v>
       </c>
     </row>
     <row r="3">
@@ -10007,7 +10007,7 @@
         <v>0.01096873598394586</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02211674433888723</v>
+        <v>0.02211674433888719</v>
       </c>
       <c r="F3" t="n">
         <v>0.01097682810503844</v>
@@ -10022,7 +10022,7 @@
         <v>0.01096873598394586</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01094313725926446</v>
+        <v>0.01094313725926447</v>
       </c>
       <c r="K3" t="n">
         <v>0.01097310735838204</v>
@@ -10086,85 +10086,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02153322098735486</v>
+        <v>0.0215332209873548</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02712782252687312</v>
+        <v>0.02712782252687303</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04651492468155952</v>
+        <v>0.0465149246815595</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03522331946898608</v>
+        <v>0.03522331946898601</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0323216612309469</v>
+        <v>0.03232166123094683</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2127783397714481</v>
+        <v>0.2127783397714463</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03266118576788104</v>
+        <v>0.03266118576788075</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03982989682021868</v>
+        <v>0.03982989682021859</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1268923569864194</v>
+        <v>0.1268923569864192</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05216532220344314</v>
+        <v>0.05216532220344315</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1111373022141047</v>
+        <v>0.1111373022141046</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04259894224582207</v>
+        <v>0.04259894224582193</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06687381608948115</v>
+        <v>0.06687381608948102</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04065077685121356</v>
+        <v>0.04065077685121372</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1229225252579678</v>
+        <v>0.1229225252579677</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03952942687541219</v>
+        <v>0.03952942687541214</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05851628027651572</v>
+        <v>0.05851628027651559</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04951361124943294</v>
+        <v>0.04951361124943304</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03552796705703377</v>
+        <v>0.03552796705703366</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06687381608948113</v>
+        <v>0.06687381608948104</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03293308615533836</v>
+        <v>0.03293308615533832</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07376623091838939</v>
+        <v>0.07376623091838924</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4315338763648204</v>
+        <v>0.4315338763648201</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4964598138096939</v>
+        <v>0.4964598138096933</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04025670707957334</v>
+        <v>0.04025670707957325</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.06580245264890552</v>
+        <v>0.06580245264890561</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.220644975072794</v>
+        <v>3.220644975072787</v>
       </c>
     </row>
     <row r="5">
@@ -10174,85 +10174,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008126867241543047</v>
+        <v>0.008126867241542962</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008126867241543047</v>
+        <v>0.008126867241542962</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008103966652099127</v>
+        <v>0.008103966652099115</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="N5" t="n">
-        <v>0.008126867241543047</v>
+        <v>0.008126867241542962</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008126867241543047</v>
+        <v>0.008126867241542962</v>
       </c>
       <c r="P5" t="n">
-        <v>0.008126867241543047</v>
+        <v>0.008126867241542962</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008126867241543047</v>
+        <v>0.008126867241542962</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="S5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="T5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="U5" t="n">
-        <v>0.007984669482222409</v>
+        <v>0.007984669482222359</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007974089227690086</v>
+        <v>0.007974089227690067</v>
       </c>
       <c r="W5" t="n">
-        <v>0.008126867241543047</v>
+        <v>0.008126867241542962</v>
       </c>
       <c r="X5" t="n">
-        <v>0.008126867241543047</v>
+        <v>0.008126867241542962</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.007984669482222409</v>
+        <v>0.007984669482222359</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.008126867241543016</v>
+        <v>0.00812686724154296</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.008126867241543047</v>
+        <v>0.008126867241542962</v>
       </c>
     </row>
     <row r="6">
@@ -10262,85 +10262,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01772184527163526</v>
+        <v>0.01160321242271019</v>
       </c>
       <c r="C6" t="n">
         <v>0.01772184527163526</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01160321242271017</v>
+        <v>0.01160321242271019</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01160321242271017</v>
+        <v>0.01772184527163526</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01160321242271017</v>
+        <v>0.01772184527163526</v>
       </c>
       <c r="G6" t="n">
+        <v>0.01160321242271019</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.01772184527163526</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.01160321242271017</v>
-      </c>
       <c r="I6" t="n">
-        <v>0.01160321242271017</v>
+        <v>0.01772184527163526</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01769894468219144</v>
+        <v>0.01158031183326634</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01160321242271017</v>
+        <v>0.01772184527163526</v>
       </c>
       <c r="L6" t="n">
+        <v>0.01160321242271019</v>
+      </c>
+      <c r="M6" t="n">
         <v>0.01772184527163526</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.01160321242271017</v>
-      </c>
       <c r="N6" t="n">
-        <v>0.0116147259526361</v>
+        <v>0.01161472595263596</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01772163405144324</v>
+        <v>0.01161472595263583</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01133136352686802</v>
+        <v>0.01133136352686766</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01160321242271017</v>
+        <v>0.01772184527163526</v>
       </c>
       <c r="R6" t="n">
         <v>0.01772184527163526</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01160321242271017</v>
+        <v>0.01160321242271019</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01160321242271017</v>
+        <v>0.01160321242271019</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01772184527163526</v>
+        <v>0.01160321242271019</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0175690672577824</v>
+        <v>0.01756906725778238</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01186398565454015</v>
+        <v>0.01186398565454008</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01772184527163526</v>
+        <v>0.01160321242271019</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01180920424064338</v>
+        <v>0.01180920424064349</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01160321242271017</v>
+        <v>0.01160321242271019</v>
       </c>
       <c r="AA6" t="n">
         <v>0.01772184527163526</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01257989912130464</v>
+        <v>0.01257989912130459</v>
       </c>
     </row>
     <row r="7">
@@ -10350,85 +10350,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01122251346465927</v>
+        <v>0.0112225134646593</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01124528388470558</v>
+        <v>0.01124528388470557</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01124528388470558</v>
+        <v>0.01124528388470557</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0112360228977681</v>
+        <v>0.01123602289776809</v>
       </c>
       <c r="V7" t="n">
         <v>0.01109263604025026</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01124541405410326</v>
+        <v>0.01124541405410315</v>
       </c>
     </row>
     <row r="8">
@@ -10438,70 +10438,70 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01898123187375246</v>
+        <v>0.01898123187375244</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.02680633583358072</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.02680633583358072</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.0226396988012057</v>
       </c>
       <c r="F8" t="n">
         <v>0.02020029161670819</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.02842892211541881</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.02680633583358072</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.02680633583358072</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0267834352441369</v>
+        <v>0.02678343524413689</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.02680633583358072</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.02680633583358072</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.02680633583357928</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02074057115319888</v>
+        <v>0.02074057115319894</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02240749595525206</v>
+        <v>0.02240749595525203</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02199889240774551</v>
+        <v>0.02199889240774555</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01744342034651102</v>
+        <v>0.01744342034651101</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.02680633583358072</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.02680633583358072</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.02680633583358072</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02198443515979105</v>
+        <v>0.02297982999342659</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02665355781972784</v>
+        <v>0.02450692285654798</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02680787369018734</v>
+        <v>0.02680787369018731</v>
       </c>
       <c r="X8" t="n">
         <v>0.01816060667281856</v>
@@ -10510,10 +10510,10 @@
         <v>0.03457438076671275</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.01883587655033014</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02680633583358076</v>
+        <v>0.02680633583358072</v>
       </c>
       <c r="AB8" t="n">
         <v>0.03498031124367166</v>
@@ -10526,85 +10526,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01959151898162191</v>
+        <v>0.01959151898162192</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02234117921260678</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.01492558291440209</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620131407286</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02314330163435628</v>
+        <v>0.02314330163435621</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02435084635840006</v>
+        <v>0.02435084635840004</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0246084863304552</v>
+        <v>0.02460848633045514</v>
       </c>
       <c r="Q9" t="n">
         <v>0.02316620131407286</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02301342420994719</v>
+        <v>0.02713852638825155</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02101098574076044</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02316620222380011</v>
+        <v>0.02316620222380006</v>
       </c>
     </row>
     <row r="10">
@@ -10617,79 +10617,79 @@
         <v>0.01074798314800825</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01066939994565124</v>
+        <v>0.01066939994565123</v>
       </c>
       <c r="D10" t="n">
         <v>0.01020736464364439</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02147921380840144</v>
+        <v>0.02147921380840138</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01054641521856084</v>
+        <v>0.01054641521856083</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005467001461636771</v>
+        <v>0.005467001461636842</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0105536589331111</v>
+        <v>0.01055365893311107</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01037568708566112</v>
+        <v>0.01037568708566116</v>
       </c>
       <c r="J10" t="n">
-        <v>0.008074250020545676</v>
+        <v>0.00807425002054568</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01001473465604226</v>
+        <v>0.01001473465604224</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008433681931961392</v>
+        <v>0.008433681931961402</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01029092042987906</v>
+        <v>0.01029092042987907</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01024978012876719</v>
+        <v>0.0102497801287672</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01024442957170967</v>
+        <v>0.01024442957170966</v>
       </c>
       <c r="P10" t="n">
-        <v>0.008137116228132672</v>
+        <v>0.008137116228132679</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01031786281827263</v>
+        <v>0.01031786281827264</v>
       </c>
       <c r="R10" t="n">
-        <v>0.009965648816026877</v>
+        <v>0.009965648816026868</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01000615561872901</v>
+        <v>0.01000615561872899</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01046440686287742</v>
+        <v>0.0104644068628774</v>
       </c>
       <c r="U10" t="n">
-        <v>0.009592594255620096</v>
+        <v>0.009592594255620097</v>
       </c>
       <c r="V10" t="n">
-        <v>0.005767395265935214</v>
+        <v>0.005767395265935212</v>
       </c>
       <c r="W10" t="n">
-        <v>0.009544439392155726</v>
+        <v>0.009544439392155721</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001089219430092407</v>
+        <v>0.001089219430092416</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.0004282562178761723</v>
+        <v>-0.0004282562178761905</v>
       </c>
       <c r="Z10" t="n">
         <v>0.0102506583835775</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.009732130079020827</v>
+        <v>0.009732130079020861</v>
       </c>
       <c r="AB10" t="n">
         <v>-0.05873326448403383</v>
@@ -10702,85 +10702,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01119631604682618</v>
+        <v>0.01119631604682619</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01073721855906799</v>
+        <v>0.01073721855906798</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01059543931448547</v>
+        <v>0.01059543931448545</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02159878106950507</v>
+        <v>0.02159878106950506</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01069728951288626</v>
+        <v>0.01069728951288623</v>
       </c>
       <c r="G11" t="n">
-        <v>0.009188678107382437</v>
+        <v>0.009188678107382442</v>
       </c>
       <c r="H11" t="n">
         <v>0.01110789790977344</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01102692015202114</v>
+        <v>0.01102692015202112</v>
       </c>
       <c r="J11" t="n">
-        <v>0.009965810657345113</v>
+        <v>0.009965810657345085</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01086469135215344</v>
+        <v>0.01086469135215339</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0101433016182845</v>
+        <v>0.01014330161828451</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01061964061381389</v>
+        <v>0.01061964061381386</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01060697253763274</v>
+        <v>0.01060697253763271</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01096719756488032</v>
+        <v>0.0109671975648803</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01000835393469209</v>
+        <v>0.01000835393469208</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01100060992608432</v>
+        <v>0.01100060992608434</v>
       </c>
       <c r="R11" t="n">
         <v>0.01083273532007951</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01085878215694005</v>
+        <v>0.01085878215694006</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01106728793338767</v>
+        <v>0.01106728793338765</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01066730470283337</v>
+        <v>0.01066730470283339</v>
       </c>
       <c r="V11" t="n">
-        <v>0.006046250980699812</v>
+        <v>0.00604625098069982</v>
       </c>
       <c r="W11" t="n">
         <v>0.01064869980244691</v>
       </c>
       <c r="X11" t="n">
-        <v>0.006755668603740871</v>
+        <v>0.006755668603740878</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.006111091518787191</v>
+        <v>0.006111091518787194</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01060671312435273</v>
+        <v>0.01060671312435275</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01073409966310526</v>
+        <v>0.01073409966310528</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.0204738059655155</v>
+        <v>-0.02047380596551551</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Hydrogen/hydrogen acidification results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen acidification results.xlsx
@@ -886,7 +886,7 @@
         <v>0.003723504305219684</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2519748288275949</v>
+        <v>0.003723504305219694</v>
       </c>
       <c r="O5" t="n">
         <v>0.003723504305219694</v>
@@ -974,7 +974,7 @@
         <v>0.01075255904187713</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2519748288275949</v>
+        <v>0.005750339994053984</v>
       </c>
       <c r="O6" t="n">
         <v>0.005750325200854549</v>
@@ -1062,7 +1062,7 @@
         <v>0.007995668386928979</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2519748288275949</v>
+        <v>0.007995668386928979</v>
       </c>
       <c r="O7" t="n">
         <v>0.007995515790551713</v>
@@ -1150,7 +1150,7 @@
         <v>0.02540667285182332</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2519748288275949</v>
+        <v>0.0185548387687453</v>
       </c>
       <c r="O8" t="n">
         <v>0.02043778226811623</v>
@@ -1238,7 +1238,7 @@
         <v>0.02314008326972366</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2519748288275949</v>
+        <v>0.02314008326972366</v>
       </c>
       <c r="O9" t="n">
         <v>0.02461072230172609</v>
@@ -1922,7 +1922,7 @@
         <v>0.003030374505058058</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02737777328690432</v>
+        <v>0.003030374505058056</v>
       </c>
       <c r="O5" t="n">
         <v>0.003030374505058056</v>
@@ -2010,7 +2010,7 @@
         <v>0.004370704649644389</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02737777328690432</v>
+        <v>0.004386288427522665</v>
       </c>
       <c r="O6" t="n">
         <v>0.008124742497337335</v>
@@ -2098,7 +2098,7 @@
         <v>0.006105136419134637</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02737777328690432</v>
+        <v>0.006105136419134637</v>
       </c>
       <c r="O7" t="n">
         <v>0.006105013351406312</v>
@@ -2186,7 +2186,7 @@
         <v>0.01960978346882849</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02737777328690432</v>
+        <v>0.01439729198010207</v>
       </c>
       <c r="O8" t="n">
         <v>0.01582972990059092</v>
@@ -2274,7 +2274,7 @@
         <v>0.01424738727196871</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02737777328690432</v>
+        <v>0.01424738727196871</v>
       </c>
       <c r="O9" t="n">
         <v>0.01510497638660558</v>
@@ -2958,7 +2958,7 @@
         <v>0.003444242847098548</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1448390780669714</v>
+        <v>0.003444242847098543</v>
       </c>
       <c r="O5" t="n">
         <v>0.003444242847098543</v>
@@ -3046,7 +3046,7 @@
         <v>0.009757312324226459</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1448390780669714</v>
+        <v>0.005178851872572794</v>
       </c>
       <c r="O6" t="n">
         <v>0.005176645790324175</v>
@@ -3134,7 +3134,7 @@
         <v>0.007291121158313947</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1448390780669714</v>
+        <v>0.007291121158313947</v>
       </c>
       <c r="O7" t="n">
         <v>0.007290983973799984</v>
@@ -3222,7 +3222,7 @@
         <v>0.02312523744663772</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1448390780669714</v>
+        <v>0.01691110226453266</v>
       </c>
       <c r="O8" t="n">
         <v>0.01861880056890381</v>
@@ -3310,7 +3310,7 @@
         <v>0.0195023138907069</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1448390780669714</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="O9" t="n">
         <v>0.02072355810705283</v>
@@ -3694,31 +3694,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01046348596572266</v>
+        <v>0.01046348596572265</v>
       </c>
       <c r="C2" t="n">
         <v>0.01012975614372371</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01093961182028163</v>
+        <v>0.01093961182028162</v>
       </c>
       <c r="E2" t="n">
         <v>0.02142392230109597</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01029177790292204</v>
+        <v>0.01029177790292203</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01035227397214875</v>
+        <v>0.01035227397214874</v>
       </c>
       <c r="H2" t="n">
         <v>0.01007412869534702</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01058345074263142</v>
+        <v>0.01058345074263141</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01063137982883028</v>
+        <v>0.01063137982883027</v>
       </c>
       <c r="K2" t="n">
         <v>0.01080980733578158</v>
@@ -3727,16 +3727,16 @@
         <v>0.01076281456794652</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01196864621456686</v>
+        <v>0.01196864621456685</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01034202740434238</v>
+        <v>0.01034202740434237</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0103188193705104</v>
+        <v>0.01031881937051039</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0103926277162322</v>
+        <v>0.01039262771623221</v>
       </c>
       <c r="Q2" t="n">
         <v>0.01024698741403173</v>
@@ -3745,16 +3745,16 @@
         <v>0.01008575064805617</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01058115305692438</v>
+        <v>0.01058115305692437</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01051795051146377</v>
+        <v>0.01051795051146375</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01125180955667678</v>
+        <v>0.01125180955667677</v>
       </c>
       <c r="V2" t="n">
-        <v>0.005813923443647972</v>
+        <v>0.005813923443647977</v>
       </c>
       <c r="W2" t="n">
         <v>0.01078260999980973</v>
@@ -3769,10 +3769,10 @@
         <v>0.01031923165284429</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01074081112590387</v>
+        <v>0.01074081112590386</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01190948062816549</v>
+        <v>0.0119094806281655</v>
       </c>
     </row>
     <row r="3">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01018597077875015</v>
+        <v>0.01018597077875013</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02150266393011303</v>
+        <v>0.02150266393011305</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01017739205441174</v>
+        <v>0.01017739205441173</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01009724942017344</v>
+        <v>0.01009724942017343</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01015879449046035</v>
+        <v>0.01015879449046034</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01017367130775534</v>
+        <v>0.01017367130775533</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01016927957164362</v>
+        <v>0.01016927957164361</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01015270059017977</v>
+        <v>0.01015270059017975</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01016209514803644</v>
+        <v>0.01016209514803643</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005663318783748419</v>
+        <v>0.005663318783748418</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01006930654141726</v>
+        <v>0.01006930654141725</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01017049113565281</v>
+        <v>0.0101704911356528</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01016929993331916</v>
+        <v>0.01016929993331915</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01004739447032873</v>
+        <v>0.01004739447032872</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1149562984835891</v>
+        <v>0.1149562984835897</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0341673987732391</v>
+        <v>0.03416739877323904</v>
       </c>
       <c r="D4" t="n">
         <v>0.2515203320477826</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06888823030954204</v>
+        <v>0.06888823030954178</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07928550157612431</v>
+        <v>0.07928550157612425</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1036193314441844</v>
+        <v>0.1036193314441846</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02526172914575143</v>
+        <v>0.02526172914575133</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1605212049577546</v>
+        <v>0.1605212049577543</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1667380120422189</v>
+        <v>0.1667380120422187</v>
       </c>
       <c r="K4" t="n">
         <v>0.1938401710388092</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1957653109942874</v>
+        <v>0.1957653109942844</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5298807234350473</v>
+        <v>0.5298807234350464</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09308692212854881</v>
+        <v>0.09308692212854872</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07736051629961171</v>
+        <v>0.0773605162996119</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09749402726002955</v>
+        <v>0.09749402726002947</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06746019009978046</v>
+        <v>0.06746019009978038</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03207582177940698</v>
+        <v>0.03207582177940697</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1429953375554889</v>
+        <v>0.1429953375554885</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1421739502524763</v>
+        <v>0.1421739502524765</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3107446022421185</v>
+        <v>0.3107446022421204</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06207319183566392</v>
+        <v>0.0620731918356642</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2032723684985449</v>
+        <v>0.2032723684985447</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6226325389774504</v>
+        <v>0.6226325389774514</v>
       </c>
       <c r="Y4" t="n">
         <v>0.6017970318466425</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.07708106187995217</v>
+        <v>0.07708106187995192</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1927602064757154</v>
+        <v>0.1927602064757153</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5688391613427366</v>
+        <v>0.5688391613427364</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00338625538480691</v>
+        <v>0.003386255384806895</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806885</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806885</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806885</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003386255384806912</v>
+        <v>0.003386255384806892</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806885</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806885</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806885</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003366558116905808</v>
+        <v>0.003366558116905788</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806885</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806889</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806885</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09308692212854881</v>
+        <v>0.003386255384806892</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003386255384806912</v>
+        <v>0.003386255384806892</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003386255384806912</v>
+        <v>0.003386255384806892</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003386255384806912</v>
+        <v>0.003386255384806892</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806885</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806885</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806885</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003276184064945314</v>
+        <v>0.003276184064945293</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003253964536109906</v>
+        <v>0.003253964536109902</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003386255384806912</v>
+        <v>0.003386255384806892</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00338625538480691</v>
+        <v>0.003386255384806895</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003276184064945314</v>
+        <v>0.003276184064945293</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806885</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003386255384806919</v>
+        <v>0.003386255384806885</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003386255384806912</v>
+        <v>0.003386255384806892</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009351882898752942</v>
+        <v>0.009351882898752906</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005044995312975351</v>
+        <v>0.005044995312975312</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009351882898752939</v>
+        <v>0.009351882898752906</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009351882898752939</v>
+        <v>0.009351882898752906</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005044995312975351</v>
+        <v>0.005044995312975312</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005044995312975351</v>
+        <v>0.005044995312975312</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005044995312975351</v>
+        <v>0.005044995312975312</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005044995312975351</v>
+        <v>0.005044995312975312</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009332185630851818</v>
+        <v>0.009332185630851808</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009351882898752939</v>
+        <v>0.009351882898752906</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009351882898752942</v>
+        <v>0.009351882898752906</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005044995312975351</v>
+        <v>0.005044995312975312</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09308692212854881</v>
+        <v>0.005078136281284118</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00935931846377192</v>
+        <v>0.009359318463771879</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009360859237021665</v>
+        <v>0.009360859237021627</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009351882898752939</v>
+        <v>0.009351882898752906</v>
       </c>
       <c r="R6" t="n">
-        <v>0.005044995312975351</v>
+        <v>0.005044995312975312</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009351882898752939</v>
+        <v>0.009351882898752906</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005044995312975351</v>
+        <v>0.005044995312975312</v>
       </c>
       <c r="U6" t="n">
-        <v>0.005044995312975351</v>
+        <v>0.005044995312975312</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009219592050055929</v>
+        <v>0.009219592050055923</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009359262297162668</v>
+        <v>0.00935926229716263</v>
       </c>
       <c r="X6" t="n">
-        <v>0.005044995312975351</v>
+        <v>0.005044995312975312</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.005179200488431772</v>
+        <v>0.005179200488431838</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.009351882898752939</v>
+        <v>0.009351882898752906</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009351882898752939</v>
+        <v>0.009351882898752906</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00541586401606256</v>
+        <v>0.005415864016062544</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006926334983164886</v>
+        <v>0.006926334983164881</v>
       </c>
       <c r="C7" t="n">
+        <v>0.006926334983164879</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.006926334983164879</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.006926334983164879</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.006926334983164879</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.006926334983164879</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.006926334983164879</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.006926334983164879</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.006906637715263775</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.006926334983164879</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.006926334983164881</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.006926334983164881</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.006926334983164881</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.006926334983164881</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.006926334983164881</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.006926334983164881</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.006926334983164881</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.006906637715263808</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.006926334983164881</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.006926334983164886</v>
-      </c>
       <c r="M7" t="n">
-        <v>0.006926334983164881</v>
+        <v>0.006926334983164879</v>
       </c>
       <c r="N7" t="n">
-        <v>0.09308692212854881</v>
+        <v>0.006926334983164879</v>
       </c>
       <c r="O7" t="n">
-        <v>0.006926207771547052</v>
+        <v>0.00692620777154703</v>
       </c>
       <c r="P7" t="n">
-        <v>0.006926207771547052</v>
+        <v>0.00692620777154703</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.006926334983164881</v>
+        <v>0.006926334983164879</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006926334983164881</v>
+        <v>0.006926334983164879</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006926334983164881</v>
+        <v>0.006926334983164879</v>
       </c>
       <c r="T7" t="n">
-        <v>0.006926334983164881</v>
+        <v>0.006926334983164879</v>
       </c>
       <c r="U7" t="n">
-        <v>0.006921814148923421</v>
+        <v>0.006921814148923403</v>
       </c>
       <c r="V7" t="n">
         <v>0.006794044134467894</v>
       </c>
       <c r="W7" t="n">
+        <v>0.006926334983164879</v>
+      </c>
+      <c r="X7" t="n">
         <v>0.006926334983164881</v>
       </c>
-      <c r="X7" t="n">
-        <v>0.006926334983164886</v>
-      </c>
       <c r="Y7" t="n">
-        <v>0.006926334983164881</v>
+        <v>0.006926334983164879</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.006926334983164881</v>
+        <v>0.006926334983164879</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.006926334983164881</v>
+        <v>0.006926334983164879</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.006926334983164881</v>
+        <v>0.006926334983164879</v>
       </c>
     </row>
     <row r="8">
@@ -4225,82 +4225,82 @@
         <v>0.01414577815023872</v>
       </c>
       <c r="C8" t="n">
+        <v>0.02153307679719699</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.02153307679719699</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.01759955817940131</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01529663294223687</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02306488129540674</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.02153307679719699</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.02153307679719699</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.02151337952929587</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.02153307679719699</v>
+      </c>
+      <c r="L8" t="n">
         <v>0.021533076797197</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.021533076797197</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.01759955817940134</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.01529663294223689</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.02306488129540676</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.021533076797197</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.021533076797197</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.0215133795292959</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.021533076797197</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.02153307679719702</v>
-      </c>
       <c r="M8" t="n">
-        <v>0.02153307679720003</v>
+        <v>0.02153307679720002</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09308692212854881</v>
+        <v>0.01580668447762681</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01738034680840983</v>
+        <v>0.0173803468084098</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01699460414612793</v>
+        <v>0.01699460414612789</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01269400535929423</v>
+        <v>0.0126940053592942</v>
       </c>
       <c r="R8" t="n">
-        <v>0.021533076797197</v>
+        <v>0.02153307679719699</v>
       </c>
       <c r="S8" t="n">
-        <v>0.021533076797197</v>
+        <v>0.02153307679719699</v>
       </c>
       <c r="T8" t="n">
-        <v>0.021533076797197</v>
+        <v>0.02153307679719699</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0179240299750279</v>
+        <v>0.01792402997502791</v>
       </c>
       <c r="V8" t="n">
         <v>0.01937797028137626</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0215345286129095</v>
+        <v>0.02153452861290946</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01337106595898788</v>
+        <v>0.01337106595898789</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02887227481780031</v>
+        <v>0.0288722748178003</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01400855528524301</v>
+        <v>0.014008555285243</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.021533076797197</v>
+        <v>0.02153307679719699</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.02924972794967963</v>
+        <v>0.02924972794967961</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01419403815848726</v>
+        <v>0.01419403815848721</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01667756318749958</v>
+        <v>0.01667756318749955</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009979710556796117</v>
+        <v>0.009979710556796086</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01742273272349906</v>
+        <v>0.01742273272349901</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01740303952158002</v>
+        <v>0.01740303952157999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0174227367894811</v>
+        <v>0.01742273678948106</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="N9" t="n">
-        <v>0.09308692212854881</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01849271787472937</v>
+        <v>0.01849271787472932</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01872542128726833</v>
+        <v>0.0187254212872683</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01742273272349906</v>
+        <v>0.01742273272349901</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="V9" t="n">
         <v>0.02101628250486132</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0174227367894811</v>
+        <v>0.01742273678948106</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01547611700751977</v>
+        <v>0.01547611700751972</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01742273678948111</v>
+        <v>0.01742273678948105</v>
       </c>
     </row>
     <row r="10">
@@ -4398,85 +4398,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00749706090764223</v>
+        <v>0.007497060907642205</v>
       </c>
       <c r="C10" t="n">
-        <v>0.009598436146090093</v>
+        <v>0.009598436146090095</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004749467075766091</v>
+        <v>0.004749467075766092</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01997782657194616</v>
+        <v>0.01997782657194618</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008603354343608621</v>
+        <v>0.008603354343608614</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007696269115602667</v>
+        <v>0.007696269115602652</v>
       </c>
       <c r="H10" t="n">
-        <v>0.009821499730608869</v>
+        <v>0.009821499730608868</v>
       </c>
       <c r="I10" t="n">
-        <v>0.006841952056390475</v>
+        <v>0.006841952056390466</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00646406044924961</v>
+        <v>0.006464060449249612</v>
       </c>
       <c r="K10" t="n">
-        <v>0.005530984060682631</v>
+        <v>0.00553098406068262</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005744315125394559</v>
+        <v>0.005744315125394576</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.001234651571252695</v>
+        <v>-0.001234651571252704</v>
       </c>
       <c r="N10" t="n">
-        <v>0.008241671258269943</v>
+        <v>0.008241671258269941</v>
       </c>
       <c r="O10" t="n">
-        <v>0.008355722683887118</v>
+        <v>0.008355722683887113</v>
       </c>
       <c r="P10" t="n">
-        <v>0.007914004160819917</v>
+        <v>0.007914004160819905</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.008803023913768046</v>
+        <v>0.008803023913768044</v>
       </c>
       <c r="R10" t="n">
-        <v>0.009647575245943524</v>
+        <v>0.009647575245943514</v>
       </c>
       <c r="S10" t="n">
-        <v>0.006807483669664057</v>
+        <v>0.006807483669664045</v>
       </c>
       <c r="T10" t="n">
-        <v>0.00722124153427395</v>
+        <v>0.007221241534273929</v>
       </c>
       <c r="U10" t="n">
-        <v>0.002799974665007623</v>
+        <v>0.002799974665007616</v>
       </c>
       <c r="V10" t="n">
-        <v>0.004263211414198549</v>
+        <v>0.004263211414198554</v>
       </c>
       <c r="W10" t="n">
-        <v>0.005634883353837631</v>
+        <v>0.005634883353837634</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.003839646851313141</v>
+        <v>-0.003839646851313132</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.003757519063880387</v>
+        <v>-0.003757519063880398</v>
       </c>
       <c r="Z10" t="n">
         <v>0.008364936787088098</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.005885074216238433</v>
+        <v>0.005885074216238431</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.00170332296888353</v>
+        <v>-0.001703322968883545</v>
       </c>
     </row>
     <row r="11">
@@ -4486,85 +4486,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.009247608693119178</v>
+        <v>0.009247608693119164</v>
       </c>
       <c r="C11" t="n">
         <v>0.009862426013501615</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008473570598112498</v>
+        <v>0.008473570598112495</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02073011644376166</v>
+        <v>0.02073011644376164</v>
       </c>
       <c r="F11" t="n">
-        <v>0.009575585728346058</v>
+        <v>0.009575585728346063</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00925982028209881</v>
+        <v>0.009259820282098808</v>
       </c>
       <c r="H11" t="n">
-        <v>0.009915878494740366</v>
+        <v>0.009915878494740359</v>
       </c>
       <c r="I11" t="n">
-        <v>0.009069496855000338</v>
+        <v>0.009069496855000334</v>
       </c>
       <c r="J11" t="n">
-        <v>0.008950264065660631</v>
+        <v>0.008950264065660629</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00869736984299709</v>
+        <v>0.008697369842997085</v>
       </c>
       <c r="L11" t="n">
-        <v>0.008749432378750952</v>
+        <v>0.008749432378750961</v>
       </c>
       <c r="M11" t="n">
-        <v>0.006779811937749547</v>
+        <v>0.006779811937749533</v>
       </c>
       <c r="N11" t="n">
-        <v>0.009464950214206878</v>
+        <v>0.009464950214206876</v>
       </c>
       <c r="O11" t="n">
-        <v>0.009493635942491054</v>
+        <v>0.009493635942491059</v>
       </c>
       <c r="P11" t="n">
-        <v>0.009366470217171135</v>
+        <v>0.00936647021717112</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.009625327471072646</v>
+        <v>0.009625327471072644</v>
       </c>
       <c r="R11" t="n">
-        <v>0.009855917006689712</v>
+        <v>0.009855917006689707</v>
       </c>
       <c r="S11" t="n">
-        <v>0.009051515943488554</v>
+        <v>0.009051515943488546</v>
       </c>
       <c r="T11" t="n">
-        <v>0.00917657454499351</v>
+        <v>0.009176574544993502</v>
       </c>
       <c r="U11" t="n">
-        <v>0.007902021275212749</v>
+        <v>0.007902021275212751</v>
       </c>
       <c r="V11" t="n">
-        <v>0.005176870128625336</v>
+        <v>0.005176870128625343</v>
       </c>
       <c r="W11" t="n">
-        <v>0.008719436005817396</v>
+        <v>0.008719436005817387</v>
       </c>
       <c r="X11" t="n">
-        <v>0.005966598718669375</v>
+        <v>0.005966598718669371</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.006041082448548693</v>
+        <v>0.006041082448548687</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.009497698670287049</v>
+        <v>0.009497698670287057</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.008791474771614873</v>
+        <v>0.008791474771614875</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.006562866746009351</v>
+        <v>0.006562866746009343</v>
       </c>
     </row>
   </sheetData>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01026736309855426</v>
+        <v>0.01026736309855428</v>
       </c>
       <c r="C2" t="n">
         <v>0.01000138413727671</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01053626646837026</v>
+        <v>0.01053626646837027</v>
       </c>
       <c r="E2" t="n">
         <v>0.02129933656951193</v>
@@ -4745,31 +4745,31 @@
         <v>0.01020509558885391</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01013227396496264</v>
+        <v>0.01013227396496266</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009947030605803679</v>
+        <v>0.009947030605803684</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01045385478521958</v>
+        <v>0.01045385478521959</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01049133477669533</v>
+        <v>0.01049133477669534</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01082519187853738</v>
+        <v>0.01082519187853739</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01051294790685415</v>
+        <v>0.01051294790685416</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01150110508138318</v>
+        <v>0.01150110508138319</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01010518006998835</v>
+        <v>0.01010518006998837</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0101114958528782</v>
+        <v>0.01011149585287821</v>
       </c>
       <c r="P2" t="n">
         <v>0.01020390403553276</v>
@@ -4781,34 +4781,34 @@
         <v>0.01003178036031496</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01042248108328778</v>
+        <v>0.01042248108328781</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01039033659801003</v>
+        <v>0.01039033659801004</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01121850867930343</v>
+        <v>0.01121850867930345</v>
       </c>
       <c r="V2" t="n">
-        <v>0.005807316123431555</v>
+        <v>0.005807316123431562</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01053095378989022</v>
+        <v>0.01053095378989023</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01269472520681778</v>
+        <v>0.01269472520681779</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01353400361040718</v>
+        <v>0.01353400361040719</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01015264502735759</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01066324734526306</v>
+        <v>0.01066324734526307</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01154956804724837</v>
+        <v>0.01154956804724839</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01005607144871741</v>
+        <v>0.01005607144871742</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02145325840055075</v>
+        <v>0.02145325840055079</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01005020554716604</v>
+        <v>0.01005020554716606</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00991765658421326</v>
+        <v>0.009917656584213275</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="J3" t="n">
         <v>0.01003675837790322</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01004506970124125</v>
+        <v>0.01004506970124126</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01003328981067384</v>
+        <v>0.01003328981067385</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0100074675506424</v>
+        <v>0.01000746755064241</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01003131878499244</v>
+        <v>0.01003131878499246</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005525831050974652</v>
+        <v>0.005525831050974638</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009993623823980812</v>
+        <v>0.009993623823980828</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01004063785137291</v>
+        <v>0.01004063785137292</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374859</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009917560310758146</v>
+        <v>0.009917560310758161</v>
       </c>
     </row>
     <row r="4">
@@ -4906,22 +4906,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0960318262207428</v>
+        <v>0.09603182622074355</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03393201881802666</v>
+        <v>0.03393201881802663</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1722300328143724</v>
+        <v>0.1722300328143727</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04767184423052997</v>
+        <v>0.04767184423053015</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08868979734562778</v>
+        <v>0.08868979734562751</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09010855219430489</v>
+        <v>0.0901085521943048</v>
       </c>
       <c r="H4" t="n">
         <v>0.02546020677239959</v>
@@ -4930,61 +4930,61 @@
         <v>0.1573612986117181</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1577979735494198</v>
+        <v>0.1577979735494195</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2271023823630317</v>
+        <v>0.2271023823630322</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1592291051435899</v>
+        <v>0.1592291051435903</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4205374595982415</v>
+        <v>0.4205374595982414</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0650803181152404</v>
+        <v>0.06508031811524044</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05965753131025072</v>
+        <v>0.05965753131025062</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08211453204884457</v>
+        <v>0.08211453204884425</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06692435774908435</v>
+        <v>0.0669243577490844</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05594426067299293</v>
+        <v>0.05594426067299296</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1339593479373902</v>
+        <v>0.1339593479373903</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1423943434698898</v>
+        <v>0.1423943434698901</v>
       </c>
       <c r="U4" t="n">
         <v>0.3218947528434749</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08998168245163368</v>
+        <v>0.0899816824516335</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1721364537659373</v>
+        <v>0.1721364537659371</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7222167367297717</v>
+        <v>0.72221673672977</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.9437740267302073</v>
+        <v>0.9437740267302087</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06547772748817113</v>
+        <v>0.06547772748817138</v>
       </c>
       <c r="AA4" t="n">
         <v>0.2066631989927945</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4966275754307907</v>
+        <v>0.4966275754307901</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003464457587922114</v>
+        <v>0.00346445758792216</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003464457587922108</v>
+        <v>0.003464457587922169</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003464457587922108</v>
+        <v>0.003464457587922169</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003464457587922108</v>
+        <v>0.003464457587922169</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003464457587922105</v>
+        <v>0.003464457587922134</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003464457587922108</v>
+        <v>0.003464457587922169</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003464457587922108</v>
+        <v>0.003464457587922169</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003464457587922108</v>
+        <v>0.003464457587922169</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003447318637625912</v>
+        <v>0.003447318637625938</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003464457587922108</v>
+        <v>0.003464457587922169</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003464457587922113</v>
+        <v>0.003464457587922171</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003464457587922108</v>
+        <v>0.003464457587922169</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0650803181152404</v>
+        <v>0.003464457587922134</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003464457587922105</v>
+        <v>0.003464457587922134</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003464457587922105</v>
+        <v>0.003464457587922134</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003464457587922105</v>
+        <v>0.003464457587922134</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003464457587922108</v>
+        <v>0.003464457587922169</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003464457587922108</v>
+        <v>0.003464457587922169</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003464457587922108</v>
+        <v>0.003464457587922169</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00338740289765026</v>
+        <v>0.003387402897650302</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003348788314781324</v>
+        <v>0.003348788314781307</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003464457587922105</v>
+        <v>0.003464457587922134</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003464457587922115</v>
+        <v>0.003464457587922135</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.00338740289765026</v>
+        <v>0.003387402897650302</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003464457587922108</v>
+        <v>0.003464457587922169</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003464457587922108</v>
+        <v>0.003464457587922169</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003464457587922105</v>
+        <v>0.003464457587922134</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.005185037514678422</v>
+        <v>0.005185037514678421</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005185037514678422</v>
+        <v>0.005185037514678421</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009352926936340277</v>
+        <v>0.009352926936340364</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009352926936340277</v>
+        <v>0.009352926936340364</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005185037514678422</v>
+        <v>0.005185037514678421</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005185037514678422</v>
+        <v>0.005185037514678421</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009352926936340277</v>
+        <v>0.009352926936340364</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005185037514678422</v>
+        <v>0.005185037514678421</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00933578798604408</v>
+        <v>0.009335787986044085</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009352926936340277</v>
+        <v>0.009352926936340364</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005185037514678422</v>
+        <v>0.005185037514678421</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005185037514678422</v>
+        <v>0.005185037514678421</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0650803181152404</v>
+        <v>0.005239154981346196</v>
       </c>
       <c r="O6" t="n">
-        <v>0.005426329684556244</v>
+        <v>0.005426329684556328</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009370896020403684</v>
+        <v>0.009370896020403734</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009352926936340277</v>
+        <v>0.009352926936340364</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009352926936340277</v>
+        <v>0.009352926936340364</v>
       </c>
       <c r="S6" t="n">
-        <v>0.005185037514678422</v>
+        <v>0.005185037514678421</v>
       </c>
       <c r="T6" t="n">
-        <v>0.009352926936340277</v>
+        <v>0.009352926936340364</v>
       </c>
       <c r="U6" t="n">
-        <v>0.009352926936340277</v>
+        <v>0.009352926936340364</v>
       </c>
       <c r="V6" t="n">
-        <v>0.005069368241537632</v>
+        <v>0.00506936824153758</v>
       </c>
       <c r="W6" t="n">
-        <v>0.005359444533663477</v>
+        <v>0.005359444533663495</v>
       </c>
       <c r="X6" t="n">
-        <v>0.005185037514678422</v>
+        <v>0.005185037514678421</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.005369640155960628</v>
+        <v>0.005369640155960572</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.005185037514678422</v>
+        <v>0.005185037514678421</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009352926936340277</v>
+        <v>0.009352926936340364</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.005317614386654432</v>
+        <v>0.005317614386654486</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006990048744146004</v>
+        <v>0.006990048744146034</v>
       </c>
       <c r="C7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="F7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006972909793849791</v>
+        <v>0.006972909793849812</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006990048744146004</v>
+        <v>0.006990048744146034</v>
       </c>
       <c r="M7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0650803181152404</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="O7" t="n">
-        <v>0.006989920148308315</v>
+        <v>0.006989920148308346</v>
       </c>
       <c r="P7" t="n">
-        <v>0.006989920148308315</v>
+        <v>0.006989920148308346</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="T7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00698430607334391</v>
+        <v>0.006984306073343906</v>
       </c>
       <c r="V7" t="n">
-        <v>0.006874379471005217</v>
+        <v>0.006874379471005176</v>
       </c>
       <c r="W7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="X7" t="n">
-        <v>0.006990048744146004</v>
+        <v>0.006990048744146034</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.006990048744145994</v>
+        <v>0.006990048744146032</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01417361488332086</v>
+        <v>0.01417361488332084</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02152061255821751</v>
+        <v>0.0215206125582175</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02152061255821751</v>
+        <v>0.0215206125582175</v>
       </c>
       <c r="E8" t="n">
         <v>0.01760855301923131</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01531819125488362</v>
+        <v>0.01531819125488361</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02304406038733611</v>
+        <v>0.02304406038733609</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02152061255821751</v>
+        <v>0.0215206125582175</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02152061255821751</v>
+        <v>0.0215206125582175</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02150347360792127</v>
+        <v>0.02150347360792126</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02152061255821751</v>
+        <v>0.0215206125582175</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02152061255821752</v>
+        <v>0.0215206125582175</v>
       </c>
       <c r="M8" t="n">
         <v>0.02152061255822166</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0650803181152404</v>
+        <v>0.01582546023421085</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01739053754298154</v>
+        <v>0.01739053754298153</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01700689927703531</v>
+        <v>0.01700689927703532</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01272976215319931</v>
+        <v>0.01272976215319934</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02152061255821751</v>
+        <v>0.0215206125582175</v>
       </c>
       <c r="S8" t="n">
-        <v>0.02152061255821751</v>
+        <v>0.0215206125582175</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02152061255821751</v>
+        <v>0.0215206125582175</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01793029028204125</v>
+        <v>0.01793029028204124</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01939209926885993</v>
+        <v>0.01939209926885992</v>
       </c>
       <c r="W8" t="n">
         <v>0.02152205645367457</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01340312908875069</v>
+        <v>0.01340312908875071</v>
       </c>
       <c r="Y8" t="n">
         <v>0.02881812221576317</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01403714062956745</v>
+        <v>0.01403714062956748</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02152061255821751</v>
+        <v>0.0215206125582175</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0291951659755093</v>
+        <v>0.02919516597550927</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01371836784674291</v>
+        <v>0.01371836784674292</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01608129046752174</v>
+        <v>0.01608129046752177</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009708692121683321</v>
+        <v>0.009708692121683361</v>
       </c>
       <c r="G9" t="n">
         <v>0.01679027384089595</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01677313825663044</v>
+        <v>0.01677313825663042</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01679027720692662</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0650803181152404</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01780829946504077</v>
+        <v>0.01780829946504078</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01802970257191397</v>
+        <v>0.01802970257191398</v>
       </c>
       <c r="Q9" t="n">
         <v>0.01679027384089595</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02021951544886916</v>
+        <v>0.02021951544886909</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01679027720692662</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01493818769096077</v>
+        <v>0.01493818769096078</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01679027720692663</v>
+        <v>0.01679027720692668</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.007775256639975082</v>
+        <v>0.007775256639975099</v>
       </c>
       <c r="C10" t="n">
-        <v>0.009473084596515767</v>
+        <v>0.009473084596515777</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006235189377331718</v>
+        <v>0.006235189377331762</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02037896896949631</v>
+        <v>0.02037896896949635</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008252131315130577</v>
+        <v>0.008252131315130605</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007796086612435442</v>
+        <v>0.00779608661243546</v>
       </c>
       <c r="H10" t="n">
-        <v>0.009689112179972042</v>
+        <v>0.009689112179972051</v>
       </c>
       <c r="I10" t="n">
-        <v>0.006724156041737305</v>
+        <v>0.006724156041737311</v>
       </c>
       <c r="J10" t="n">
-        <v>0.006463877219091264</v>
+        <v>0.006463877219091286</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00457063538746995</v>
+        <v>0.004570635387469955</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006337674778730565</v>
+        <v>0.006337674778730575</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0006195415343434708</v>
+        <v>0.000619541534343494</v>
       </c>
       <c r="N10" t="n">
-        <v>0.008754835125610632</v>
+        <v>0.008754835125610639</v>
       </c>
       <c r="O10" t="n">
-        <v>0.008701069912377091</v>
+        <v>0.008701069912377107</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0081092142201171</v>
+        <v>0.008109214220117112</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.008655089388701329</v>
+        <v>0.008655089388701334</v>
       </c>
       <c r="R10" t="n">
-        <v>0.008991019210980021</v>
+        <v>0.008991019210980031</v>
       </c>
       <c r="S10" t="n">
-        <v>0.006862305599787844</v>
+        <v>0.006862305599787865</v>
       </c>
       <c r="T10" t="n">
-        <v>0.00709185794996943</v>
+        <v>0.007091857949969443</v>
       </c>
       <c r="U10" t="n">
-        <v>0.002106438660476227</v>
+        <v>0.002106438660476234</v>
       </c>
       <c r="V10" t="n">
-        <v>0.003364525699190955</v>
+        <v>0.003364525699190938</v>
       </c>
       <c r="W10" t="n">
-        <v>0.006237598192362204</v>
+        <v>0.006237598192362219</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.006715345672157443</v>
+        <v>-0.006715345672157422</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.01145154922316737</v>
+        <v>-0.01145154922316734</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.008467035882330706</v>
+        <v>0.008467035882330715</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.005460539550257357</v>
+        <v>0.005460539550257363</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.0004723206012035416</v>
+        <v>-0.000472320601203528</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.009237140727080933</v>
+        <v>0.009237140727080945</v>
       </c>
       <c r="C11" t="n">
-        <v>0.009736123261656097</v>
+        <v>0.009736123261656102</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008805308584491052</v>
+        <v>0.008805308584491073</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02081053145482483</v>
+        <v>0.02081053145482487</v>
       </c>
       <c r="F11" t="n">
-        <v>0.009386966083155182</v>
+        <v>0.00938696608315521</v>
       </c>
       <c r="G11" t="n">
-        <v>0.009166952866761415</v>
+        <v>0.009166952866761427</v>
       </c>
       <c r="H11" t="n">
-        <v>0.009787618604124677</v>
+        <v>0.009787618604124694</v>
       </c>
       <c r="I11" t="n">
-        <v>0.008945378291889213</v>
+        <v>0.008945378291889223</v>
       </c>
       <c r="J11" t="n">
-        <v>0.008865662463339218</v>
+        <v>0.008865662463339223</v>
       </c>
       <c r="K11" t="n">
-        <v>0.008334306819784415</v>
+        <v>0.008334306819784428</v>
       </c>
       <c r="L11" t="n">
         <v>0.008828621207213021</v>
       </c>
       <c r="M11" t="n">
-        <v>0.007215009532936468</v>
+        <v>0.007215009532936488</v>
       </c>
       <c r="N11" t="n">
-        <v>0.009520669031210622</v>
+        <v>0.009520669031210635</v>
       </c>
       <c r="O11" t="n">
-        <v>0.009502521470739645</v>
+        <v>0.009502521470739657</v>
       </c>
       <c r="P11" t="n">
-        <v>0.009328443510164357</v>
+        <v>0.009328443510164363</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.009492637036387001</v>
+        <v>0.009492637036387008</v>
       </c>
       <c r="R11" t="n">
-        <v>0.009569293126539919</v>
+        <v>0.009569293126539936</v>
       </c>
       <c r="S11" t="n">
-        <v>0.008976863079126957</v>
+        <v>0.008976863079126981</v>
       </c>
       <c r="T11" t="n">
-        <v>0.009049165644721743</v>
+        <v>0.009049165644721757</v>
       </c>
       <c r="U11" t="n">
-        <v>0.007612662967554082</v>
+        <v>0.007612662967554092</v>
       </c>
       <c r="V11" t="n">
-        <v>0.004823915300698483</v>
+        <v>0.004823915300698492</v>
       </c>
       <c r="W11" t="n">
-        <v>0.008801091924526329</v>
+        <v>0.008801091924526326</v>
       </c>
       <c r="X11" t="n">
-        <v>0.00509209083774854</v>
+        <v>0.005092090837748564</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.003755523299009285</v>
+        <v>0.003755523299009297</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.009436651116671465</v>
+        <v>0.009436651116671474</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.008579821321402489</v>
+        <v>0.008579821321402498</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.00682213912171993</v>
+        <v>0.006822139121719951</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>0.003148983555137642</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08957227574141909</v>
+        <v>0.003148983555137649</v>
       </c>
       <c r="O5" t="n">
         <v>0.003148983555137649</v>
@@ -6154,7 +6154,7 @@
         <v>0.008870724624968285</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08957227574141909</v>
+        <v>0.004609730238361637</v>
       </c>
       <c r="O6" t="n">
         <v>0.008891404643734632</v>
@@ -6242,7 +6242,7 @@
         <v>0.006579123543078457</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08957227574141909</v>
+        <v>0.006579123543078457</v>
       </c>
       <c r="O7" t="n">
         <v>0.006578993474745366</v>
@@ -6330,7 +6330,7 @@
         <v>0.02147544085445641</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08957227574141909</v>
+        <v>0.01570690530461501</v>
       </c>
       <c r="O8" t="n">
         <v>0.01729214896106791</v>
@@ -6418,7 +6418,7 @@
         <v>0.0169078441044159</v>
       </c>
       <c r="N9" t="n">
-        <v>0.08957227574141909</v>
+        <v>0.0169078441044159</v>
       </c>
       <c r="O9" t="n">
         <v>0.01795504579843846</v>
@@ -6814,7 +6814,7 @@
         <v>0.02095045486571361</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009608218426430896</v>
+        <v>0.009608218426430894</v>
       </c>
       <c r="G2" t="n">
         <v>0.009528378464857164</v>
@@ -6832,7 +6832,7 @@
         <v>0.009601423988974409</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009609579324191642</v>
+        <v>0.009609579324191641</v>
       </c>
       <c r="M2" t="n">
         <v>0.009576997175997722</v>
@@ -6880,7 +6880,7 @@
         <v>0.009701542471969818</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.009433492057884834</v>
+        <v>0.009433492057884832</v>
       </c>
     </row>
     <row r="3">
@@ -7102,7 +7102,7 @@
         <v>0.003016784184813798</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03012752360198173</v>
+        <v>0.003016784184813789</v>
       </c>
       <c r="O5" t="n">
         <v>0.003016784184813789</v>
@@ -7190,7 +7190,7 @@
         <v>0.008117898266018114</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03012752360198173</v>
+        <v>0.004348146288798461</v>
       </c>
       <c r="O6" t="n">
         <v>0.008124501691893308</v>
@@ -7217,7 +7217,7 @@
         <v>0.004219768769746335</v>
       </c>
       <c r="W6" t="n">
-        <v>0.004459832634878212</v>
+        <v>0.004459832634878211</v>
       </c>
       <c r="X6" t="n">
         <v>0.008117898266018114</v>
@@ -7278,7 +7278,7 @@
         <v>0.006068740433879374</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03012752360198173</v>
+        <v>0.006068740433879374</v>
       </c>
       <c r="O7" t="n">
         <v>0.00606861790874035</v>
@@ -7366,7 +7366,7 @@
         <v>0.01952173178476805</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03012752360198173</v>
+        <v>0.01433375943078584</v>
       </c>
       <c r="O8" t="n">
         <v>0.01575945928015846</v>
@@ -7454,7 +7454,7 @@
         <v>0.01466742257144326</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03012752360198173</v>
+        <v>0.01466742257144326</v>
       </c>
       <c r="O9" t="n">
         <v>0.01555564491646764</v>
@@ -7512,7 +7512,7 @@
         <v>0.009335211028259526</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00905882701933089</v>
+        <v>0.009058827019330891</v>
       </c>
       <c r="E10" t="n">
         <v>0.02066932616209725</v>
@@ -7521,7 +7521,7 @@
         <v>0.009206258523524509</v>
       </c>
       <c r="G10" t="n">
-        <v>0.009155705235895685</v>
+        <v>0.009155705235895683</v>
       </c>
       <c r="H10" t="n">
         <v>0.009171587578271634</v>
@@ -7654,7 +7654,7 @@
         <v>0.009425989542450152</v>
       </c>
       <c r="V11" t="n">
-        <v>0.004967233693771163</v>
+        <v>0.004967233693771162</v>
       </c>
       <c r="W11" t="n">
         <v>0.009230509587288684</v>
@@ -8050,7 +8050,7 @@
         <v>0.02313628396317434</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02479861528802854</v>
+        <v>0.02479861528802855</v>
       </c>
       <c r="O4" t="n">
         <v>0.0374670832432918</v>
@@ -8138,7 +8138,7 @@
         <v>0.003018753949256941</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02479861528802855</v>
+        <v>0.003018753949256947</v>
       </c>
       <c r="O5" t="n">
         <v>0.003018753949256947</v>
@@ -8226,7 +8226,7 @@
         <v>0.008065436242657516</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02479861528802854</v>
+        <v>0.004367250128469655</v>
       </c>
       <c r="O6" t="n">
         <v>0.004554743052177459</v>
@@ -8314,7 +8314,7 @@
         <v>0.006059754348790034</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02479861528802854</v>
+        <v>0.006059754348790034</v>
       </c>
       <c r="O7" t="n">
         <v>0.006059630836006172</v>
@@ -8402,7 +8402,7 @@
         <v>0.01947590924513306</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02479861528802854</v>
+        <v>0.01430471759718227</v>
       </c>
       <c r="O8" t="n">
         <v>0.01572580596287081</v>
@@ -8490,7 +8490,7 @@
         <v>0.01415966695540629</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02479861528802854</v>
+        <v>0.01415966695540629</v>
       </c>
       <c r="O9" t="n">
         <v>0.01501072448401596</v>
@@ -9174,7 +9174,7 @@
         <v>0.003359819143766252</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1631566420862821</v>
+        <v>0.003359819143766255</v>
       </c>
       <c r="O5" t="n">
         <v>0.003359819143766255</v>
@@ -9262,7 +9262,7 @@
         <v>0.00495437850281695</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1631566420862821</v>
+        <v>0.004981447452015018</v>
       </c>
       <c r="O6" t="n">
         <v>0.009512388374831168</v>
@@ -9350,7 +9350,7 @@
         <v>0.007090466475653488</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1631566420862821</v>
+        <v>0.007090466475653488</v>
       </c>
       <c r="O7" t="n">
         <v>0.007090332057791348</v>
@@ -9438,7 +9438,7 @@
         <v>0.0226714308886099</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1631566420862821</v>
+        <v>0.016578044973127</v>
       </c>
       <c r="O8" t="n">
         <v>0.01825256033059976</v>
@@ -9526,7 +9526,7 @@
         <v>0.01891121263363821</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1631566420862821</v>
+        <v>0.01891121263363821</v>
       </c>
       <c r="O9" t="n">
         <v>0.02009381485013472</v>
@@ -10210,7 +10210,7 @@
         <v>0.003183521491757861</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03586611091647047</v>
+        <v>0.00318352149175786</v>
       </c>
       <c r="O5" t="n">
         <v>0.00318352149175786</v>
@@ -10298,7 +10298,7 @@
         <v>0.004529420477710383</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03586611091647047</v>
+        <v>0.004546276969716057</v>
       </c>
       <c r="O6" t="n">
         <v>0.009530618149371133</v>
@@ -10386,7 +10386,7 @@
         <v>0.006414579007075296</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03586611091647047</v>
+        <v>0.006414579007075296</v>
       </c>
       <c r="O7" t="n">
         <v>0.006414456418827572</v>
@@ -10474,7 +10474,7 @@
         <v>0.02049753804691136</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03586611091647047</v>
+        <v>0.01504438532457647</v>
       </c>
       <c r="O8" t="n">
         <v>0.01654295904160374</v>
@@ -10562,7 +10562,7 @@
         <v>0.01593505232748493</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03586611091647047</v>
+        <v>0.01593505232748493</v>
       </c>
       <c r="O9" t="n">
         <v>0.01690743698209092</v>

--- a/Results/Phase 2/Hydrogen/hydrogen acidification results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen acidification results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01095027868405264</v>
+        <v>0.01095027868405262</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01037632639009646</v>
+        <v>0.01037632639009645</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01100441258264226</v>
+        <v>0.01100441258264225</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02155950517545155</v>
+        <v>0.02155950517545158</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01068074794309478</v>
+        <v>0.01068074794309476</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01068613529095364</v>
+        <v>0.01068613529095363</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01074349069397232</v>
+        <v>0.01074349069397235</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01100282896956648</v>
+        <v>0.01100282896956647</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01088527771352587</v>
+        <v>0.01088527771352586</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01137561127602656</v>
+        <v>0.01137561127602654</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01119183182925337</v>
+        <v>0.01119183182925335</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01267803371568261</v>
+        <v>0.0126780337156826</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01104728711267479</v>
+        <v>0.01104728711267476</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01075235213592654</v>
+        <v>0.01075235213592651</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01060299756691752</v>
+        <v>0.01060299756691751</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01063036597142735</v>
+        <v>0.01063036597142733</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0106439533831572</v>
+        <v>0.01064395338315718</v>
       </c>
       <c r="S2" t="n">
         <v>0.01086300161985298</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01099562990898043</v>
+        <v>0.01099562990898041</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01179632885168493</v>
+        <v>0.01179632885168492</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0061737895554463</v>
+        <v>0.006173789555446295</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01116322605324506</v>
+        <v>0.01116322605324504</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0112427553236637</v>
+        <v>0.01124275532366367</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01158330183643124</v>
+        <v>0.01158330183643123</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01060450225851545</v>
+        <v>0.01060450225851542</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01117731397543695</v>
+        <v>0.01117731397543693</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01245688917039048</v>
+        <v>0.01245688917039046</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02160479214511261</v>
+        <v>0.02160479214511263</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01037444052135853</v>
+        <v>0.01037444052135851</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005959881941896677</v>
+        <v>0.005959881941896675</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01038459169849191</v>
+        <v>0.01038459169849188</v>
       </c>
     </row>
     <row r="4">
@@ -762,25 +762,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2039909728424263</v>
+        <v>0.2039909728424261</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0542905087334974</v>
+        <v>0.05429050873349742</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2459335048038666</v>
+        <v>0.245933504803867</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08850534362201898</v>
+        <v>0.08850534362201881</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1504928642814289</v>
+        <v>0.1504928642814287</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1365007268210827</v>
+        <v>0.1365007268210826</v>
       </c>
       <c r="H4" t="n">
-        <v>0.172952355510373</v>
+        <v>0.1729523555103729</v>
       </c>
       <c r="I4" t="n">
         <v>0.2480566028373535</v>
@@ -789,58 +789,58 @@
         <v>0.2033108497892381</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3562315114061286</v>
+        <v>0.3562315114061281</v>
       </c>
       <c r="L4" t="n">
-        <v>0.287775411001165</v>
+        <v>0.2877754110011633</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7621453115718384</v>
+        <v>0.7621453115718392</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2519748288275949</v>
+        <v>0.2519748288275951</v>
       </c>
       <c r="O4" t="n">
         <v>0.1476739019459354</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1123201515702128</v>
+        <v>0.1123201515702126</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1295778131557528</v>
+        <v>0.1295778131557525</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1393000323142809</v>
+        <v>0.1393000323142806</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1857995467229781</v>
+        <v>0.1857995467229779</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2441402217161403</v>
+        <v>0.2441402217161409</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4533127381887138</v>
+        <v>0.4533127381887136</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09172243266326817</v>
+        <v>0.09172243266326793</v>
       </c>
       <c r="W4" t="n">
-        <v>0.281554273624213</v>
+        <v>0.2815542736242125</v>
       </c>
       <c r="X4" t="n">
-        <v>0.314239213737636</v>
+        <v>0.3142392137376358</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4033346327404157</v>
+        <v>0.4033346327404161</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1138153762547575</v>
+        <v>0.1138153762547576</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2875139151208691</v>
+        <v>0.2875139151208687</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.720195190647678</v>
+        <v>0.7201951906476777</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01656750469390054</v>
+        <v>0.01656750469390056</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02540667285182338</v>
+        <v>0.02540667285182329</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02540667285182338</v>
+        <v>0.02540667285182329</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0207000765469402</v>
+        <v>0.02070007654694026</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01794454378733446</v>
+        <v>0.01794454378733445</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0272395319511732</v>
+        <v>0.02723953195117318</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02540667285182338</v>
+        <v>0.02540667285182329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02540667285182338</v>
+        <v>0.02540667285182329</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02538939161708048</v>
+        <v>0.02538939161708045</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02540667285182338</v>
+        <v>0.02540667285182329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02540667285182338</v>
+        <v>0.02540667285182329</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02540667285182333</v>
+        <v>0.02540667285182324</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2519748288275949</v>
+        <v>0.01855483876874524</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02043778226811622</v>
+        <v>0.02043778226811621</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01997622731814017</v>
+        <v>0.01997622731814022</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0148304064067872</v>
+        <v>0.01483040640678713</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02540667285182338</v>
+        <v>0.02540667285182329</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02540667285182338</v>
+        <v>0.02540667285182329</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02540667285182338</v>
+        <v>0.02540667285182329</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02109109861360221</v>
+        <v>0.02109109861360219</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02287337791807178</v>
+        <v>0.02287337791807177</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02540841000135787</v>
+        <v>0.02540841000135786</v>
       </c>
       <c r="X5" t="n">
         <v>0.01564053373198018</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03419304249876255</v>
+        <v>0.0341930424987625</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01640331260736123</v>
+        <v>0.01640331260736127</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02540667285182338</v>
+        <v>0.02540667285182329</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.034639923111721</v>
+        <v>0.03463992311172098</v>
       </c>
     </row>
     <row r="6">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01870238560017698</v>
+        <v>0.01870238560017699</v>
       </c>
       <c r="C6" t="n">
         <v>0.0231400832697237</v>
@@ -947,13 +947,13 @@
         <v>0.0231400832697237</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02211587603136394</v>
+        <v>0.02211587603136385</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01290998698361039</v>
+        <v>0.01290998698361035</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02314007713706324</v>
+        <v>0.0231400771370632</v>
       </c>
       <c r="H6" t="n">
         <v>0.0231400832697237</v>
@@ -962,7 +962,7 @@
         <v>0.0231400832697237</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02312280203498082</v>
+        <v>0.02312280203498075</v>
       </c>
       <c r="K6" t="n">
         <v>0.0231400832697237</v>
@@ -974,16 +974,16 @@
         <v>0.0231400832697237</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2519748288275949</v>
+        <v>0.0231400832697237</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02461072230172612</v>
+        <v>0.02461072230172607</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0249305623930186</v>
+        <v>0.02493056239301852</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02314007713706324</v>
+        <v>0.0231400771370632</v>
       </c>
       <c r="R6" t="n">
         <v>0.0231400832697237</v>
@@ -998,7 +998,7 @@
         <v>0.0231400832697237</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02814508375935335</v>
+        <v>0.02814508375935333</v>
       </c>
       <c r="W6" t="n">
         <v>0.0231400832697237</v>
@@ -1010,7 +1010,7 @@
         <v>0.0231400832697237</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02046454375524904</v>
+        <v>0.02046454375524899</v>
       </c>
       <c r="AA6" t="n">
         <v>0.0231400832697237</v>
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006087086026286977</v>
+        <v>0.006087086026286975</v>
       </c>
       <c r="C7" t="n">
         <v>0.009514378410942567</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005836363529611796</v>
+        <v>0.005836363529611776</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01988203090706976</v>
+        <v>0.01988203090706975</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007745236984427338</v>
+        <v>0.007745236984427314</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007660043162694338</v>
+        <v>0.007660043162694313</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007385164466574858</v>
+        <v>0.00738516446657481</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005854156672266411</v>
+        <v>0.005854156672266375</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006437518469164781</v>
+        <v>0.006437518469164757</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003652509762337954</v>
+        <v>0.003652509762337926</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004686100643107162</v>
+        <v>0.004686100643107191</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.003912420383674189</v>
+        <v>-0.00391242038367422</v>
       </c>
       <c r="N7" t="n">
-        <v>0.005564874115628643</v>
+        <v>0.005564874115628618</v>
       </c>
       <c r="O7" t="n">
-        <v>0.007261175442408921</v>
+        <v>0.007261175442408907</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008148685585924367</v>
+        <v>0.008148685585924336</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008021297302397113</v>
+        <v>0.008021297302397095</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007957410067287028</v>
+        <v>0.007957410067287016</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006618011523097291</v>
+        <v>0.00661801152309729</v>
       </c>
       <c r="T7" t="n">
-        <v>0.005890670679935407</v>
+        <v>0.005890670679935389</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001103144091508333</v>
+        <v>0.001103144091508305</v>
       </c>
       <c r="V7" t="n">
         <v>0.00416693226394912</v>
       </c>
       <c r="W7" t="n">
-        <v>0.004864456904062689</v>
+        <v>0.004864456904062672</v>
       </c>
       <c r="X7" t="n">
-        <v>0.004434532443206825</v>
+        <v>0.004434532443206821</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002398115561277951</v>
+        <v>0.002398115561277922</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008146664481293354</v>
+        <v>0.008146664481293359</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.004785874713054616</v>
+        <v>0.004785874713054599</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.002668582930858964</v>
+        <v>-0.00266858293085898</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008994899907861405</v>
+        <v>0.008994899907861394</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009980376571056304</v>
+        <v>0.00998037657105628</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008934954271458653</v>
+        <v>0.008934954271458606</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02077564332202774</v>
+        <v>0.0207756433220277</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009479833137070999</v>
+        <v>0.009479833137070964</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009446457024544738</v>
+        <v>0.009446457024544724</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009378741744842637</v>
+        <v>0.009378741744842628</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008941466594994093</v>
+        <v>0.008941466594994106</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009093965633551556</v>
+        <v>0.009093965633551507</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008312492541204319</v>
+        <v>0.008312492541204293</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008599000239039827</v>
+        <v>0.008599000239039837</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006172847656422891</v>
+        <v>0.006172847656422867</v>
       </c>
       <c r="N8" t="n">
-        <v>0.008854300252943412</v>
+        <v>0.008854300252943377</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009331187785671758</v>
+        <v>0.009331187785671718</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009585653160289287</v>
+        <v>0.009585653160289283</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009555059489831841</v>
+        <v>0.009555059489831829</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009539578005990057</v>
+        <v>0.009539578005990028</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009149195636669622</v>
+        <v>0.00914919563666961</v>
       </c>
       <c r="T8" t="n">
-        <v>0.008950881524260676</v>
+        <v>0.008950881524260663</v>
       </c>
       <c r="U8" t="n">
-        <v>0.007573240612288866</v>
+        <v>0.007573240612288823</v>
       </c>
       <c r="V8" t="n">
-        <v>0.005357991738188555</v>
+        <v>0.005357991738188551</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008651547130153968</v>
+        <v>0.008651547130153942</v>
       </c>
       <c r="X8" t="n">
-        <v>0.008535459400795224</v>
+        <v>0.008535459400795226</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.007949429742609567</v>
+        <v>0.00794942974260953</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009586238242839225</v>
+        <v>0.009586238242839181</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.008629879905010603</v>
+        <v>0.008629879905010582</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.006517653116036456</v>
+        <v>0.00651765311603644</v>
       </c>
     </row>
   </sheetData>
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.009441423349158925</v>
+        <v>0.009441423349158928</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009470510973130373</v>
+        <v>0.009470510973130364</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009468547657756133</v>
+        <v>0.009468547657756137</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02090335225754549</v>
+        <v>0.02090335225754546</v>
       </c>
       <c r="F2" t="n">
         <v>0.009494767709417777</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009383395105526405</v>
+        <v>0.009383395105526403</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009477384021497431</v>
+        <v>0.009477384021497422</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009478788917387217</v>
+        <v>0.009478788917387211</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009528536341996754</v>
+        <v>0.009528536341996746</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009521714694508016</v>
+        <v>0.009521714694508009</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009534578540206092</v>
+        <v>0.009534578540206088</v>
       </c>
       <c r="M2" t="n">
         <v>0.009501355495453027</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00948847083638305</v>
+        <v>0.009488470836383043</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009500671611027333</v>
+        <v>0.009500671611027326</v>
       </c>
       <c r="P2" t="n">
-        <v>0.009495920940305085</v>
+        <v>0.009495920940305075</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.009464584066991225</v>
+        <v>0.009464584066991218</v>
       </c>
       <c r="R2" t="n">
-        <v>0.009514359475972603</v>
+        <v>0.009514359475972588</v>
       </c>
       <c r="S2" t="n">
-        <v>0.009517329065328739</v>
+        <v>0.009517329065328737</v>
       </c>
       <c r="T2" t="n">
         <v>0.009478110828524074</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009561037777428961</v>
+        <v>0.009561037777428949</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00503403708787466</v>
+        <v>0.005034037087874641</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009547976876413105</v>
+        <v>0.009547976876413107</v>
       </c>
       <c r="X2" t="n">
         <v>0.01120157690890284</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01049605242466406</v>
+        <v>0.01049605242466405</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009512936879500935</v>
+        <v>0.009512936879500942</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.009655756859614541</v>
+        <v>0.009655756859614536</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.009350992558032069</v>
+        <v>0.009350992558032064</v>
       </c>
     </row>
     <row r="3">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009578667474531091</v>
+        <v>0.009578667474531094</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02118462809201522</v>
+        <v>0.02118462809201521</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009572801572979722</v>
+        <v>0.009572801572979725</v>
       </c>
       <c r="G3" t="n">
         <v>0.009440252610026945</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009559320478003888</v>
+        <v>0.00955932047800389</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00956766572705493</v>
+        <v>0.009567665727054933</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009555885836487518</v>
+        <v>0.00955588583648752</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="R3" t="n">
-        <v>0.009530063576456079</v>
+        <v>0.009530063576456083</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="U3" t="n">
         <v>0.009553914810806124</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005009685615608292</v>
+        <v>0.005009685615608266</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009516219849794495</v>
+        <v>0.009516219849794498</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009563233877186588</v>
+        <v>0.009563233877186592</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009562061799562257</v>
+        <v>0.00956206179956226</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009440156336571828</v>
+        <v>0.009440156336571831</v>
       </c>
     </row>
     <row r="4">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01468483344720268</v>
+        <v>0.01468483344720267</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01918610193158139</v>
+        <v>0.01918610193158137</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0225299746131945</v>
+        <v>0.02252997461319448</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01687928245251106</v>
+        <v>0.01687928245251102</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02686152706668728</v>
+        <v>0.02686152706668723</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02688362655778659</v>
+        <v>0.02688362655778651</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02580409562352428</v>
+        <v>0.02580409562352426</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02542711990256944</v>
+        <v>0.02542711990256946</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03665026612811263</v>
+        <v>0.0366502661281126</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03317248078070787</v>
+        <v>0.03317248078070782</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03655830826041562</v>
+        <v>0.03655830826041563</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03113362610182707</v>
+        <v>0.03113362610182702</v>
       </c>
       <c r="N4" t="n">
         <v>0.02737777328690433</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0280744856527574</v>
+        <v>0.02807448565275741</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02820537491781609</v>
+        <v>0.02820537491781607</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02086480453124417</v>
+        <v>0.02086480453124416</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04307627027546263</v>
+        <v>0.04307627027546258</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0319409345574411</v>
+        <v>0.03194093455744106</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0251902282489455</v>
+        <v>0.02519022824894546</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04365060637759288</v>
+        <v>0.04365060637759276</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03160247681884792</v>
+        <v>0.0316024768188479</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04184277768620864</v>
+        <v>0.04184277768620859</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4548196493636436</v>
+        <v>0.4548196493636443</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2855398752485229</v>
+        <v>0.2855398752485227</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02990902394513799</v>
+        <v>0.029909023945138</v>
       </c>
       <c r="AA4" t="n">
         <v>0.06975384465746889</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02185867612694037</v>
+        <v>0.02185867612694036</v>
       </c>
     </row>
     <row r="5">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01288543955846434</v>
+        <v>0.01288543955846431</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01960978346882827</v>
+        <v>0.01960978346882825</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01960978346882827</v>
+        <v>0.01960978346882825</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01602926869226851</v>
+        <v>0.0160292686922685</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01393301375064903</v>
+        <v>0.01393301375064901</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02100411998367644</v>
+        <v>0.0210041199836764</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01960978346882827</v>
+        <v>0.01960978346882825</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01960978346882827</v>
+        <v>0.01960978346882825</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01959271873960739</v>
+        <v>0.01959271873960735</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01960978346882827</v>
+        <v>0.01960978346882825</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01960978346882827</v>
+        <v>0.01960978346882825</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01960978346882852</v>
+        <v>0.01960978346882847</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02737777328690433</v>
+        <v>0.01439729198010206</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01582972990059092</v>
+        <v>0.0158297299005909</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0154786047537159</v>
+        <v>0.01547860475371587</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01156395250438442</v>
+        <v>0.01156395250438443</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01960978346882827</v>
+        <v>0.01960978346882825</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01960978346882827</v>
+        <v>0.01960978346882825</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01960978346882827</v>
+        <v>0.01960978346882825</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0163238532262323</v>
+        <v>0.01632385322623227</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01765239209679643</v>
+        <v>0.01765239209679642</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01961110499522465</v>
+        <v>0.01961110499522458</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01218025198533378</v>
+        <v>0.0121802519853338</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02628902900422922</v>
+        <v>0.02628902900422918</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01276053141803549</v>
+        <v>0.01276053141803547</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01960978346882827</v>
+        <v>0.01960978346882825</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0266339229638264</v>
+        <v>0.02663392296382636</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01165960454280696</v>
+        <v>0.01165960454280695</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01365013832833134</v>
+        <v>0.01365013832833132</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008281840527370306</v>
+        <v>0.008281840527370292</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01424738825334646</v>
+        <v>0.01424738825334643</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01423032254274788</v>
+        <v>0.01423032254274784</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02737777328690433</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01510497638660561</v>
+        <v>0.01510497638660558</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01529148709185496</v>
+        <v>0.01529148709185495</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01424738825334646</v>
+        <v>0.01424738825334643</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01711837287223594</v>
+        <v>0.0171183728722359</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="Z6" t="n">
         <v>0.01268718479059703</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01424738727196875</v>
+        <v>0.01424738727196872</v>
       </c>
     </row>
     <row r="7">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009397219471819668</v>
+        <v>0.009397219471819662</v>
       </c>
       <c r="C7" t="n">
         <v>0.009334735752933469</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009241037785795096</v>
+        <v>0.009241037785795093</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02087007410669454</v>
+        <v>0.02087007410669453</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009157767860343684</v>
+        <v>0.009157767860343691</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008958688509198865</v>
+        <v>0.00895868850919887</v>
       </c>
       <c r="H7" t="n">
         <v>0.00919186654969459</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009181782003772055</v>
+        <v>0.00918178200377205</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008865623523977807</v>
+        <v>0.008865623523977798</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008964342490921902</v>
+        <v>0.008964342490921911</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008847600691171534</v>
+        <v>0.00884760069117153</v>
       </c>
       <c r="M7" t="n">
-        <v>0.009050851842644725</v>
+        <v>0.009050851842644732</v>
       </c>
       <c r="N7" t="n">
-        <v>0.009122441716300687</v>
+        <v>0.009122441716300693</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009044166064888502</v>
+        <v>0.009044166064888507</v>
       </c>
       <c r="P7" t="n">
-        <v>0.009032197805249231</v>
+        <v>0.009032197805249229</v>
       </c>
       <c r="Q7" t="n">
         <v>0.00926346601268023</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008772455219781849</v>
+        <v>0.008772455219781844</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008947578523576076</v>
+        <v>0.008947578523576074</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009185267515351092</v>
+        <v>0.009185267515351094</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00863809421322872</v>
+        <v>0.008638094213228725</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004405023993180319</v>
+        <v>0.004405023993180294</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008769732933709496</v>
+        <v>0.008769732933709487</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.001211781414944594</v>
+        <v>-0.001211781414944583</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003184546813417509</v>
+        <v>0.003184546813417506</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008979976073188617</v>
+        <v>0.008979976073188612</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.008134789109812336</v>
+        <v>0.008134789109812328</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.009155246291362844</v>
+        <v>0.009155246291362841</v>
       </c>
     </row>
     <row r="8">
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009366419564714719</v>
+        <v>0.009366419564714713</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009359521262439182</v>
+        <v>0.009359521262439179</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009322480708449245</v>
+        <v>0.009322480708449243</v>
       </c>
       <c r="E8" t="n">
         <v>0.02076022919180052</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009305926047534425</v>
+        <v>0.009305926047534423</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009164281904995889</v>
+        <v>0.009164281904995884</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009308944003065383</v>
+        <v>0.009308944003065369</v>
       </c>
       <c r="I8" t="n">
         <v>0.009305760398422867</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00921290201723386</v>
+        <v>0.009212902017233862</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009247200699390418</v>
+        <v>0.009247200699390406</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009209496459035845</v>
+        <v>0.009209496459035843</v>
       </c>
       <c r="M8" t="n">
         <v>0.009268753335926081</v>
@@ -1928,40 +1928,40 @@
         <v>0.009265027401314987</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009257641217196922</v>
+        <v>0.009257641217196941</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009328722032391577</v>
+        <v>0.009328722032391584</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009169645259331258</v>
+        <v>0.009169645259331241</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009237737216513039</v>
+        <v>0.009237737216513033</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009306668228435854</v>
+        <v>0.009306668228435845</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009144336486984163</v>
+        <v>0.009144336486984159</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004758914122727675</v>
+        <v>0.004758914122727655</v>
       </c>
       <c r="W8" t="n">
-        <v>0.009187464717447816</v>
+        <v>0.009187464717447812</v>
       </c>
       <c r="X8" t="n">
-        <v>0.006320302145335038</v>
+        <v>0.006320302145335036</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.007594262782033842</v>
+        <v>0.007594262782033834</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009247552719949521</v>
+        <v>0.009247552719949516</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.009006343237330138</v>
+        <v>0.009006343237330129</v>
       </c>
       <c r="AB8" t="n">
         <v>0.009221357579507542</v>
@@ -2130,52 +2130,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01061585310410224</v>
+        <v>0.01061585310410227</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01018983337464184</v>
+        <v>0.01018983337464185</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01083863754088138</v>
+        <v>0.01083863754088139</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0214405759788574</v>
+        <v>0.02144057597885744</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01032053075657389</v>
+        <v>0.0103205307565739</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01041871045562147</v>
+        <v>0.01041871045562148</v>
       </c>
       <c r="H2" t="n">
         <v>0.01020210892959684</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01045386972762056</v>
+        <v>0.01045386972762057</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01066103712920626</v>
+        <v>0.01066103712920627</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01103737106828486</v>
+        <v>0.01103737106828487</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01093078737121288</v>
+        <v>0.01093078737121291</v>
       </c>
       <c r="M2" t="n">
         <v>0.01230157823736935</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01053151584580536</v>
+        <v>0.01053151584580537</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01044413857506995</v>
+        <v>0.01044413857506996</v>
       </c>
       <c r="P2" t="n">
         <v>0.01045582151138334</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01031815049884894</v>
+        <v>0.01031815049884896</v>
       </c>
       <c r="R2" t="n">
         <v>0.01022038778037063</v>
@@ -2184,31 +2184,31 @@
         <v>0.01066273794782473</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01059952755407811</v>
+        <v>0.01059952755407812</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01146459066591618</v>
+        <v>0.01146459066591619</v>
       </c>
       <c r="V2" t="n">
-        <v>0.005778151239265146</v>
+        <v>0.005778151239265149</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01089504778603932</v>
+        <v>0.01089504778603933</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01124870527109865</v>
+        <v>0.01124870527109866</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01122694570292685</v>
+        <v>0.01122694570292686</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0103484169956628</v>
+        <v>0.01034841699566283</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0107546003768548</v>
+        <v>0.01075460037685481</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01206986807311207</v>
+        <v>0.01206986807311208</v>
       </c>
     </row>
     <row r="3">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0102114791023437</v>
+        <v>0.01021147910234371</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02151910228395809</v>
+        <v>0.02151910228395812</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01020133895748117</v>
+        <v>0.01020133895748118</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01013453650207704</v>
+        <v>0.01013453650207706</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01018215823249171</v>
+        <v>0.01018215823249173</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01019868708393666</v>
+        <v>0.01019868708393667</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01019556271706791</v>
+        <v>0.01019556271706793</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01019618282385798</v>
+        <v>0.01019618282385799</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01019641215994383</v>
+        <v>0.01019641215994384</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005675604576081393</v>
+        <v>0.005675604576081401</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01018722802331003</v>
+        <v>0.01018722802331004</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01019631368166632</v>
+        <v>0.01019631368166633</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0101956052490219</v>
+        <v>0.01019560524902191</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01007369978603147</v>
+        <v>0.01007369978603148</v>
       </c>
     </row>
     <row r="4">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.152917522635672</v>
+        <v>0.1529175226356731</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04640035053841889</v>
+        <v>0.04640035053841891</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2362636559017173</v>
+        <v>0.2362636559017168</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07368143247061634</v>
+        <v>0.07368143247061858</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08743504771206533</v>
+        <v>0.08743504771206559</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1204192071791172</v>
+        <v>0.1204192071791174</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05701106438132653</v>
+        <v>0.0570110643813266</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1280368605442038</v>
+        <v>0.1280368605442039</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1809866237641353</v>
+        <v>0.1809866237641349</v>
       </c>
       <c r="K4" t="n">
-        <v>0.270608979578529</v>
+        <v>0.2706089795785293</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2493599045625399</v>
+        <v>0.2493599045625506</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6551598094542866</v>
+        <v>0.6551598094542849</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1448390780669711</v>
+        <v>0.1448390780669714</v>
       </c>
       <c r="O4" t="n">
         <v>0.1076474784297695</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1151466622088613</v>
+        <v>0.1151466622088622</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08603051233484074</v>
+        <v>0.08603051233484185</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06137403867399</v>
+        <v>0.06137403867399002</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1688972645730275</v>
+        <v>0.1688972645730283</v>
       </c>
       <c r="T4" t="n">
-        <v>0.167918174144345</v>
+        <v>0.1679181741443457</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3848409883838092</v>
+        <v>0.3848409883838091</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05555617413234677</v>
+        <v>0.05555617413234679</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2414686718361838</v>
+        <v>0.2414686718361837</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3486567588511785</v>
+        <v>0.3486567588511801</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3278078995920282</v>
+        <v>0.327807899592028</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.08792964615432221</v>
+        <v>0.08792964615432285</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2028774266225251</v>
+        <v>0.2028774266225262</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6481395694259453</v>
+        <v>0.6481395694259477</v>
       </c>
     </row>
     <row r="5">
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01510872899579621</v>
+        <v>0.01510872899579619</v>
       </c>
       <c r="C5" t="n">
         <v>0.02312523744663657</v>
@@ -2403,13 +2403,13 @@
         <v>0.02312523744663657</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01885668316881609</v>
+        <v>0.01885668316881608</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0163576073215003</v>
+        <v>0.01635760732150028</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02478751269659594</v>
+        <v>0.0247875126965959</v>
       </c>
       <c r="H5" t="n">
         <v>0.02312523744663657</v>
@@ -2418,7 +2418,7 @@
         <v>0.02312523744663657</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02310407027442139</v>
+        <v>0.02310407027442134</v>
       </c>
       <c r="K5" t="n">
         <v>0.02312523744663657</v>
@@ -2427,43 +2427,43 @@
         <v>0.02312523744663657</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02312523744663777</v>
+        <v>0.02312523744663775</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1448390780669711</v>
+        <v>0.01691110226453267</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01861880056890386</v>
+        <v>0.01861880056890384</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01820020245073644</v>
+        <v>0.01820020245073645</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01353330211739629</v>
+        <v>0.01353330211739625</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02312523744663657</v>
+        <v>0.02312523744663656</v>
       </c>
       <c r="S5" t="n">
         <v>0.02312523744663657</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02312523744663657</v>
+        <v>0.02312523744663656</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01921092040094153</v>
+        <v>0.01921092040094149</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02079059142076517</v>
+        <v>0.02079059142076514</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02312681292003219</v>
+        <v>0.02312681292003214</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01426803104582771</v>
+        <v>0.01426803104582768</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03109318990653618</v>
+        <v>0.03109318990653613</v>
       </c>
       <c r="Z5" t="n">
         <v>0.01495981823566282</v>
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01581717133622108</v>
+        <v>0.01581717133622106</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01865179386028017</v>
+        <v>0.01865179386028018</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01100706159141678</v>
+        <v>0.01100706159141677</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01950230848216293</v>
+        <v>0.01950230848216294</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="J6" t="n">
         <v>0.01948114671849175</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1448390780669711</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02072355810705283</v>
+        <v>0.02072355810705286</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02098915894735148</v>
+        <v>0.02098915894735149</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01950230848216293</v>
+        <v>0.01950230848216294</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02361298766697704</v>
+        <v>0.02361298766697707</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="Z6" t="n">
         <v>0.01728049847834076</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01950231389070692</v>
+        <v>0.0195023138907069</v>
       </c>
     </row>
     <row r="7">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006770645207805077</v>
+        <v>0.00677064520780505</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009418906978469038</v>
+        <v>0.009418906978469052</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005518602758606344</v>
+        <v>0.005518602758606357</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0199910094705159</v>
+        <v>0.01999100947051586</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00859777188519636</v>
+        <v>0.008597771885196366</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007551855053268319</v>
+        <v>0.007551855053268327</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009253562125422143</v>
+        <v>0.009253562125422153</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007776948536630959</v>
+        <v>0.007776948536630975</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006444689252576477</v>
+        <v>0.006444689252576482</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004365820800093589</v>
+        <v>0.004365820800093605</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004930365401169342</v>
+        <v>0.004930365401169266</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.003000309184483504</v>
+        <v>-0.003000309184483491</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0073053567393779</v>
+        <v>0.007305356739377915</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00778957533503508</v>
+        <v>0.00778957533503509</v>
       </c>
       <c r="P7" t="n">
-        <v>0.007717513465929142</v>
+        <v>0.007717513465929154</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008563180585298745</v>
+        <v>0.008563180585298754</v>
       </c>
       <c r="R7" t="n">
-        <v>0.009147879448640829</v>
+        <v>0.009147879448640844</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006503187911369392</v>
+        <v>0.006503187911369354</v>
       </c>
       <c r="T7" t="n">
-        <v>0.006921284423480219</v>
+        <v>0.006921284423480216</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001771359261633983</v>
+        <v>0.00177135926163399</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004558757079241429</v>
+        <v>0.004558757079241434</v>
       </c>
       <c r="W7" t="n">
-        <v>0.005150101997256581</v>
+        <v>0.005150101997256589</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003056534082188755</v>
+        <v>0.003056534082188749</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003202577029993221</v>
+        <v>0.003202577029993235</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008368268651273872</v>
+        <v>0.008368268651273859</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.005982456312061199</v>
+        <v>0.005982456312061203</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.00246494170328081</v>
+        <v>-0.002464941703280822</v>
       </c>
     </row>
     <row r="8">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009057485370648544</v>
+        <v>0.009057485370648559</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009829210532501388</v>
+        <v>0.009829210532501393</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008710586503019733</v>
+        <v>0.008710586503019729</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02074528887899836</v>
+        <v>0.02074528887899835</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009590902628419254</v>
+        <v>0.009590902628419259</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00924358216589607</v>
+        <v>0.009243582165896077</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009773476306245629</v>
+        <v>0.00977347630624564</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009353373215681068</v>
+        <v>0.009353373215681077</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008960476832737896</v>
+        <v>0.008960476832737908</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008383398320894324</v>
+        <v>0.008383398320894336</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008535086461116153</v>
+        <v>0.008535086461116162</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006297395117240254</v>
+        <v>0.006297395117240263</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009216443563241843</v>
+        <v>0.009216443563241855</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009349387296643566</v>
+        <v>0.009349387296643578</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009328301205040784</v>
+        <v>0.009328301205040796</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009575392074626172</v>
+        <v>0.009575392074626182</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009743406403902182</v>
+        <v>0.009743406403902186</v>
       </c>
       <c r="S8" t="n">
-        <v>0.008982676292156974</v>
+        <v>0.008982676292156981</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009109701143815303</v>
+        <v>0.00910970114381531</v>
       </c>
       <c r="U8" t="n">
-        <v>0.007631164748134668</v>
+        <v>0.007631164748134672</v>
       </c>
       <c r="V8" t="n">
-        <v>0.00526998206902117</v>
+        <v>0.005269982069021171</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008599327727421275</v>
+        <v>0.008599327727421282</v>
       </c>
       <c r="X8" t="n">
-        <v>0.008004216803715188</v>
+        <v>0.008004216803715184</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.008045095577810161</v>
+        <v>0.008045095577810166</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009516650681200386</v>
+        <v>0.009516650681200403</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.008837604184028661</v>
+        <v>0.008837604184028675</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.006364746237195437</v>
+        <v>0.006364746237195438</v>
       </c>
     </row>
   </sheetData>
@@ -2902,28 +2902,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01046348596572265</v>
+        <v>0.01046348596572266</v>
       </c>
       <c r="C2" t="n">
         <v>0.01012975614372371</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0109396118202816</v>
+        <v>0.01093961182028162</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02142392230109595</v>
+        <v>0.02142392230109598</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01029177790292202</v>
+        <v>0.01029177790292203</v>
       </c>
       <c r="G2" t="n">
         <v>0.01035227397214874</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01007412869534701</v>
+        <v>0.01007412869534702</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0105834507426314</v>
+        <v>0.01058345074263141</v>
       </c>
       <c r="J2" t="n">
         <v>0.01063137982883027</v>
@@ -2944,16 +2944,16 @@
         <v>0.01031881937051039</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01039262771623219</v>
+        <v>0.0103926277162322</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01024698741403172</v>
+        <v>0.01024698741403173</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01008575064805615</v>
+        <v>0.01008575064805616</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01058115305692437</v>
+        <v>0.01058115305692438</v>
       </c>
       <c r="T2" t="n">
         <v>0.01051795051146375</v>
@@ -2962,25 +2962,25 @@
         <v>0.01125180955667676</v>
       </c>
       <c r="V2" t="n">
-        <v>0.005813923443647964</v>
+        <v>0.005813923443647969</v>
       </c>
       <c r="W2" t="n">
         <v>0.01078260999980972</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01229521683756616</v>
+        <v>0.01229521683756617</v>
       </c>
       <c r="Y2" t="n">
         <v>0.01237782947441325</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01031923165284428</v>
+        <v>0.01031923165284429</v>
       </c>
       <c r="AA2" t="n">
         <v>0.01074081112590386</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01190948062816549</v>
+        <v>0.0119094806281655</v>
       </c>
     </row>
     <row r="3">
@@ -2993,7 +2993,7 @@
         <v>0.01016929993331915</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01018597077875013</v>
+        <v>0.01018597077875014</v>
       </c>
       <c r="D3" t="n">
         <v>0.01016929993331915</v>
@@ -3032,7 +3032,7 @@
         <v>0.01016929993331915</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01016927957164361</v>
+        <v>0.0101692795716436</v>
       </c>
       <c r="Q3" t="n">
         <v>0.01016929993331915</v>
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1149562984835887</v>
+        <v>0.1149562984835891</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03416739877323903</v>
+        <v>0.03416739877323906</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2515203320477826</v>
+        <v>0.2515203320477825</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06888823030954204</v>
+        <v>0.06888823030954194</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07928550157612424</v>
+        <v>0.07928550157612428</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1036193314441844</v>
+        <v>0.1036193314441846</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02526172914575124</v>
+        <v>0.02526172914575128</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1605212049577544</v>
+        <v>0.1605212049577542</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1667380120422189</v>
+        <v>0.166738012042219</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1938401710388091</v>
+        <v>0.193840171038809</v>
       </c>
       <c r="L4" t="n">
         <v>0.1957653109942871</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5298807234350472</v>
+        <v>0.5298807234350471</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09308692212854859</v>
+        <v>0.09308692212854876</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07736051629961126</v>
+        <v>0.0773605162996118</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09749402726002865</v>
+        <v>0.09749402726002947</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06746019009977999</v>
+        <v>0.06746019009978028</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03207582177940679</v>
+        <v>0.03207582177940695</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1429953375554884</v>
+        <v>0.1429953375554888</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1421739502524762</v>
+        <v>0.1421739502524766</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3107446022421186</v>
+        <v>0.3107446022421185</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06207319183566327</v>
+        <v>0.06207319183566389</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2032723684985448</v>
+        <v>0.2032723684985447</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6226325389774495</v>
+        <v>0.6226325389774499</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6017970318466414</v>
+        <v>0.6017970318466429</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.07708106187995196</v>
+        <v>0.07708106187995198</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1927602064757153</v>
+        <v>0.1927602064757155</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5688391613427368</v>
+        <v>0.5688391613427376</v>
       </c>
     </row>
     <row r="5">
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01414577815023868</v>
+        <v>0.01414577815023871</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02153307679719696</v>
+        <v>0.02153307679719699</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02153307679719696</v>
+        <v>0.02153307679719699</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01759955817940131</v>
+        <v>0.01759955817940132</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01529663294223683</v>
+        <v>0.01529663294223686</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02306488129540666</v>
+        <v>0.02306488129540674</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02153307679719696</v>
+        <v>0.02153307679719699</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02153307679719696</v>
+        <v>0.02153307679719699</v>
       </c>
       <c r="J5" t="n">
         <v>0.02151337952929588</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02153307679719696</v>
+        <v>0.02153307679719699</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02153307679719697</v>
+        <v>0.021533076797197</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0215330767972</v>
+        <v>0.02153307679720004</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09308692212854859</v>
+        <v>0.01580668447762681</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01738034680840977</v>
+        <v>0.01738034680840982</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01699460414612787</v>
+        <v>0.01699460414612789</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01269400535929417</v>
+        <v>0.01269400535929422</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02153307679719696</v>
+        <v>0.02153307679719699</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02153307679719696</v>
+        <v>0.02153307679719699</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02153307679719696</v>
+        <v>0.02153307679719699</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01792402997502787</v>
+        <v>0.0179240299750279</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01937797028137624</v>
+        <v>0.01937797028137626</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02153452861290944</v>
+        <v>0.02153452861290946</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01337106595898786</v>
+        <v>0.01337106595898788</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02887227481780021</v>
+        <v>0.02887227481780027</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01400855528524298</v>
+        <v>0.014008555285243</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02153307679719696</v>
+        <v>0.02153307679719699</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02924972794967956</v>
+        <v>0.02924972794967958</v>
       </c>
     </row>
     <row r="6">
@@ -3257,82 +3257,82 @@
         <v>0.01419403815848723</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01667756318749957</v>
+        <v>0.01667756318749958</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009979710556796093</v>
+        <v>0.00997971055679611</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01742273272349905</v>
+        <v>0.01742273272349906</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01740303952158</v>
+        <v>0.01740303952158001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01742273678948108</v>
+        <v>0.0174227367894811</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09308692212854859</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01849271787472936</v>
+        <v>0.01849271787472935</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01872542128726828</v>
+        <v>0.0187254212872683</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01742273272349905</v>
+        <v>0.01742273272349906</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02101628250486132</v>
+        <v>0.02101628250486134</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01742273678948108</v>
+        <v>0.0174227367894811</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01547611700751972</v>
+        <v>0.01547611700751974</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01742273678948107</v>
+        <v>0.01742273678948109</v>
       </c>
     </row>
     <row r="7">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007497060907642211</v>
+        <v>0.007497060907642223</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009598436146090081</v>
+        <v>0.009598436146090093</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004749467075766074</v>
+        <v>0.004749467075766088</v>
       </c>
       <c r="E7" t="n">
         <v>0.01997782657194618</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008603354343608607</v>
+        <v>0.008603354343608611</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00769626911560265</v>
+        <v>0.007696269115602657</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009821499730608871</v>
+        <v>0.009821499730608864</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006841952056390474</v>
+        <v>0.006841952056390467</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006464060449249614</v>
+        <v>0.006464060449249616</v>
       </c>
       <c r="K7" t="n">
         <v>0.00553098406068262</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005744315125394566</v>
+        <v>0.00574431512539456</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.001234651571252709</v>
+        <v>-0.001234651571252698</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008241671258269937</v>
+        <v>0.008241671258269943</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008355722683887104</v>
+        <v>0.008355722683887111</v>
       </c>
       <c r="P7" t="n">
-        <v>0.007914004160819903</v>
+        <v>0.0079140041608199</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008803023913768044</v>
+        <v>0.008803023913768039</v>
       </c>
       <c r="R7" t="n">
-        <v>0.009647575245943505</v>
+        <v>0.009647575245943514</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006807483669664051</v>
+        <v>0.00680748366966405</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00722124153427393</v>
+        <v>0.007221241534273932</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002799974665007621</v>
+        <v>0.002799974665007624</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00426321141419856</v>
+        <v>0.004263211414198546</v>
       </c>
       <c r="W7" t="n">
-        <v>0.005634883353837622</v>
+        <v>0.00563488335383763</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.003839646851313138</v>
+        <v>-0.003839646851313149</v>
       </c>
       <c r="Y7" t="n">
         <v>-0.003757519063880395</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008364936787088091</v>
+        <v>0.008364936787088089</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.005885074216238423</v>
+        <v>0.005885074216238426</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.001703322968883538</v>
+        <v>-0.001703322968883546</v>
       </c>
     </row>
     <row r="8">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009247608693119162</v>
+        <v>0.009247608693119176</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0098624260135016</v>
+        <v>0.009862426013501614</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008473570598112478</v>
+        <v>0.008473570598112485</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02073011644376165</v>
+        <v>0.02073011644376167</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009575585728346049</v>
+        <v>0.009575585728346051</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009259820282098792</v>
+        <v>0.009259820282098799</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00991587849474037</v>
+        <v>0.009915878494740363</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009069496855000322</v>
+        <v>0.009069496855000332</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008950264065660612</v>
+        <v>0.008950264065660627</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008697369842997075</v>
+        <v>0.008697369842997082</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008749432378750942</v>
+        <v>0.00874943237875095</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00677981193774954</v>
+        <v>0.006779811937749547</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009464950214206864</v>
+        <v>0.009464950214206871</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009493635942491042</v>
+        <v>0.009493635942491052</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009366470217171128</v>
+        <v>0.009366470217171121</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009625327471072634</v>
+        <v>0.009625327471072642</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0098559170066897</v>
+        <v>0.00985591700668971</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009051515943488542</v>
+        <v>0.009051515943488539</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009176574544993486</v>
+        <v>0.009176574544993502</v>
       </c>
       <c r="U8" t="n">
-        <v>0.007902021275212742</v>
+        <v>0.00790202127521274</v>
       </c>
       <c r="V8" t="n">
-        <v>0.005176870128625337</v>
+        <v>0.005176870128625335</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008719436005817385</v>
+        <v>0.008719436005817392</v>
       </c>
       <c r="X8" t="n">
-        <v>0.005966598718669353</v>
+        <v>0.005966598718669371</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.006041082448548672</v>
+        <v>0.006041082448548686</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009497698670287047</v>
+        <v>0.009497698670287049</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.008791474771614861</v>
+        <v>0.00879147477161487</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.006562866746009329</v>
+        <v>0.006562866746009347</v>
       </c>
     </row>
   </sheetData>
@@ -3674,82 +3674,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01026736309855426</v>
+        <v>0.01026736309855425</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01000138413727669</v>
+        <v>0.0100013841372767</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01053626646837025</v>
+        <v>0.01053626646837027</v>
       </c>
       <c r="E2" t="n">
         <v>0.02129933656951193</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01020509558885388</v>
+        <v>0.01020509558885391</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01013227396496265</v>
+        <v>0.01013227396496266</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009947030605803675</v>
+        <v>0.009947030605803674</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01045385478521957</v>
+        <v>0.01045385478521958</v>
       </c>
       <c r="J2" t="n">
         <v>0.01049133477669533</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01082519187853738</v>
+        <v>0.01082519187853739</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01051294790685417</v>
+        <v>0.01051294790685415</v>
       </c>
       <c r="M2" t="n">
         <v>0.01150110508138318</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01010518006998834</v>
+        <v>0.01010518006998837</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01011149585287816</v>
+        <v>0.01011149585287819</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01020390403553273</v>
+        <v>0.01020390403553275</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01012253270332925</v>
+        <v>0.01012253270332926</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01003178036031493</v>
+        <v>0.01003178036031496</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01042248108328776</v>
+        <v>0.0104224810832878</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01039033659801001</v>
+        <v>0.01039033659801003</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01121850867930341</v>
+        <v>0.01121850867930343</v>
       </c>
       <c r="V2" t="n">
-        <v>0.005807316123431561</v>
+        <v>0.005807316123431564</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0105309537898902</v>
+        <v>0.01053095378989022</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01269472520681774</v>
+        <v>0.01269472520681778</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0135340036104072</v>
+        <v>0.01353400361040718</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01015264502735759</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01066324734526302</v>
+        <v>0.01066324734526305</v>
       </c>
       <c r="AB2" t="n">
         <v>0.01154956804724838</v>
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0100560714487174</v>
+        <v>0.01005607144871741</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02145325840055073</v>
+        <v>0.02145325840055074</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01005020554716603</v>
+        <v>0.01005020554716604</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009917656584213253</v>
+        <v>0.009917656584213265</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="J3" t="n">
         <v>0.01003675837790322</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01004506970124124</v>
+        <v>0.01004506970124125</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01003328981067383</v>
+        <v>0.01003328981067384</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01000746755064239</v>
+        <v>0.0100074675506424</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01003131878499243</v>
+        <v>0.01003131878499245</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005525831050974636</v>
+        <v>0.005525831050974638</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009993623823980806</v>
+        <v>0.009993623823980816</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0100406378513729</v>
+        <v>0.01004063785137291</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01003946577374857</v>
+        <v>0.01003946577374858</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009917560310758139</v>
+        <v>0.009917560310758149</v>
       </c>
     </row>
     <row r="4">
@@ -3850,85 +3850,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09603182622074345</v>
+        <v>0.09603182622074341</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03393201881802663</v>
+        <v>0.03393201881802665</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1722300328143719</v>
+        <v>0.1722300328143722</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04767184423053009</v>
+        <v>0.04767184423053003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0886897973456278</v>
+        <v>0.08868979734562792</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09010855219430511</v>
+        <v>0.09010855219430483</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02546020677239947</v>
+        <v>0.0254602067723996</v>
       </c>
       <c r="I4" t="n">
         <v>0.157361298611718</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1577979735494194</v>
+        <v>0.1577979735494195</v>
       </c>
       <c r="K4" t="n">
-        <v>0.227102382363032</v>
+        <v>0.2271023823630325</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1592291051435905</v>
+        <v>0.1592291051435913</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4205374595982414</v>
+        <v>0.4205374595982416</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06508031811524045</v>
+        <v>0.06508031811524044</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05965753131025056</v>
+        <v>0.05965753131025062</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08211453204884472</v>
+        <v>0.08211453204884463</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06692435774908441</v>
+        <v>0.06692435774908437</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05594426067299297</v>
+        <v>0.055944260672993</v>
       </c>
       <c r="S4" t="n">
-        <v>0.13395934793739</v>
+        <v>0.1339593479373902</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1423943434698898</v>
+        <v>0.1423943434698901</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3218947528434747</v>
+        <v>0.3218947528434744</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08998168245163378</v>
+        <v>0.08998168245163388</v>
       </c>
       <c r="W4" t="n">
-        <v>0.172136453765937</v>
+        <v>0.1721364537659372</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7222167367297706</v>
+        <v>0.7222167367297705</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.9437740267302093</v>
+        <v>0.9437740267302088</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06547772748817132</v>
+        <v>0.06547772748817146</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2066631989927944</v>
+        <v>0.2066631989927948</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4966275754307911</v>
+        <v>0.496627575430791</v>
       </c>
     </row>
     <row r="5">
@@ -3947,13 +3947,13 @@
         <v>0.02152061255821755</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01760855301923129</v>
+        <v>0.01760855301923136</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01531819125488362</v>
+        <v>0.01531819125488365</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02304406038733611</v>
+        <v>0.02304406038733614</v>
       </c>
       <c r="H5" t="n">
         <v>0.02152061255821755</v>
@@ -3962,28 +3962,28 @@
         <v>0.02152061255821755</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02150347360792126</v>
+        <v>0.02150347360792132</v>
       </c>
       <c r="K5" t="n">
         <v>0.02152061255821755</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02152061255821755</v>
+        <v>0.02152061255821756</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02152061255822169</v>
+        <v>0.0215206125582217</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06508031811524045</v>
+        <v>0.01582546023421089</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01739053754298154</v>
+        <v>0.01739053754298158</v>
       </c>
       <c r="P5" t="n">
         <v>0.01700689927703533</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01272976215319927</v>
+        <v>0.01272976215319936</v>
       </c>
       <c r="R5" t="n">
         <v>0.02152061255821755</v>
@@ -3995,28 +3995,28 @@
         <v>0.02152061255821755</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01793029028204125</v>
+        <v>0.01793029028204128</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01939209926885996</v>
+        <v>0.01939209926885998</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02152205645367462</v>
+        <v>0.02152205645367463</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01340312908875069</v>
+        <v>0.01340312908875074</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02881812221576324</v>
+        <v>0.02881812221576321</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01403714062956751</v>
+        <v>0.0140371406295675</v>
       </c>
       <c r="AA5" t="n">
         <v>0.02152061255821755</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02919516597550937</v>
+        <v>0.02919516597550933</v>
       </c>
     </row>
     <row r="6">
@@ -4026,82 +4026,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01371836784674289</v>
+        <v>0.01371836784674293</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01679027720692664</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01679027720692664</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01608129046752171</v>
+        <v>0.01608129046752174</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009708692121683321</v>
+        <v>0.009708692121683342</v>
       </c>
       <c r="G6" t="n">
         <v>0.01679027384089594</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01679027720692664</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01679027720692664</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="J6" t="n">
         <v>0.01677313825663043</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01679027720692664</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="L6" t="n">
         <v>0.01679027720692664</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01679027720692664</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06508031811524045</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0178082994650407</v>
+        <v>0.01780829946504076</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01802970257191394</v>
+        <v>0.01802970257191396</v>
       </c>
       <c r="Q6" t="n">
         <v>0.01679027384089594</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01679027720692664</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01679027720692664</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01679027720692664</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01679027720692664</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0202195154488691</v>
+        <v>0.02021951544886913</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01679027720692664</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="X6" t="n">
         <v>0.01679027720692664</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01679027720692664</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="Z6" t="n">
         <v>0.01493818769096078</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01679027720692664</v>
+        <v>0.01679027720692663</v>
       </c>
       <c r="AB6" t="n">
         <v>0.01679027720692664</v>
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007775256639975054</v>
+        <v>0.007775256639975085</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009473084596515776</v>
+        <v>0.009473084596515774</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006235189377331739</v>
+        <v>0.006235189377331728</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02037896896949629</v>
+        <v>0.02037896896949632</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008252131315130576</v>
+        <v>0.008252131315130584</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007796086612435434</v>
+        <v>0.007796086612435464</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009689112179972037</v>
+        <v>0.00968911217997204</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006724156041737279</v>
+        <v>0.006724156041737307</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006463877219091286</v>
+        <v>0.006463877219091272</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004570635387469955</v>
+        <v>0.004570635387469942</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006337674778730563</v>
+        <v>0.006337674778730552</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0006195415343434748</v>
+        <v>0.0006195415343434705</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008754835125610604</v>
+        <v>0.008754835125610632</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008701069912377065</v>
+        <v>0.008701069912377088</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008109214220117095</v>
+        <v>0.008109214220117096</v>
       </c>
       <c r="Q7" t="n">
         <v>0.00865508938870134</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008991019210980005</v>
+        <v>0.008991019210980019</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006862305599787863</v>
+        <v>0.006862305599787852</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007091857949969456</v>
+        <v>0.007091857949969432</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002106438660476219</v>
+        <v>0.00210643866047624</v>
       </c>
       <c r="V7" t="n">
-        <v>0.003364525699190929</v>
+        <v>0.003364525699190933</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0062375981923622</v>
+        <v>0.006237598192362204</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.00671534567215746</v>
+        <v>-0.006715345672157431</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.01145154922316735</v>
+        <v>-0.01145154922316736</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008467035882330689</v>
+        <v>0.008467035882330699</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.005460539550257363</v>
+        <v>0.005460539550257355</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.0004723206012035482</v>
+        <v>-0.0004723206012035338</v>
       </c>
     </row>
     <row r="8">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009237140727080893</v>
+        <v>0.009237140727080938</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009736123261656102</v>
+        <v>0.009736123261656097</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008805308584491049</v>
+        <v>0.008805308584491063</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02081053145482487</v>
+        <v>0.02081053145482484</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009386966083155177</v>
+        <v>0.009386966083155196</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0091669528667614</v>
+        <v>0.009166952866761422</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009787618604124681</v>
+        <v>0.009787618604124682</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008945378291889199</v>
+        <v>0.008945378291889206</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008865662463339223</v>
+        <v>0.008865662463339209</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008334306819784401</v>
+        <v>0.008334306819784414</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008828621207213028</v>
+        <v>0.008828621207213005</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007215009532936478</v>
+        <v>0.00721500953293649</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00952066903121066</v>
+        <v>0.009520669031210629</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009502521470739636</v>
+        <v>0.009502521470739649</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009328443510164345</v>
+        <v>0.009328443510164352</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009492637036387017</v>
+        <v>0.009492637036386989</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009569293126539914</v>
+        <v>0.009569293126539917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.008976863079126946</v>
+        <v>0.008976863079126958</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009049165644721713</v>
+        <v>0.009049165644721734</v>
       </c>
       <c r="U8" t="n">
-        <v>0.007612662967554072</v>
+        <v>0.007612662967554088</v>
       </c>
       <c r="V8" t="n">
-        <v>0.00482391530069849</v>
+        <v>0.004823915300698492</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008801091924526305</v>
+        <v>0.008801091924526327</v>
       </c>
       <c r="X8" t="n">
-        <v>0.005092090837748557</v>
+        <v>0.00509209083774855</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003755523299009289</v>
+        <v>0.003755523299009284</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009436651116671465</v>
+        <v>0.009436651116671458</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.008579821321402503</v>
+        <v>0.008579821321402486</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.006822139121719922</v>
+        <v>0.006822139121719942</v>
       </c>
     </row>
   </sheetData>
@@ -4446,52 +4446,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.009761652436223482</v>
+        <v>0.009761652436223484</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009691866947515958</v>
+        <v>0.009691866947515957</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009986562839470099</v>
+        <v>0.009986562839470105</v>
       </c>
       <c r="E2" t="n">
         <v>0.02108332280399229</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009735818208502183</v>
+        <v>0.009735818208502186</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009750020509773048</v>
+        <v>0.009750020509773045</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009791155824424096</v>
+        <v>0.009791155824424089</v>
       </c>
       <c r="I2" t="n">
         <v>0.009848877454338269</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009890957690108167</v>
+        <v>0.009890957690108171</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01009042605308065</v>
+        <v>0.01009042605308064</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009973095152397048</v>
+        <v>0.009973095152397046</v>
       </c>
       <c r="M2" t="n">
         <v>0.010389261625744</v>
       </c>
       <c r="N2" t="n">
-        <v>0.009959761732481949</v>
+        <v>0.009959761732481946</v>
       </c>
       <c r="O2" t="n">
         <v>0.009763184332234743</v>
       </c>
       <c r="P2" t="n">
-        <v>0.009866672709611952</v>
+        <v>0.009866672709611951</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.009814238725141967</v>
+        <v>0.009814238725141965</v>
       </c>
       <c r="R2" t="n">
         <v>0.009779351494023505</v>
@@ -4500,13 +4500,13 @@
         <v>0.009828286582447956</v>
       </c>
       <c r="T2" t="n">
-        <v>0.009792035178151699</v>
+        <v>0.009792035178151698</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01023151313374421</v>
+        <v>0.01023151313374422</v>
       </c>
       <c r="V2" t="n">
-        <v>0.005323199361657971</v>
+        <v>0.005323199361657967</v>
       </c>
       <c r="W2" t="n">
         <v>0.01008309901070066</v>
@@ -4515,13 +4515,13 @@
         <v>0.01004265926839343</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00986865880714554</v>
+        <v>0.009868658807145539</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009827717468568573</v>
+        <v>0.009827717468568571</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01002350107282937</v>
+        <v>0.01002350107282938</v>
       </c>
       <c r="AB2" t="n">
         <v>0.01168207834879544</v>
@@ -4534,85 +4534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009825449755830473</v>
+        <v>0.009825449755830469</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02128575698720917</v>
+        <v>0.02128575698720919</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009815309610967942</v>
+        <v>0.009815309610967939</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009748507155563821</v>
+        <v>0.009748507155563817</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009802445717116482</v>
+        <v>0.009802445717116474</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009812657737423435</v>
+        <v>0.009812657737423432</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009809533370554688</v>
+        <v>0.009809533370554685</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="R3" t="n">
-        <v>0.009810153477344754</v>
+        <v>0.009810153477344751</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="U3" t="n">
-        <v>0.009810382813430607</v>
+        <v>0.009810382813430605</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005323702937566899</v>
+        <v>0.005323702937566894</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009801198676796801</v>
+        <v>0.009801198676796798</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009810284335153093</v>
+        <v>0.00981028433515309</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009809575902508671</v>
+        <v>0.009809575902508668</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009687670439518242</v>
+        <v>0.009687670439518238</v>
       </c>
     </row>
     <row r="4">
@@ -4622,85 +4622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0345392573295443</v>
+        <v>0.03453925732954427</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01457408466406326</v>
+        <v>0.01457408466406322</v>
       </c>
       <c r="D4" t="n">
         <v>0.1008619385719559</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03970770885607356</v>
+        <v>0.03970770885607353</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02943137279457082</v>
+        <v>0.0294313727945708</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04425159688420068</v>
+        <v>0.04425159688420067</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04815677071516936</v>
+        <v>0.04815677071516941</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06311724363767064</v>
+        <v>0.06311724363767063</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0703453164132367</v>
+        <v>0.07034531641323666</v>
       </c>
       <c r="K4" t="n">
         <v>0.118669103865734</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08465729395870553</v>
+        <v>0.0846572939587056</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1972160440686042</v>
+        <v>0.1972160440686043</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08957227574141909</v>
+        <v>0.08957227574141904</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03457143738865433</v>
+        <v>0.03457143738865444</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06139150410608339</v>
+        <v>0.06139150410608304</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05024594836909235</v>
+        <v>0.05024594836909223</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04397654766347978</v>
+        <v>0.0439765476634797</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04775835651459654</v>
+        <v>0.04775835651459652</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0455706731268337</v>
+        <v>0.04557067312683366</v>
       </c>
       <c r="U4" t="n">
-        <v>0.155789821512955</v>
+        <v>0.1557898215129552</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02915914347318684</v>
+        <v>0.02915914347318679</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1241915099439977</v>
+        <v>0.1241915099439978</v>
       </c>
       <c r="X4" t="n">
         <v>0.1172019617801615</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06535522276856265</v>
+        <v>0.06535522276856268</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04975546323255631</v>
+        <v>0.04975546323255602</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1077659639654627</v>
+        <v>0.1077659639654626</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6193868552005435</v>
+        <v>0.6193868552005427</v>
       </c>
     </row>
     <row r="5">
@@ -4710,85 +4710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01403377558173894</v>
+        <v>0.01403377558173895</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0214754408544559</v>
+        <v>0.02147544085445589</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0214754408544559</v>
+        <v>0.02147544085445589</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01751297361212968</v>
+        <v>0.01751297361212969</v>
       </c>
       <c r="F5" t="n">
         <v>0.01519310005864684</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02301851862668939</v>
+        <v>0.02301851862668938</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0214754408544559</v>
+        <v>0.02147544085445589</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0214754408544559</v>
+        <v>0.02147544085445589</v>
       </c>
       <c r="J5" t="n">
         <v>0.02145565645733704</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0214754408544559</v>
+        <v>0.02147544085445589</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0214754408544559</v>
+        <v>0.02147544085445589</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0214754408544564</v>
+        <v>0.02147544085445639</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08957227574141909</v>
+        <v>0.01570690530461502</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01729214896106792</v>
+        <v>0.0172921489610679</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01690356743601338</v>
+        <v>0.01690356743601337</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01257131850793603</v>
+        <v>0.01257131850793601</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0214754408544559</v>
+        <v>0.02147544085445589</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0214754408544559</v>
+        <v>0.02147544085445589</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0214754408544559</v>
+        <v>0.02147544085445589</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01783948365276065</v>
+        <v>0.01783948365276064</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01930426210929672</v>
+        <v>0.01930426210929671</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02147690335489655</v>
+        <v>0.02147690335489652</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01325336191698553</v>
+        <v>0.01325336191698552</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02886805327652128</v>
+        <v>0.02886805327652127</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01389554282874329</v>
+        <v>0.01389554282874328</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0214754408544559</v>
+        <v>0.02147544085445589</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02924888249372852</v>
+        <v>0.02924888249372848</v>
       </c>
     </row>
     <row r="6">
@@ -4798,85 +4798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01374789360946753</v>
+        <v>0.01374789360946752</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="E6" t="n">
         <v>0.01617853940117301</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009623297509064087</v>
+        <v>0.009623297509064091</v>
       </c>
       <c r="G6" t="n">
         <v>0.01690784278069434</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01688805970729702</v>
+        <v>0.01688805970729703</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08957227574141909</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01795504579843846</v>
+        <v>0.01795504579843849</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01818279448781983</v>
+        <v>0.01818279448781985</v>
       </c>
       <c r="Q6" t="n">
         <v>0.01690784278069434</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="V6" t="n">
         <v>0.02042126338107085</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01500267442408837</v>
+        <v>0.01500267442408839</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01690784410441592</v>
+        <v>0.01690784410441591</v>
       </c>
     </row>
     <row r="7">
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009191509061814759</v>
+        <v>0.009191509061814757</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009710661733149292</v>
+        <v>0.009710661733149285</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007883772509612095</v>
+        <v>0.007883772509612101</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02049795816501177</v>
+        <v>0.02049795816501181</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009391075258003839</v>
+        <v>0.009391075258003834</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008868136489457137</v>
+        <v>0.008868136489457131</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009033718345872797</v>
+        <v>0.009033718345872804</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008692383962460694</v>
+        <v>0.008692383962460698</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008385602896643659</v>
+        <v>0.008385602896643663</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007291385074131254</v>
+        <v>0.007291385074131252</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007945438467622691</v>
+        <v>0.007945438467622688</v>
       </c>
       <c r="M7" t="n">
-        <v>0.005541251453858359</v>
+        <v>0.005541251453858357</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00803323347803382</v>
+        <v>0.008033233478033811</v>
       </c>
       <c r="O7" t="n">
         <v>0.009181700554078846</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008563971601110719</v>
+        <v>0.008563971601110729</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008890795728017216</v>
+        <v>0.008890795728017207</v>
       </c>
       <c r="R7" t="n">
-        <v>0.009104024253030829</v>
+        <v>0.009104024253030843</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00879825567540863</v>
+        <v>0.008798255675408618</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009023730675589174</v>
+        <v>0.009023730675589167</v>
       </c>
       <c r="U7" t="n">
-        <v>0.006419486961638639</v>
+        <v>0.00641948696163864</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004839164244268303</v>
+        <v>0.004839164244268297</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00729932576536038</v>
+        <v>0.007299325765360375</v>
       </c>
       <c r="X7" t="n">
-        <v>0.007499744019250862</v>
+        <v>0.007499744019250861</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.008566973416525641</v>
+        <v>0.008566973416525649</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008804164658659696</v>
+        <v>0.008804164658659692</v>
       </c>
       <c r="AA7" t="n">
         <v>0.007652835700160687</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.002819342993249454</v>
+        <v>-0.002819342993249458</v>
       </c>
     </row>
     <row r="8">
@@ -4983,76 +4983,76 @@
         <v>0.009110316158530899</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02072487182932656</v>
+        <v>0.02072487182932657</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009542790225948861</v>
+        <v>0.009542790225948854</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009349449051119656</v>
+        <v>0.009349449051119653</v>
       </c>
       <c r="H8" t="n">
         <v>0.009438138163643453</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009340551561336978</v>
+        <v>0.009340551561336974</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009246289691582877</v>
+        <v>0.009246289691582872</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008943238956463455</v>
+        <v>0.008943238956463461</v>
       </c>
       <c r="L8" t="n">
         <v>0.009124906678870412</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008447160399265177</v>
+        <v>0.008447160399265173</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009151520268478474</v>
+        <v>0.009151520268478468</v>
       </c>
       <c r="O8" t="n">
         <v>0.009477499047779163</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009299938135145101</v>
+        <v>0.009299938135145104</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009396190817769649</v>
+        <v>0.009396190817769656</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009458060446660361</v>
+        <v>0.009458060446660354</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009368132656231102</v>
+        <v>0.0093681326562311</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009434473095563193</v>
+        <v>0.009434473095563172</v>
       </c>
       <c r="U8" t="n">
-        <v>0.008688644715034981</v>
+        <v>0.008688644715034987</v>
       </c>
       <c r="V8" t="n">
-        <v>0.005102732712073913</v>
+        <v>0.005102732712073909</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008940927198605652</v>
+        <v>0.008940927198605656</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00899549006490922</v>
+        <v>0.008995490064909214</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.009303270716084094</v>
+        <v>0.009303270716084092</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009369929809450903</v>
+        <v>0.009369929809450908</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.009042177407637839</v>
+        <v>0.009042177407637826</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.005991347379399236</v>
+        <v>0.005991347379399238</v>
       </c>
     </row>
   </sheetData>
@@ -5218,46 +5218,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00956658182862285</v>
+        <v>0.009566581828622845</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00959503222156868</v>
+        <v>0.009595032221568676</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009624207715177814</v>
+        <v>0.009624207715177812</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02095045486571363</v>
+        <v>0.02095045486571362</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009608218426430899</v>
+        <v>0.009608218426430896</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009528378464857178</v>
+        <v>0.009528378464857171</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009605547696030973</v>
+        <v>0.00960554769603097</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009606861594569386</v>
+        <v>0.009606861594569385</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009615988091395326</v>
+        <v>0.009615988091395321</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009601423988974416</v>
+        <v>0.009601423988974414</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009609579324191642</v>
+        <v>0.009609579324191641</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009576997175997727</v>
+        <v>0.009576997175997722</v>
       </c>
       <c r="N2" t="n">
-        <v>0.009608901862541782</v>
+        <v>0.009608901862541775</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009615182441615567</v>
+        <v>0.009615182441615565</v>
       </c>
       <c r="P2" t="n">
         <v>0.00960780953751009</v>
@@ -5266,34 +5266,34 @@
         <v>0.009563490322176581</v>
       </c>
       <c r="R2" t="n">
-        <v>0.009639247392570088</v>
+        <v>0.009639247392570086</v>
       </c>
       <c r="S2" t="n">
-        <v>0.009619931230664201</v>
+        <v>0.009619931230664206</v>
       </c>
       <c r="T2" t="n">
-        <v>0.009567915748764817</v>
+        <v>0.009567915748764807</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009564813322162097</v>
+        <v>0.009564813322162096</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0052158580516045</v>
+        <v>0.005215858051604504</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009691513453758916</v>
+        <v>0.009691513453758909</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01020197883979935</v>
+        <v>0.01020197883979936</v>
       </c>
       <c r="Y2" t="n">
         <v>0.01003738928197103</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009635831597992462</v>
+        <v>0.009635831597992457</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00970154247196982</v>
+        <v>0.009701542471969821</v>
       </c>
       <c r="AB2" t="n">
         <v>0.009433492057884836</v>
@@ -5306,85 +5306,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009686731816984543</v>
+        <v>0.009686731816984541</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02119618326353081</v>
+        <v>0.02119618326353079</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009678153092646139</v>
+        <v>0.009678153092646137</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009598010458407837</v>
+        <v>0.009598010458407835</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009666585957309144</v>
+        <v>0.009666585957309147</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009674432345989737</v>
+        <v>0.009674432345989735</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009670040609878014</v>
+        <v>0.00967004060987801</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00965346162841416</v>
+        <v>0.009653461628414158</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="U3" t="n">
-        <v>0.009662856186270838</v>
+        <v>0.009662856186270835</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005204520411804909</v>
+        <v>0.005204520411804882</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009570067579651658</v>
+        <v>0.009570067579651656</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009671252173887205</v>
+        <v>0.009671252173887203</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009670060971553558</v>
+        <v>0.009670060971553556</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009548155508563128</v>
+        <v>0.009548155508563127</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01908267211377479</v>
+        <v>0.01908267211377482</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02365882090105602</v>
+        <v>0.023658820901056</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03455342971530213</v>
+        <v>0.03455342971530209</v>
       </c>
       <c r="E4" t="n">
         <v>0.02595791336664086</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02915666834990344</v>
+        <v>0.02915666834990343</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02515579020085658</v>
+        <v>0.02515579020085664</v>
       </c>
       <c r="H4" t="n">
         <v>0.03173450068547438</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03100374753060809</v>
+        <v>0.03100374753060805</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03185536007253952</v>
+        <v>0.03185536007253955</v>
       </c>
       <c r="K4" t="n">
         <v>0.02752264861000086</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02833884425104602</v>
+        <v>0.02833884425104595</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02327382454936856</v>
+        <v>0.02327382454936854</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03012752360198175</v>
+        <v>0.03012752360198172</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02989010873082587</v>
+        <v>0.02989010873082589</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02851900741373827</v>
+        <v>0.02851900741373829</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01889372447020354</v>
+        <v>0.01889372447020353</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04390358995135604</v>
+        <v>0.04390358995135597</v>
       </c>
       <c r="S4" t="n">
         <v>0.03009703955224195</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02094346792523545</v>
+        <v>0.02094346792523542</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02074841034460159</v>
+        <v>0.02074841034460157</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02920608973156715</v>
+        <v>0.02920608973156733</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04947925570643595</v>
+        <v>0.04947925570643591</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1953238009230988</v>
+        <v>0.1953238009230991</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1389777398064623</v>
+        <v>0.1389777398064624</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03394378151019524</v>
+        <v>0.03394378151019518</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05395652479935011</v>
+        <v>0.05395652479935022</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01552135936175948</v>
+        <v>0.01552135936175946</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01282901863960291</v>
+        <v>0.01282901863960287</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01952173178476882</v>
+        <v>0.01952173178476874</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01952173178476882</v>
+        <v>0.01952173178476874</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01595805945762475</v>
+        <v>0.01595805945762469</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01387166512824736</v>
+        <v>0.01387166512824731</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02090950945439926</v>
+        <v>0.02090950945439918</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01952173178476882</v>
+        <v>0.01952173178476874</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01952173178476882</v>
+        <v>0.01952173178476874</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01950357591138144</v>
+        <v>0.01950357591138135</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01952173178476882</v>
+        <v>0.01952173178476874</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01952173178476882</v>
+        <v>0.01952173178476874</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01952173178476813</v>
+        <v>0.01952173178476804</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03012752360198175</v>
+        <v>0.01433375943078584</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01575945928015853</v>
+        <v>0.01575945928015845</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01540998579732879</v>
+        <v>0.01540998579732873</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01151374775281729</v>
+        <v>0.01151374775281726</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01952173178476882</v>
+        <v>0.01952173178476874</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01952173178476882</v>
+        <v>0.01952173178476874</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01952173178476882</v>
+        <v>0.01952173178476874</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01625177097450652</v>
+        <v>0.01625177097450647</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01756632278335722</v>
+        <v>0.01756632278335716</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01952304709482681</v>
+        <v>0.01952304709482676</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0121271482112909</v>
+        <v>0.01212714821129085</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02617043574810417</v>
+        <v>0.02617043574810407</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01270469805687496</v>
+        <v>0.01270469805687491</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01952173178476882</v>
+        <v>0.01952173178476874</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02651283030060952</v>
+        <v>0.02651283030060944</v>
       </c>
     </row>
     <row r="6">
@@ -5570,85 +5570,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01198720453119539</v>
+        <v>0.01198720453119538</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01404884010220032</v>
+        <v>0.0140488401022003</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008488786923151566</v>
+        <v>0.008488786923151559</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01466742377013178</v>
+        <v>0.01466742377013176</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0146492666980559</v>
+        <v>0.01464926669805585</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03012752360198175</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01555564491646764</v>
+        <v>0.01555564491646762</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01574881777648724</v>
+        <v>0.01574881777648721</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01466742377013178</v>
+        <v>0.01466742377013176</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01763782853912274</v>
+        <v>0.0176378285391227</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="Z6" t="n">
         <v>0.01305148990344692</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01466742257144326</v>
+        <v>0.01466742257144325</v>
       </c>
     </row>
     <row r="7">
@@ -5658,13 +5658,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009391927628399677</v>
+        <v>0.009391927628399665</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009335211028259531</v>
+        <v>0.009335211028259528</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009058827019330902</v>
+        <v>0.009058827019330893</v>
       </c>
       <c r="E7" t="n">
         <v>0.02066932616209725</v>
@@ -5673,22 +5673,22 @@
         <v>0.009206258523524507</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00915570523589568</v>
+        <v>0.009155705235895688</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009171587578271632</v>
+        <v>0.00917158757827163</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009161405929880927</v>
+        <v>0.009161405929880925</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009077543135152907</v>
+        <v>0.009077543135152917</v>
       </c>
       <c r="K7" t="n">
         <v>0.009219395570647404</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009139543984608069</v>
+        <v>0.009139543984608067</v>
       </c>
       <c r="M7" t="n">
         <v>0.00933667381390196</v>
@@ -5697,46 +5697,46 @@
         <v>0.009146231379150709</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009102164552702463</v>
+        <v>0.009102164552702467</v>
       </c>
       <c r="P7" t="n">
-        <v>0.009145469632407043</v>
+        <v>0.009145469632407048</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009413800425260958</v>
+        <v>0.009413800425260957</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00886842723285204</v>
+        <v>0.008868427232852036</v>
       </c>
       <c r="S7" t="n">
-        <v>0.009076413550203217</v>
+        <v>0.009076413550203218</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009388744625237196</v>
+        <v>0.0093887446252372</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00935775111506254</v>
+        <v>0.009357751115062539</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004658097078869747</v>
+        <v>0.004658097078869718</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008656872756980028</v>
+        <v>0.008656872756980018</v>
       </c>
       <c r="X7" t="n">
-        <v>0.005034910087097813</v>
+        <v>0.005034910087097814</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.006620471635586281</v>
+        <v>0.006620471635586279</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008988385353936583</v>
+        <v>0.008988385353936585</v>
       </c>
       <c r="AA7" t="n">
         <v>0.008598563313781629</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.009401544179663998</v>
+        <v>0.009401544179663997</v>
       </c>
     </row>
     <row r="8">
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009440030271129456</v>
+        <v>0.009440030271129454</v>
       </c>
       <c r="C8" t="n">
         <v>0.009435089142468515</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009346094319029472</v>
+        <v>0.009346094319029467</v>
       </c>
       <c r="E8" t="n">
         <v>0.02071073320556738</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009393504893641807</v>
+        <v>0.009393504893641805</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009327128179071038</v>
+        <v>0.009327128179071043</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009378740713547249</v>
+        <v>0.009378740713547246</v>
       </c>
       <c r="I8" t="n">
         <v>0.009375421929620901</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009347971730146155</v>
+        <v>0.009347971730146148</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009394380806077483</v>
+        <v>0.009394380806077485</v>
       </c>
       <c r="L8" t="n">
         <v>0.009368192404474103</v>
       </c>
       <c r="M8" t="n">
-        <v>0.009425304956824417</v>
+        <v>0.009425304956824419</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009370557728652621</v>
+        <v>0.009370557728652612</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009356787761259809</v>
+        <v>0.009356787761259812</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009369128071052278</v>
+        <v>0.009369128071052283</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009446890956959532</v>
+        <v>0.009446890956959534</v>
       </c>
       <c r="R8" t="n">
         <v>0.009282054240833138</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009349819762107714</v>
+        <v>0.009349819762107718</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009439915914688865</v>
+        <v>0.009439915914688866</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009425989542450159</v>
+        <v>0.009425989542450157</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004967233693771159</v>
+        <v>0.004967233693771167</v>
       </c>
       <c r="W8" t="n">
-        <v>0.009230509587288691</v>
+        <v>0.009230509587288688</v>
       </c>
       <c r="X8" t="n">
-        <v>0.008138467727997957</v>
+        <v>0.008138467727997954</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.008649816415641323</v>
+        <v>0.00864981641564133</v>
       </c>
       <c r="Z8" t="n">
         <v>0.009325125018747491</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.009214007623023161</v>
+        <v>0.009214007623023157</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.009366783436013146</v>
+        <v>0.009366783436013137</v>
       </c>
     </row>
   </sheetData>
@@ -5990,85 +5990,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00945442053891369</v>
+        <v>0.009454420538913677</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009458934427095148</v>
+        <v>0.009458934427095139</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009476198820543723</v>
+        <v>0.009476198820543709</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02098239897418187</v>
+        <v>0.02098239897418184</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009469825926514854</v>
+        <v>0.009469825926514836</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009334187163326187</v>
+        <v>0.009334187163326176</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009452357971689819</v>
+        <v>0.009452357971689808</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009451606576208712</v>
+        <v>0.0094516065762087</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009476865029692163</v>
+        <v>0.009476865029692158</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009453426484665444</v>
+        <v>0.009453426484665441</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009479230691519756</v>
+        <v>0.009479230691519749</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00944077027022421</v>
+        <v>0.0094407702702242</v>
       </c>
       <c r="N2" t="n">
-        <v>0.009450972013372225</v>
+        <v>0.009450972013372213</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009514020477867431</v>
+        <v>0.009514020477867426</v>
       </c>
       <c r="P2" t="n">
-        <v>0.009479825492537211</v>
+        <v>0.009479825492537201</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.009429722601503866</v>
+        <v>0.009429722601503853</v>
       </c>
       <c r="R2" t="n">
-        <v>0.009491479666490403</v>
+        <v>0.00949147966649039</v>
       </c>
       <c r="S2" t="n">
-        <v>0.009474988916377675</v>
+        <v>0.00947498891637766</v>
       </c>
       <c r="T2" t="n">
-        <v>0.009430297539630612</v>
+        <v>0.009430297539630605</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009435267024000818</v>
+        <v>0.009435267024000812</v>
       </c>
       <c r="V2" t="n">
-        <v>0.005020274622181053</v>
+        <v>0.005020274622181054</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009517777314427805</v>
+        <v>0.009517777314427793</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01034375639875443</v>
+        <v>0.01034375639875442</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.009848206411901664</v>
+        <v>0.009848206411901648</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00947894865121501</v>
+        <v>0.009478948651215001</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.009572530808581</v>
+        <v>0.009572530808580997</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.009319240486776523</v>
+        <v>0.009319240486776516</v>
       </c>
     </row>
     <row r="3">
@@ -6078,85 +6078,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009549359581870377</v>
+        <v>0.00954935958187037</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02120162298955969</v>
+        <v>0.02120162298955968</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009543493680319008</v>
+        <v>0.009543493680319001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009410944717366228</v>
+        <v>0.009410944717366223</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009530914462217654</v>
+        <v>0.009530914462217648</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009538357834394216</v>
+        <v>0.009538357834394209</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009526577943826805</v>
+        <v>0.009526577943826798</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="R3" t="n">
-        <v>0.009500755683795365</v>
+        <v>0.009500755683795358</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00952460691814541</v>
+        <v>0.009524606918145403</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004986298875538807</v>
+        <v>0.004986298875538806</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009486911957133781</v>
+        <v>0.009486911957133774</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009533925984525874</v>
+        <v>0.009533925984525867</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009532753906901543</v>
+        <v>0.009532753906901536</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009410848443911114</v>
+        <v>0.009410848443911107</v>
       </c>
     </row>
     <row r="4">
@@ -6169,82 +6169,82 @@
         <v>0.0243587908032037</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02343058740737137</v>
+        <v>0.02343058740737138</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03164281891034393</v>
+        <v>0.03164281891034392</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03142838575852154</v>
+        <v>0.03142838575852153</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0280439908217126</v>
+        <v>0.02804399082171264</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0223805799429425</v>
+        <v>0.02238057994294258</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02680003361658128</v>
+        <v>0.02680003361658131</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02589276702032278</v>
+        <v>0.02589276702032276</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03081313519748179</v>
+        <v>0.03081313519748187</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02443477110622627</v>
+        <v>0.02443477110622628</v>
       </c>
       <c r="L4" t="n">
         <v>0.02990571116299976</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02313628396317435</v>
+        <v>0.02313628396317437</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02479861528802856</v>
+        <v>0.0247986152880286</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03746708324329184</v>
+        <v>0.03746708324329179</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03106219300887932</v>
+        <v>0.03106219300887927</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01940123003323497</v>
+        <v>0.01940123003323499</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04456869498737336</v>
+        <v>0.04456869498737331</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02883467410511031</v>
+        <v>0.02883467410511032</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02026447821869568</v>
+        <v>0.02026447821869571</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02210223542156491</v>
+        <v>0.02210223542156492</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03374346834615509</v>
+        <v>0.03374346834615514</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04072536490969764</v>
+        <v>0.04072536490969769</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2463680674351874</v>
+        <v>0.2463680674351873</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1268186335360094</v>
+        <v>0.1268186335360096</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02882676074490916</v>
+        <v>0.02882676074490914</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0556394594457669</v>
+        <v>0.05563945944576692</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02100800694544193</v>
+        <v>0.02100800694544192</v>
       </c>
     </row>
     <row r="5">
@@ -6254,7 +6254,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0128048439508149</v>
+        <v>0.01280484395081491</v>
       </c>
       <c r="C5" t="n">
         <v>0.01947590924513418</v>
@@ -6263,13 +6263,13 @@
         <v>0.01947590924513418</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01592376375997962</v>
+        <v>0.01592376375997961</v>
       </c>
       <c r="F5" t="n">
         <v>0.01384411795730908</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02085919809187464</v>
+        <v>0.02085919809187465</v>
       </c>
       <c r="H5" t="n">
         <v>0.01947590924513418</v>
@@ -6278,7 +6278,7 @@
         <v>0.01947590924513418</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01945900996655756</v>
+        <v>0.01945900996655757</v>
       </c>
       <c r="K5" t="n">
         <v>0.01947590924513418</v>
@@ -6287,19 +6287,19 @@
         <v>0.01947590924513418</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01947590924513308</v>
+        <v>0.01947590924513309</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02479861528802856</v>
+        <v>0.0143047175971823</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01572580596287082</v>
+        <v>0.01572580596287081</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01537746286611692</v>
+        <v>0.01537746286611691</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01149382736078838</v>
+        <v>0.0114938273607884</v>
       </c>
       <c r="R5" t="n">
         <v>0.01947590924513418</v>
@@ -6311,28 +6311,28 @@
         <v>0.01947590924513418</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01621667194933098</v>
+        <v>0.01621667194933099</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01753488971411927</v>
+        <v>0.01753488971411929</v>
       </c>
       <c r="W5" t="n">
         <v>0.01947722030084198</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01210524375076209</v>
+        <v>0.01210524375076208</v>
       </c>
       <c r="Y5" t="n">
         <v>0.02610335865816509</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01268092548802359</v>
+        <v>0.01268092548802361</v>
       </c>
       <c r="AA5" t="n">
         <v>0.01947590924513418</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02644439477067084</v>
+        <v>0.02644439477067087</v>
       </c>
     </row>
     <row r="6">
@@ -6342,85 +6342,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01159159363551508</v>
+        <v>0.01159159363551509</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01356696691295093</v>
+        <v>0.01356696691295091</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008239555693682194</v>
+        <v>0.008239555693682191</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01415966800167653</v>
+        <v>0.01415966800167654</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0141427676768297</v>
+        <v>0.01414276767682968</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02479861528802856</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01501072448401598</v>
+        <v>0.01501072448401597</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0151958146672546</v>
+        <v>0.01519581466725457</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01415966800167653</v>
+        <v>0.01415966800167654</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01700895927145027</v>
+        <v>0.01700895927145026</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="Z6" t="n">
         <v>0.01261134752096379</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01415966695540631</v>
+        <v>0.0141596669554063</v>
       </c>
     </row>
     <row r="7">
@@ -6430,82 +6430,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00911830322813942</v>
+        <v>0.009118303228139417</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009203487670313079</v>
+        <v>0.009203487670313088</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008997280865522895</v>
+        <v>0.008997280865522893</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02051810449839132</v>
+        <v>0.02051810449839131</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0091050399250533</v>
+        <v>0.009105039925053293</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009049774406572978</v>
+        <v>0.009049774406572973</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009139672719554244</v>
+        <v>0.009139672719554239</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009142082894112814</v>
+        <v>0.009142082894112811</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008976111596176197</v>
+        <v>0.008976111596176185</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009165729460132638</v>
+        <v>0.009165729460132634</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008974295662080693</v>
+        <v>0.008974295662080687</v>
       </c>
       <c r="M7" t="n">
-        <v>0.009206088663454574</v>
+        <v>0.009206088663454567</v>
       </c>
       <c r="N7" t="n">
-        <v>0.009143363925933828</v>
+        <v>0.009143363925933823</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008762883571583314</v>
+        <v>0.008762883571583311</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008926207333578635</v>
+        <v>0.008926207333578634</v>
       </c>
       <c r="Q7" t="n">
         <v>0.009268816580264875</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008707674704733801</v>
+        <v>0.008707674704733799</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008997627890554404</v>
+        <v>0.008997627890554397</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009266325242009769</v>
+        <v>0.009266325242009764</v>
       </c>
       <c r="U7" t="n">
-        <v>0.009181689453939572</v>
+        <v>0.009181689453939565</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0043262449639594</v>
+        <v>0.004326244963959402</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008747743030180968</v>
+        <v>0.008747743030180955</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003618660491640244</v>
+        <v>0.003618660491640237</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.006801992433915849</v>
+        <v>0.006801992433915847</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008980551071900362</v>
+        <v>0.008980551071900352</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.008425499921605722</v>
+        <v>0.008425499921605711</v>
       </c>
       <c r="AB7" t="n">
         <v>0.009142291320916573</v>
@@ -6518,85 +6518,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009265844159300977</v>
+        <v>0.009265844159300965</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009301561605108203</v>
+        <v>0.009301561605108201</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009232556880265122</v>
+        <v>0.009232556880265121</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02067139588245603</v>
+        <v>0.02067139588245602</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009270328070599748</v>
+        <v>0.009270328070599737</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009169853520933762</v>
+        <v>0.009169853520933757</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009273504778771384</v>
+        <v>0.009273504778771381</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009273850020395193</v>
+        <v>0.009273850020395191</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009224427957591461</v>
+        <v>0.009224427957591456</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009283879386880252</v>
+        <v>0.009283879386880255</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009225130410425443</v>
+        <v>0.009225130410425436</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00929213654343548</v>
+        <v>0.009292136543435475</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009273798331119671</v>
+        <v>0.009273798331119661</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009163727021866455</v>
+        <v>0.009163727021866458</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009206654951606686</v>
+        <v>0.009206654951606679</v>
       </c>
       <c r="Q8" t="n">
         <v>0.009309630276765825</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009130625293618263</v>
+        <v>0.009130625293618262</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00923150487359429</v>
+        <v>0.009231504873594287</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009309071648047071</v>
+        <v>0.009309071648047064</v>
       </c>
       <c r="U8" t="n">
         <v>0.009279238484974041</v>
       </c>
       <c r="V8" t="n">
-        <v>0.00471994798894541</v>
+        <v>0.004719947988945412</v>
       </c>
       <c r="W8" t="n">
-        <v>0.009160594863838719</v>
+        <v>0.009160594863838717</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00767368328094706</v>
+        <v>0.007673683280947045</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.008605701239272706</v>
+        <v>0.008605701239272699</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009227161302469198</v>
+        <v>0.009227161302469191</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.009068726716662319</v>
+        <v>0.009068726716662303</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.009197046139973231</v>
+        <v>0.009197046139973223</v>
       </c>
     </row>
   </sheetData>
@@ -6765,13 +6765,13 @@
         <v>0.01026608569393086</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01000513162717027</v>
+        <v>0.01000513162717028</v>
       </c>
       <c r="D2" t="n">
         <v>0.01045208345915854</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02129397400386424</v>
+        <v>0.02129397400386426</v>
       </c>
       <c r="F2" t="n">
         <v>0.01010425520837592</v>
@@ -6780,7 +6780,7 @@
         <v>0.01028226898580474</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01007737585026737</v>
+        <v>0.01007737585026736</v>
       </c>
       <c r="I2" t="n">
         <v>0.01033311592465649</v>
@@ -6789,7 +6789,7 @@
         <v>0.01046337929419773</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01057835106755386</v>
+        <v>0.01057835106755385</v>
       </c>
       <c r="L2" t="n">
         <v>0.01070043059711513</v>
@@ -6798,7 +6798,7 @@
         <v>0.01210721835454962</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01048020645153436</v>
+        <v>0.01048020645153437</v>
       </c>
       <c r="O2" t="n">
         <v>0.01018626316649987</v>
@@ -6807,22 +6807,22 @@
         <v>0.01027881823292579</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01011917755863067</v>
+        <v>0.01011917755863068</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01012698621351623</v>
+        <v>0.01012698621351624</v>
       </c>
       <c r="S2" t="n">
         <v>0.01030926663660081</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01029450826107118</v>
+        <v>0.01029450826107117</v>
       </c>
       <c r="U2" t="n">
         <v>0.01112771481576379</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00562250517093632</v>
+        <v>0.005622505170936327</v>
       </c>
       <c r="W2" t="n">
         <v>0.01051307565098608</v>
@@ -6831,13 +6831,13 @@
         <v>0.01150516043681544</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01110256326963866</v>
+        <v>0.01110256326963867</v>
       </c>
       <c r="Z2" t="n">
         <v>0.01018637091961429</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01055103277178316</v>
+        <v>0.01055103277178317</v>
       </c>
       <c r="AB2" t="n">
         <v>0.01166337581886996</v>
@@ -6859,7 +6859,7 @@
         <v>0.01007591248779717</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0214392677963101</v>
+        <v>0.02143926779631013</v>
       </c>
       <c r="F3" t="n">
         <v>0.01008164619625644</v>
@@ -6892,7 +6892,7 @@
         <v>0.01007591248779717</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01007586995584318</v>
+        <v>0.01007586995584319</v>
       </c>
       <c r="Q3" t="n">
         <v>0.01007591248779717</v>
@@ -6907,10 +6907,10 @@
         <v>0.01007591248779717</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0100767193987191</v>
+        <v>0.01007671939871911</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005554535294062581</v>
+        <v>0.005554535294062588</v>
       </c>
       <c r="W3" t="n">
         <v>0.01007591248779717</v>
@@ -6928,7 +6928,7 @@
         <v>0.01007591248779717</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009954007024806737</v>
+        <v>0.009954007024806741</v>
       </c>
     </row>
     <row r="4">
@@ -6938,79 +6938,79 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09451083406014517</v>
+        <v>0.0945108340601459</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02823679487897564</v>
+        <v>0.02823679487897566</v>
       </c>
       <c r="D4" t="n">
         <v>0.1598358499804639</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05544108915319485</v>
+        <v>0.05544108915319498</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05904483932553237</v>
+        <v>0.05904483932553232</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1113896128954846</v>
+        <v>0.1113896128954847</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05500964746256896</v>
+        <v>0.05500964746256889</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1259436751253661</v>
+        <v>0.1259436751253659</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1528975593861732</v>
+        <v>0.1528975593861734</v>
       </c>
       <c r="K4" t="n">
         <v>0.1750444455782345</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2114070276747101</v>
+        <v>0.2114070276747118</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5813854681226809</v>
+        <v>0.5813854681226821</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1631566420862825</v>
+        <v>0.1631566420862824</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07329530668200823</v>
+        <v>0.07329530668200815</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09995047435284082</v>
+        <v>0.09995047435284085</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06243184663830738</v>
+        <v>0.06243184663830741</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06857572050779424</v>
+        <v>0.06857572050779401</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1023495561922394</v>
+        <v>0.1023495561922396</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1147295162591988</v>
+        <v>0.1147295162591987</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3247830650873185</v>
+        <v>0.3247830650873187</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04661479701210192</v>
+        <v>0.04661479701210199</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1695923322104665</v>
+        <v>0.1695923322104666</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4527858725395604</v>
+        <v>0.4527858725395619</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3250388970234838</v>
+        <v>0.3250388970234839</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.07510013275866599</v>
+        <v>0.07510013275866607</v>
       </c>
       <c r="AA4" t="n">
         <v>0.1794373049507177</v>
@@ -7026,85 +7026,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01481069431718182</v>
+        <v>0.01481069431718185</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02267143088860835</v>
+        <v>0.02267143088860837</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02267143088860835</v>
+        <v>0.02267143088860837</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01848582054158436</v>
+        <v>0.01848582054158438</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01603530520462162</v>
+        <v>0.01603530520462164</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02430140582461372</v>
+        <v>0.02430140582461375</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02267143088860835</v>
+        <v>0.02267143088860836</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02267143088860835</v>
+        <v>0.02267143088860837</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0226503683510429</v>
+        <v>0.02265036835104293</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02267143088860835</v>
+        <v>0.02267143088860837</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02267143088860835</v>
+        <v>0.02267143088860837</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02267143088860988</v>
+        <v>0.02267143088860991</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1631566420862825</v>
+        <v>0.01657804497312705</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01825256033059977</v>
+        <v>0.01825256033059978</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01784209615452759</v>
+        <v>0.0178420961545276</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01326588016839643</v>
+        <v>0.01326588016839646</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02267143088860835</v>
+        <v>0.02267143088860836</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02267143088860835</v>
+        <v>0.02267143088860836</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02267143088860835</v>
+        <v>0.02267143088860837</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01883205189281214</v>
+        <v>0.01883205189281218</v>
       </c>
       <c r="V5" t="n">
         <v>0.02037880414414587</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02267297574840146</v>
+        <v>0.0226729757484015</v>
       </c>
       <c r="X5" t="n">
         <v>0.01398633229457855</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03048263460560468</v>
+        <v>0.03048263460560472</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01466467709967854</v>
+        <v>0.01466467709967856</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02267143088860835</v>
+        <v>0.02267143088860836</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03088262754139415</v>
+        <v>0.03088262754139413</v>
       </c>
     </row>
     <row r="6">
@@ -7114,85 +7114,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01534267232447106</v>
+        <v>0.01534267232447104</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01808760382851109</v>
+        <v>0.01808760382851106</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01068476049870304</v>
+        <v>0.01068476049870303</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01891120709858947</v>
+        <v>0.01891120709858946</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01889015009607279</v>
+        <v>0.01889015009607274</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1631566420862825</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02009381485013479</v>
+        <v>0.02009381485013477</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02035101174596388</v>
+        <v>0.02035101174596389</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01891120709858947</v>
+        <v>0.01891120709858946</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="S6" t="n">
         <v>0.01891121263363822</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02288797927754425</v>
+        <v>0.02288797927754427</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01675969795628934</v>
+        <v>0.01675969795628932</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01891121263363823</v>
+        <v>0.01891121263363822</v>
       </c>
     </row>
     <row r="7">
@@ -7202,85 +7202,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008027214067291222</v>
+        <v>0.008027214067291217</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009687847800174374</v>
+        <v>0.009687847800174376</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006969449739333731</v>
+        <v>0.006969449739333727</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02030971624837423</v>
+        <v>0.02030971624837426</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009048410017388398</v>
+        <v>0.009048410017388403</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007539251316680245</v>
+        <v>0.00753925131668024</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009170535006513218</v>
+        <v>0.00917053500651323</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007670836438956201</v>
+        <v>0.007670836438956198</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006794569316848051</v>
+        <v>0.006794569316848047</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006243967689208971</v>
+        <v>0.006243967689208968</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00547236066331972</v>
+        <v>0.005472360663319704</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.002676933806135649</v>
+        <v>-0.00267693380613564</v>
       </c>
       <c r="N7" t="n">
-        <v>0.006790834270211913</v>
+        <v>0.006790834270211933</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008500366140023021</v>
+        <v>0.008500366140023018</v>
       </c>
       <c r="P7" t="n">
-        <v>0.007946967999602809</v>
+        <v>0.007946967999602804</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008916471595007103</v>
+        <v>0.008916471595007098</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008882153804243271</v>
+        <v>0.008882153804243269</v>
       </c>
       <c r="S7" t="n">
-        <v>0.007777474585602437</v>
+        <v>0.00777747458560243</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007893844845526405</v>
+        <v>0.007893844845526412</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002944367473380506</v>
+        <v>0.002944367473380497</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004650796181820321</v>
+        <v>0.004650796181820324</v>
       </c>
       <c r="W7" t="n">
-        <v>0.006585823223268192</v>
+        <v>0.006585823223268196</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0007388214480796034</v>
+        <v>0.0007388214480795943</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003117953439314408</v>
+        <v>0.003117953439314421</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008507763258523661</v>
+        <v>0.008507763258523657</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.006364830031536851</v>
+        <v>0.006364830031536869</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.0008976919028874844</v>
+        <v>-0.0008976919028874641</v>
       </c>
     </row>
     <row r="8">
@@ -7290,85 +7290,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009333921383786194</v>
+        <v>0.009333921383786178</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009821338303764736</v>
+        <v>0.009821338303764734</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009038633008898282</v>
+        <v>0.009038633008898287</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02078002444988622</v>
+        <v>0.02078002444988624</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009634129454262636</v>
+        <v>0.009634129454262641</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009155866543561488</v>
+        <v>0.009155866543561484</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009665426211016322</v>
+        <v>0.009665426211016329</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009238798657911244</v>
+        <v>0.009238798657911249</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008976290036965061</v>
+        <v>0.008976290036965057</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008833401727805263</v>
+        <v>0.008833401727805267</v>
       </c>
       <c r="L8" t="n">
         <v>0.008605799846328704</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00630463264990044</v>
+        <v>0.006304632649900441</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00898548539360995</v>
+        <v>0.008985485393609957</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009469384557294337</v>
+        <v>0.009469384557294342</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009310161058428428</v>
+        <v>0.009310161058428431</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009591628257492291</v>
+        <v>0.0095916282574923</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009583559409824971</v>
+        <v>0.009583559409824973</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009263470066415227</v>
+        <v>0.009263470066415225</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009301660530000989</v>
+        <v>0.009301660530001001</v>
       </c>
       <c r="U8" t="n">
         <v>0.007882471960277779</v>
       </c>
       <c r="V8" t="n">
-        <v>0.005211300994820428</v>
+        <v>0.005211300994820429</v>
       </c>
       <c r="W8" t="n">
-        <v>0.008925073913370839</v>
+        <v>0.008925073913370831</v>
       </c>
       <c r="X8" t="n">
-        <v>0.007260565922595854</v>
+        <v>0.00726056592259586</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.007936669728879173</v>
+        <v>0.007936669728879178</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009472535683788912</v>
+        <v>0.009472535683788915</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.00886247842766665</v>
+        <v>0.008862478427666645</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.006725818224456502</v>
+        <v>0.006725818224456509</v>
       </c>
     </row>
   </sheetData>
@@ -7540,76 +7540,76 @@
         <v>0.009768946506524059</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009827475226407771</v>
+        <v>0.00982747522640778</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02106740711120973</v>
+        <v>0.02106740711120975</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009777110375905078</v>
+        <v>0.009777110375905083</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009992529291186361</v>
+        <v>0.009992529291186365</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009770643105804286</v>
+        <v>0.009770643105804288</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009796125124196293</v>
+        <v>0.009796125124196298</v>
       </c>
       <c r="J2" t="n">
         <v>0.01001544863865775</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009858515366858698</v>
+        <v>0.009858515366858701</v>
       </c>
       <c r="L2" t="n">
         <v>0.01004010083844343</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009929518441474916</v>
+        <v>0.009929518441474907</v>
       </c>
       <c r="N2" t="n">
         <v>0.0098145854278515</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009789365930280841</v>
+        <v>0.009789365930280848</v>
       </c>
       <c r="P2" t="n">
-        <v>0.009966502110320134</v>
+        <v>0.009966502110320141</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.009803150511762214</v>
+        <v>0.009803150511762213</v>
       </c>
       <c r="R2" t="n">
-        <v>0.009831489258574135</v>
+        <v>0.009831489258574137</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00984396833103288</v>
+        <v>0.009843968331032883</v>
       </c>
       <c r="T2" t="n">
-        <v>0.009776078957747156</v>
+        <v>0.009776078957747144</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009917841953061803</v>
+        <v>0.0099178419530618</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00533003935296604</v>
+        <v>0.005330039352966038</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009954649535864392</v>
+        <v>0.009954649535864401</v>
       </c>
       <c r="X2" t="n">
         <v>0.01130837287345513</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01183737385826743</v>
+        <v>0.01183737385826742</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009807204219738283</v>
+        <v>0.009807204219738285</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.009898591796625536</v>
+        <v>0.009898591796625538</v>
       </c>
       <c r="AB2" t="n">
         <v>0.02119486674275919</v>
@@ -7631,7 +7631,7 @@
         <v>0.00985901275870941</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02131058592162276</v>
+        <v>0.02131058592162275</v>
       </c>
       <c r="F3" t="n">
         <v>0.009867104879801991</v>
@@ -7664,7 +7664,7 @@
         <v>0.00985901275870941</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009858992397033866</v>
+        <v>0.009858992397033863</v>
       </c>
       <c r="Q3" t="n">
         <v>0.00985901275870941</v>
@@ -7682,7 +7682,7 @@
         <v>0.009851807973426689</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005337026968938309</v>
+        <v>0.00533702696893831</v>
       </c>
       <c r="W3" t="n">
         <v>0.00985901275870941</v>
@@ -7710,76 +7710,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01588730813078054</v>
+        <v>0.01588730813078053</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02068525545050152</v>
+        <v>0.02068525545050154</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03946844866467174</v>
+        <v>0.03946844866467179</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02685664318729243</v>
+        <v>0.02685664318729247</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02485663781551739</v>
+        <v>0.0248566378155174</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08591240206239326</v>
+        <v>0.08591240206239324</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02596863309032217</v>
+        <v>0.02596863309032218</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03199485355512767</v>
+        <v>0.03199485355512766</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08626498656576052</v>
+        <v>0.08626498656576061</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04374618467308975</v>
+        <v>0.04374618467308976</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08478237681564103</v>
+        <v>0.08478237681564109</v>
       </c>
       <c r="M4" t="n">
         <v>0.06306006864648923</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03586611091647035</v>
+        <v>0.03586611091647041</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02728568978856017</v>
+        <v>0.02728568978856036</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06841088479268165</v>
+        <v>0.06841088479268154</v>
       </c>
       <c r="Q4" t="n">
         <v>0.03144748577332993</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04601222987696688</v>
+        <v>0.04601222987696695</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0392535463551828</v>
+        <v>0.03925354635518279</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02649002341706275</v>
+        <v>0.02649002341706272</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05899688897694328</v>
+        <v>0.05899688897694323</v>
       </c>
       <c r="V4" t="n">
-        <v>0.025826970149062</v>
+        <v>0.02582697014906197</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07083562405262109</v>
+        <v>0.07083562405262106</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4331380406253187</v>
+        <v>0.4331380406253186</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5409192454902122</v>
+        <v>0.5409192454902111</v>
       </c>
       <c r="Z4" t="n">
         <v>0.03076180606311501</v>
@@ -7788,7 +7788,7 @@
         <v>0.05666776165272155</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.139857348992824</v>
+        <v>3.139857348992826</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01346273053120797</v>
+        <v>0.01346273053120799</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02049753804691111</v>
+        <v>0.02049753804691114</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02049753804691111</v>
+        <v>0.02049753804691114</v>
       </c>
       <c r="E5" t="n">
         <v>0.01675171055864492</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01455867132462174</v>
+        <v>0.01455867132462176</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02195625121279824</v>
+        <v>0.02195625121279825</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02049753804691111</v>
+        <v>0.02049753804691114</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02049753804691111</v>
+        <v>0.02049753804691114</v>
       </c>
       <c r="J5" t="n">
         <v>0.0204776117852132</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02049753804691111</v>
+        <v>0.02049753804691114</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02049753804691111</v>
+        <v>0.02049753804691114</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02049753804691131</v>
+        <v>0.02049753804691134</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03586611091647035</v>
+        <v>0.01504438532457646</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0165429590416037</v>
+        <v>0.01654295904160372</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01617562241294196</v>
+        <v>0.01617562241294199</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01208023029273797</v>
+        <v>0.01208023029273798</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02049753804691111</v>
+        <v>0.02049753804691114</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02049753804691111</v>
+        <v>0.02049753804691114</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02049753804691111</v>
+        <v>0.02049753804691114</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01705996269747947</v>
+        <v>0.01705996269747948</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01843662720642839</v>
+        <v>0.01843662720642841</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02049892058813995</v>
+        <v>0.02049892058813998</v>
       </c>
       <c r="X5" t="n">
         <v>0.0127249843799171</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02748527893944699</v>
+        <v>0.027485278939447</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01333205536993292</v>
+        <v>0.01333205536993295</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02049753804691111</v>
+        <v>0.02049753804691114</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02784598273813857</v>
+        <v>0.02784598273813862</v>
       </c>
     </row>
     <row r="6">
@@ -7895,13 +7895,13 @@
         <v>0.01593505232748491</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0152578501771195</v>
+        <v>0.01525785017711948</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009170936814317373</v>
+        <v>0.009170936814317378</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01593504967019829</v>
+        <v>0.01593504967019831</v>
       </c>
       <c r="H6" t="n">
         <v>0.01593505232748491</v>
@@ -7916,13 +7916,13 @@
         <v>0.01593505232748491</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01593505232748492</v>
+        <v>0.01593505232748491</v>
       </c>
       <c r="M6" t="n">
         <v>0.01593505232748491</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03586611091647035</v>
+        <v>0.01593505232748491</v>
       </c>
       <c r="O6" t="n">
         <v>0.0169074369820909</v>
@@ -7931,7 +7931,7 @@
         <v>0.01711891453907088</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01593504967019829</v>
+        <v>0.01593504967019831</v>
       </c>
       <c r="R6" t="n">
         <v>0.01593505232748491</v>
@@ -7974,85 +7974,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00966811361695726</v>
+        <v>0.009668113616957264</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009604515423025681</v>
+        <v>0.009604515423025678</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009156101029481171</v>
+        <v>0.009156101029481173</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02076735211098189</v>
+        <v>0.02076735211098187</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009504353937653127</v>
+        <v>0.009504353937653124</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007700417407405395</v>
+        <v>0.007700417407405389</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009491567238729761</v>
+        <v>0.009491567238729754</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00934072701459799</v>
+        <v>0.009340727014597984</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007964904620062102</v>
+        <v>0.007964904620062108</v>
       </c>
       <c r="K7" t="n">
         <v>0.009000817448550334</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007892477688447629</v>
+        <v>0.007892477688447625</v>
       </c>
       <c r="M7" t="n">
-        <v>0.008563355423250076</v>
+        <v>0.008563355423250082</v>
       </c>
       <c r="N7" t="n">
-        <v>0.009228904986991851</v>
+        <v>0.00922890498699184</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009371114923986998</v>
+        <v>0.009371114923987007</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008314642972586286</v>
+        <v>0.008314642972586288</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009297123332885472</v>
+        <v>0.00929712333288548</v>
       </c>
       <c r="R7" t="n">
-        <v>0.009030391597125997</v>
+        <v>0.009030391597126</v>
       </c>
       <c r="S7" t="n">
         <v>0.0090493586663621</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00945741843483606</v>
+        <v>0.009457418434836053</v>
       </c>
       <c r="U7" t="n">
-        <v>0.008567833876903285</v>
+        <v>0.008567833876903281</v>
       </c>
       <c r="V7" t="n">
         <v>0.004894553781566286</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008400107334325859</v>
+        <v>0.008400107334325843</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0001630860718974731</v>
+        <v>-0.0001630860718974773</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.002691368096120122</v>
+        <v>-0.002691368096120119</v>
       </c>
       <c r="Z7" t="n">
         <v>0.009273864305351171</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.008731885663066059</v>
+        <v>0.008731885663066066</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.05818766316959319</v>
+        <v>-0.05818766316959322</v>
       </c>
     </row>
     <row r="8">
@@ -8062,85 +8062,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009652674759388399</v>
+        <v>0.009652674759388394</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009645564119955144</v>
+        <v>0.009645564119955147</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00950764814956215</v>
+        <v>0.009507648149562157</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02082023399618475</v>
+        <v>0.02082023399618478</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009612057541208686</v>
+        <v>0.009612057541208691</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009043144740400475</v>
+        <v>0.009043144740400477</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00960345422323417</v>
+        <v>0.009603454223234159</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009560303458946942</v>
+        <v>0.009560303458946944</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009158731608655874</v>
+        <v>0.009158731608655882</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009466044776530933</v>
+        <v>0.00946604477653093</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009145321114498898</v>
+        <v>0.0091453211144989</v>
       </c>
       <c r="M8" t="n">
-        <v>0.009339990224825977</v>
+        <v>0.009339990224825973</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009527884383685688</v>
+        <v>0.009527884383685674</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009567370860643997</v>
+        <v>0.009567370860644013</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00926381820064689</v>
+        <v>0.009263818200646879</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009547489032376951</v>
+        <v>0.009547489032376972</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009462016743422111</v>
+        <v>0.009462016743422112</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009475573138800372</v>
+        <v>0.009475573138800365</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009593352260579609</v>
+        <v>0.00959335226057959</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009333629647360984</v>
+        <v>0.009333629647360972</v>
       </c>
       <c r="V8" t="n">
-        <v>0.005128712642633389</v>
+        <v>0.005128712642633386</v>
       </c>
       <c r="W8" t="n">
-        <v>0.009290842918514132</v>
+        <v>0.009290842918514145</v>
       </c>
       <c r="X8" t="n">
-        <v>0.006793783278970472</v>
+        <v>0.006793783278970457</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.006126910573629335</v>
+        <v>0.00612691057362931</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00954041780784488</v>
+        <v>0.009540417807844866</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.009385745376166897</v>
+        <v>0.009385745376166902</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.009711120282357606</v>
+        <v>-0.009711120282357617</v>
       </c>
     </row>
   </sheetData>
